--- a/Diseño Red FT.xlsx
+++ b/Diseño Red FT.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00\CFT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EAEDBC-37CE-4DDC-B40A-7BE9E2E6CB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B869B26C-F11A-4810-ABA2-7F2C8FA06F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Red" sheetId="1" r:id="rId1"/>
     <sheet name="Grafo Visual" sheetId="2" r:id="rId2"/>
     <sheet name="MatrizDeAdyacencia" sheetId="3" r:id="rId3"/>
+    <sheet name="MatrizPonderada" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -92,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="196">
   <si>
     <t>GENERADOR DE MODELOS DE REDES SINTÉTICAS DE FINANCIACIÓN DEL TERRORISMO</t>
   </si>
@@ -671,13 +672,22 @@
   </si>
   <si>
     <t>La hoja ENLACES es la fuente de verdad de la red.</t>
+  </si>
+  <si>
+    <t>Pesos por Propiedad del Enlace</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Peso</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -762,8 +772,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -793,8 +824,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1017,11 +1054,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1116,6 +1162,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1152,17 +1204,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="132">
+  <dxfs count="129">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFFFFFF"/>
@@ -1437,6 +1543,1267 @@
           <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
       <font>
@@ -1542,23 +2909,6 @@
           <color rgb="FFD9D9D9"/>
         </top>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-      <border outline="0">
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
       </border>
     </dxf>
     <dxf>
@@ -1597,1075 +2947,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFE89F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.1498764000366222"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF006100"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFED7D31"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF006100"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFED7D31"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF006100"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFED7D31"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF006100"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFED7D31"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF006100"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFED7D31"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF006100"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFED7D31"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF006100"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFED7D31"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF006100"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFED7D31"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF006100"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFED7D31"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF006100"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFED7D31"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1" tint="0.34998626667073579"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="7"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2675,6 +2956,11 @@
         <family val="2"/>
       </font>
       <alignment horizontal="center" vertical="center"/>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3026,118 +3312,223 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblTiposDeNodo" displayName="tblTiposDeNodo" ref="A4:C8" headerRowDxfId="131" dataDxfId="130" totalsRowDxfId="129">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblTiposDeNodo" displayName="tblTiposDeNodo" ref="A4:C8" headerRowDxfId="128" dataDxfId="127" totalsRowDxfId="126">
   <autoFilter ref="A4:C8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tipo" dataDxfId="128"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descripción" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Capa" dataDxfId="126"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tipo" dataDxfId="125"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descripción" dataDxfId="124"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Capa" dataDxfId="123"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblNodos" displayName="tblNodos" ref="E4:H23" headerRowDxfId="125" dataDxfId="124" totalsRowDxfId="123">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblNodos" displayName="tblNodos" ref="E4:H23" headerRowDxfId="122" dataDxfId="121" totalsRowDxfId="120">
   <autoFilter ref="E4:H23" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="NodoID" dataDxfId="122"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Nombre" dataDxfId="121"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tipo" dataDxfId="120"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Activo" dataDxfId="119"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="NodoID" dataDxfId="119"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Nombre" dataDxfId="118"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tipo" dataDxfId="117"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Activo" dataDxfId="116"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="J4:V58" headerRowDxfId="118" dataDxfId="117" totalsRowDxfId="116">
-  <autoFilter ref="J4:V58" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="29"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="28"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Fuente GAFI" dataDxfId="110"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Observaciones" dataDxfId="109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="J4:W58" headerRowDxfId="115" dataDxfId="114" totalsRowDxfId="113">
+  <autoFilter ref="J4:W58" xr:uid="{00000000-0009-0000-0100-000003000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="O1"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="I1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="112"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="111"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="110"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="109"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="108"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="107"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="105"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="104"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="103"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="102"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Fuente GAFI" dataDxfId="101"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Observaciones" dataDxfId="100"/>
+    <tableColumn id="14" xr3:uid="{9DEDFDB7-A2E0-4CB1-947F-B304ED7D5C52}" name="Peso" dataDxfId="55" totalsRowDxfId="56">
+      <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="108" dataDxfId="106" headerRowBorderDxfId="107" tableBorderDxfId="105" totalsRowBorderDxfId="104">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="99" dataDxfId="97" headerRowBorderDxfId="98" tableBorderDxfId="96" totalsRowBorderDxfId="95">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="103">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="94">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="102"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="101">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="92">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,D$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="100">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="91">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,E$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="99">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="90">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,F$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="98">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="89">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,G$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="97">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="88">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,H$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="96">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="87">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,I$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="I1" dataDxfId="95">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="I1" dataDxfId="86">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,J$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="I2" dataDxfId="94">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="I2" dataDxfId="85">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,K$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="I3" dataDxfId="93">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="I3" dataDxfId="84">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,L$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="I4" dataDxfId="92">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="I4" dataDxfId="83">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,M$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="I5" dataDxfId="91">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="I5" dataDxfId="82">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,N$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="I6" dataDxfId="90">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="I6" dataDxfId="81">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,O$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="I7" dataDxfId="89">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="I7" dataDxfId="80">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,P$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="I8" dataDxfId="88">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="I8" dataDxfId="79">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,Q$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="I9" dataDxfId="87">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="I9" dataDxfId="78">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,R$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="G1" dataDxfId="86">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="G1" dataDxfId="77">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,S$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="G2" dataDxfId="85">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="G2" dataDxfId="76">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,T$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="G3" dataDxfId="84">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="G3" dataDxfId="75">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,U$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D" dataDxfId="83">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D" dataDxfId="74">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$K$5:$K$58,$C4,Red!$L$5:$L$58,V$3,Red!$N$5:$N$58,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{619F938E-46CC-49F1-9A1F-6017755965D1}" name="tblMatrizPonderada" displayName="tblMatrizPonderada" ref="B3:V22" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72" headerRowBorderDxfId="70" tableBorderDxfId="71" totalsRowBorderDxfId="69">
+  <tableColumns count="21">
+    <tableColumn id="21" xr3:uid="{2A9AC9D7-CC14-4058-8CF2-7CDFEC15F78F}" name="Nombre Nodo" dataDxfId="68">
+      <calculatedColumnFormula>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="1" xr3:uid="{3A911174-7F39-43D0-8D1B-0D1A251C78CF}" name="NodoOrigen \ NodoDestino" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{79E6108F-3B54-4663-83BD-0E9A6288B0A8}" name="O1" dataDxfId="30">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{74BBA163-10F6-4D74-863C-C4517633500F}" name="O2" dataDxfId="36">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{5D6ADA5C-E165-41EC-803D-18F7A270611C}" name="O3" dataDxfId="35">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{035B34FA-1623-4B86-B0EE-0CC6694FFD7C}" name="O4" dataDxfId="34">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{27739639-E082-4698-9A4C-15EDA8612A83}" name="O5" dataDxfId="33">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{ED768978-7E7B-49CD-A202-FE8EBE9E64E0}" name="O6" dataDxfId="54">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{37684012-4DC0-48DA-8E67-185403ABB81C}" name="I1" dataDxfId="29">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{E3684910-7769-4AEF-8800-33DC2F8D7ABC}" name="I2" dataDxfId="53">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{A095B3C4-5019-4082-93A5-E12BDE733061}" name="I3" dataDxfId="52">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{C5072B89-856A-4694-9D8B-17C4DB67DFF8}" name="I4" dataDxfId="51">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{0BD76649-1EE0-46D9-8718-F9A6F67BE379}" name="I5" dataDxfId="50">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{263255E9-BE7D-4E45-A463-5AD358998CB9}" name="I6" dataDxfId="49">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{7AF510BB-CB1B-461F-8746-C7133DC25996}" name="I7" dataDxfId="48">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{42A7B19E-8A6C-4FA9-A2E9-2B83EC8917D4}" name="I8" dataDxfId="47">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{C9AE28B0-4117-4A3D-8381-F7E9417F1616}" name="I9" dataDxfId="46">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{92A0B734-1347-429D-A2CB-8D857E4CD34E}" name="G1" dataDxfId="45">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="18" xr3:uid="{667134D2-C221-4A4D-9FB1-909ACDC0DDB5}" name="G2" dataDxfId="44">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="19" xr3:uid="{338C87EB-B9DD-49EE-9C5C-4BCE63EF4744}" name="G3" dataDxfId="43">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="20" xr3:uid="{6E3807F5-486A-4D01-9C7A-D8CBDABFB157}" name="D" dataDxfId="42">
+      <calculatedColumnFormula>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}" name="tblPesos" displayName="tblPesos" ref="Y4:AD9" totalsRowShown="0" headerRowDxfId="57" dataDxfId="58" headerRowBorderDxfId="65" tableBorderDxfId="66">
+  <autoFilter ref="Y4:AD9" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{E1E6CBAC-71D7-49B4-97B4-D7CD1992E449}" name="Valor" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{6BADB4E4-C92B-4EF0-944B-902CF0A800D2}" name="Eficiencia" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{5D97B706-55F4-46C7-B8B4-663F39805E8B}" name="Coste" dataDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{F51D81B9-0B45-49B1-93E6-620238508F92}" name="Exposición" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{3AA3F40F-30E8-4B81-A020-7A0005D3DBF0}" name="Capacidad" dataDxfId="60"/>
+    <tableColumn id="7" xr3:uid="{11B22656-E184-490F-8509-2FF36373FA3A}" name="Resiliencia" dataDxfId="59"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3456,61 +3847,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
+      <c r="A1" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
       <c r="V1" s="28"/>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="E3" s="34" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="E3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="J3" s="34" t="s">
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="J3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
       <c r="W3" s="18"/>
     </row>
     <row r="4" spans="1:23" s="18" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3553,19 +3944,19 @@
       <c r="O4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="48" t="s">
+      <c r="P4" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="Q4" s="48" t="s">
+      <c r="Q4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="R4" s="48" t="s">
+      <c r="R4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="S4" s="48" t="s">
+      <c r="S4" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="T4" s="49" t="s">
+      <c r="T4" s="33" t="s">
         <v>20</v>
       </c>
       <c r="U4" s="2" t="s">
@@ -3574,8 +3965,11 @@
       <c r="V4" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="W4" s="54" t="s">
+        <v>195</v>
+      </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -3636,8 +4030,12 @@
       <c r="V5" s="25" t="s">
         <v>182</v>
       </c>
+      <c r="W5" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>21</v>
+      </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
@@ -3698,8 +4096,12 @@
       <c r="V6" s="25" t="s">
         <v>89</v>
       </c>
+      <c r="W6" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>19</v>
+      </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
@@ -3760,8 +4162,12 @@
       <c r="V7" s="25" t="s">
         <v>172</v>
       </c>
+      <c r="W7" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>19</v>
+      </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>51</v>
       </c>
@@ -3822,8 +4228,12 @@
       <c r="V8" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="W8" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>19</v>
+      </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E9" s="1" t="s">
         <v>60</v>
       </c>
@@ -3875,8 +4285,12 @@
       <c r="V9" s="25" t="s">
         <v>162</v>
       </c>
+      <c r="W9" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>18</v>
+      </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E10" s="1" t="s">
         <v>65</v>
       </c>
@@ -3928,8 +4342,12 @@
       <c r="V10" s="25" t="s">
         <v>59</v>
       </c>
+      <c r="W10" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>18</v>
+      </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E11" s="1" t="s">
         <v>28</v>
       </c>
@@ -3981,8 +4399,12 @@
       <c r="V11" s="25" t="s">
         <v>140</v>
       </c>
+      <c r="W11" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>18</v>
+      </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E12" s="1" t="s">
         <v>41</v>
       </c>
@@ -4034,8 +4456,12 @@
       <c r="V12" s="25" t="s">
         <v>170</v>
       </c>
+      <c r="W12" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>18</v>
+      </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E13" s="1" t="s">
         <v>49</v>
       </c>
@@ -4087,8 +4513,12 @@
       <c r="V13" s="25" t="s">
         <v>93</v>
       </c>
+      <c r="W13" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E14" s="1" t="s">
         <v>56</v>
       </c>
@@ -4140,8 +4570,12 @@
       <c r="V14" s="25" t="s">
         <v>108</v>
       </c>
+      <c r="W14" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E15" s="1" t="s">
         <v>82</v>
       </c>
@@ -4193,8 +4627,12 @@
       <c r="V15" s="25" t="s">
         <v>117</v>
       </c>
+      <c r="W15" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E16" s="1" t="s">
         <v>86</v>
       </c>
@@ -4246,8 +4684,12 @@
       <c r="V16" s="25" t="s">
         <v>142</v>
       </c>
+      <c r="W16" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E17" s="1" t="s">
         <v>90</v>
       </c>
@@ -4299,8 +4741,12 @@
       <c r="V17" s="25" t="s">
         <v>112</v>
       </c>
+      <c r="W17" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E18" s="1" t="s">
         <v>94</v>
       </c>
@@ -4352,8 +4798,12 @@
       <c r="V18" s="25" t="s">
         <v>146</v>
       </c>
+      <c r="W18" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E19" s="1" t="s">
         <v>63</v>
       </c>
@@ -4405,8 +4855,12 @@
       <c r="V19" s="25" t="s">
         <v>148</v>
       </c>
+      <c r="W19" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E20" s="1" t="s">
         <v>101</v>
       </c>
@@ -4458,8 +4912,12 @@
       <c r="V20" s="25" t="s">
         <v>176</v>
       </c>
+      <c r="W20" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E21" s="1" t="s">
         <v>105</v>
       </c>
@@ -4511,8 +4969,12 @@
       <c r="V21" s="25" t="s">
         <v>97</v>
       </c>
+      <c r="W21" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>15</v>
+      </c>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E22" s="1" t="s">
         <v>109</v>
       </c>
@@ -4564,8 +5026,12 @@
       <c r="V22" s="25" t="s">
         <v>43</v>
       </c>
+      <c r="W22" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>21</v>
+      </c>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="E23" s="1" t="s">
         <v>51</v>
       </c>
@@ -4617,8 +5083,12 @@
       <c r="V23" s="25" t="s">
         <v>123</v>
       </c>
+      <c r="W23" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>21</v>
+      </c>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J24" s="1" t="s">
         <v>165</v>
       </c>
@@ -4658,8 +5128,12 @@
       <c r="V24" s="25" t="s">
         <v>166</v>
       </c>
+      <c r="W24" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>21</v>
+      </c>
     </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J25" s="1" t="s">
         <v>185</v>
       </c>
@@ -4699,8 +5173,12 @@
       <c r="V25" s="25" t="s">
         <v>186</v>
       </c>
+      <c r="W25" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>20</v>
+      </c>
     </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J26" s="1" t="s">
         <v>70</v>
       </c>
@@ -4740,8 +5218,12 @@
       <c r="V26" s="25" t="s">
         <v>72</v>
       </c>
+      <c r="W26" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>22</v>
+      </c>
     </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J27" s="1" t="s">
         <v>80</v>
       </c>
@@ -4781,8 +5263,12 @@
       <c r="V27" s="25" t="s">
         <v>81</v>
       </c>
+      <c r="W27" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>22</v>
+      </c>
     </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="B28" s="29" t="s">
         <v>124</v>
       </c>
@@ -4831,17 +5317,21 @@
       <c r="V28" s="25" t="s">
         <v>134</v>
       </c>
+      <c r="W28" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>22</v>
+      </c>
     </row>
-    <row r="29" spans="2:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
+    <row r="29" spans="2:23" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="43"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="45"/>
       <c r="J29" s="1" t="s">
         <v>131</v>
       </c>
@@ -4881,17 +5371,21 @@
       <c r="V29" s="25" t="s">
         <v>132</v>
       </c>
+      <c r="W29" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>18</v>
+      </c>
     </row>
-    <row r="30" spans="2:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="36" t="s">
+    <row r="30" spans="2:23" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="38"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="40"/>
       <c r="J30" s="1" t="s">
         <v>48</v>
       </c>
@@ -4931,8 +5425,12 @@
       <c r="V30" s="25" t="s">
         <v>50</v>
       </c>
+      <c r="W30" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J31" s="1" t="s">
         <v>74</v>
       </c>
@@ -4972,8 +5470,12 @@
       <c r="V31" s="25" t="s">
         <v>75</v>
       </c>
+      <c r="W31" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J32" s="1" t="s">
         <v>114</v>
       </c>
@@ -5013,8 +5515,12 @@
       <c r="V32" s="25" t="s">
         <v>115</v>
       </c>
+      <c r="W32" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="33" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J33" s="1" t="s">
         <v>137</v>
       </c>
@@ -5054,8 +5560,12 @@
       <c r="V33" s="25" t="s">
         <v>138</v>
       </c>
+      <c r="W33" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="34" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J34" s="1" t="s">
         <v>167</v>
       </c>
@@ -5095,8 +5605,12 @@
       <c r="V34" s="25" t="s">
         <v>168</v>
       </c>
+      <c r="W34" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="35" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J35" s="1" t="s">
         <v>187</v>
       </c>
@@ -5136,8 +5650,12 @@
       <c r="V35" s="25" t="s">
         <v>188</v>
       </c>
+      <c r="W35" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="36" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J36" s="1" t="s">
         <v>84</v>
       </c>
@@ -5177,8 +5695,12 @@
       <c r="V36" s="25" t="s">
         <v>85</v>
       </c>
+      <c r="W36" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>18</v>
+      </c>
     </row>
-    <row r="37" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J37" s="1" t="s">
         <v>135</v>
       </c>
@@ -5218,8 +5740,12 @@
       <c r="V37" s="25" t="s">
         <v>136</v>
       </c>
+      <c r="W37" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>18</v>
+      </c>
     </row>
-    <row r="38" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J38" s="1" t="s">
         <v>143</v>
       </c>
@@ -5259,8 +5785,12 @@
       <c r="V38" s="25" t="s">
         <v>144</v>
       </c>
+      <c r="W38" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>16</v>
+      </c>
     </row>
-    <row r="39" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J39" s="1" t="s">
         <v>173</v>
       </c>
@@ -5300,8 +5830,12 @@
       <c r="V39" s="25" t="s">
         <v>174</v>
       </c>
+      <c r="W39" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>16</v>
+      </c>
     </row>
-    <row r="40" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="10:23" x14ac:dyDescent="0.25">
       <c r="J40" s="1" t="s">
         <v>27</v>
       </c>
@@ -5341,8 +5875,12 @@
       <c r="V40" s="25" t="s">
         <v>35</v>
       </c>
+      <c r="W40" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>23</v>
+      </c>
     </row>
-    <row r="41" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J41" s="1" t="s">
         <v>163</v>
       </c>
@@ -5382,8 +5920,12 @@
       <c r="V41" s="25" t="s">
         <v>164</v>
       </c>
+      <c r="W41" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>21</v>
+      </c>
     </row>
-    <row r="42" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J42" s="1" t="s">
         <v>183</v>
       </c>
@@ -5423,8 +5965,12 @@
       <c r="V42" s="25" t="s">
         <v>184</v>
       </c>
+      <c r="W42" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>20</v>
+      </c>
     </row>
-    <row r="43" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J43" s="1" t="s">
         <v>67</v>
       </c>
@@ -5464,8 +6010,12 @@
       <c r="V43" s="25" t="s">
         <v>68</v>
       </c>
+      <c r="W43" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>22</v>
+      </c>
     </row>
-    <row r="44" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J44" s="1" t="s">
         <v>77</v>
       </c>
@@ -5505,8 +6055,12 @@
       <c r="V44" s="25" t="s">
         <v>78</v>
       </c>
+      <c r="W44" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>22</v>
+      </c>
     </row>
-    <row r="45" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J45" s="1" t="s">
         <v>103</v>
       </c>
@@ -5546,8 +6100,12 @@
       <c r="V45" s="25" t="s">
         <v>104</v>
       </c>
+      <c r="W45" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>21</v>
+      </c>
     </row>
-    <row r="46" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J46" s="1" t="s">
         <v>118</v>
       </c>
@@ -5587,8 +6145,12 @@
       <c r="V46" s="25" t="s">
         <v>119</v>
       </c>
+      <c r="W46" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J47" s="1" t="s">
         <v>151</v>
       </c>
@@ -5628,8 +6190,12 @@
       <c r="V47" s="25" t="s">
         <v>152</v>
       </c>
+      <c r="W47" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>16</v>
+      </c>
     </row>
-    <row r="48" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J48" s="1" t="s">
         <v>153</v>
       </c>
@@ -5669,8 +6235,12 @@
       <c r="V48" s="25" t="s">
         <v>154</v>
       </c>
+      <c r="W48" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>15</v>
+      </c>
     </row>
-    <row r="49" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J49" s="1" t="s">
         <v>159</v>
       </c>
@@ -5710,8 +6280,12 @@
       <c r="V49" s="25" t="s">
         <v>160</v>
       </c>
+      <c r="W49" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>20</v>
+      </c>
     </row>
-    <row r="50" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J50" s="1" t="s">
         <v>99</v>
       </c>
@@ -5751,8 +6325,12 @@
       <c r="V50" s="25" t="s">
         <v>100</v>
       </c>
+      <c r="W50" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>13</v>
+      </c>
     </row>
-    <row r="51" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J51" s="1" t="s">
         <v>149</v>
       </c>
@@ -5792,8 +6370,12 @@
       <c r="V51" s="25" t="s">
         <v>150</v>
       </c>
+      <c r="W51" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>13</v>
+      </c>
     </row>
-    <row r="52" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J52" s="1" t="s">
         <v>62</v>
       </c>
@@ -5833,8 +6415,12 @@
       <c r="V52" s="25" t="s">
         <v>64</v>
       </c>
+      <c r="W52" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>15</v>
+      </c>
     </row>
-    <row r="53" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J53" s="1" t="s">
         <v>120</v>
       </c>
@@ -5874,8 +6460,12 @@
       <c r="V53" s="25" t="s">
         <v>121</v>
       </c>
+      <c r="W53" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>15</v>
+      </c>
     </row>
-    <row r="54" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J54" s="1" t="s">
         <v>155</v>
       </c>
@@ -5915,8 +6505,12 @@
       <c r="V54" s="25" t="s">
         <v>156</v>
       </c>
+      <c r="W54" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>15</v>
+      </c>
     </row>
-    <row r="55" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J55" s="1" t="s">
         <v>157</v>
       </c>
@@ -5956,8 +6550,12 @@
       <c r="V55" s="25" t="s">
         <v>158</v>
       </c>
+      <c r="W55" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>15</v>
+      </c>
     </row>
-    <row r="56" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J56" s="1" t="s">
         <v>177</v>
       </c>
@@ -5997,8 +6595,12 @@
       <c r="V56" s="25" t="s">
         <v>178</v>
       </c>
+      <c r="W56" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>15</v>
+      </c>
     </row>
-    <row r="57" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J57" s="1" t="s">
         <v>128</v>
       </c>
@@ -6038,8 +6640,12 @@
       <c r="V57" s="25" t="s">
         <v>129</v>
       </c>
+      <c r="W57" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>14</v>
+      </c>
     </row>
-    <row r="58" spans="10:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="10:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="J58" s="1" t="s">
         <v>125</v>
       </c>
@@ -6078,6 +6684,10 @@
       </c>
       <c r="V58" s="25" t="s">
         <v>126</v>
+      </c>
+      <c r="W58" s="55">
+        <f>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesos[Valor],tblPesos[Eficiencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesos[Valor],tblPesos[Capacidad]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesos[Valor],tblPesos[Resiliencia]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesos[Valor],tblPesos[Coste]),0)+IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesos[Valor],tblPesos[Exposición]),0)</f>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -6090,129 +6700,89 @@
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="J3:V3"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q5:Q58">
-    <cfRule type="expression" dxfId="34" priority="26">
-      <formula>$Q5="Bajo"</formula>
+  <conditionalFormatting sqref="P5:P58">
+    <cfRule type="expression" dxfId="28" priority="51">
+      <formula>$P5="Alto"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="52">
+      <formula>$P5="Medio-Alto"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="53">
+      <formula>$P5="Medio"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="54">
+      <formula>$P5="Medio-Bajo"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="55">
+      <formula>$P5="Bajo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q58">
-    <cfRule type="expression" dxfId="57" priority="27">
+    <cfRule type="expression" dxfId="23" priority="26">
+      <formula>$Q5="Bajo"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="27">
       <formula>$Q5="Medio-Bajo"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q58">
-    <cfRule type="expression" dxfId="33" priority="28">
+    <cfRule type="expression" dxfId="21" priority="28">
       <formula>$Q5="Medio"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q58">
-    <cfRule type="expression" dxfId="56" priority="29">
+    <cfRule type="expression" dxfId="20" priority="29">
       <formula>$Q5="Medio-Alto"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q58">
-    <cfRule type="expression" dxfId="55" priority="30">
+    <cfRule type="expression" dxfId="19" priority="30">
       <formula>$Q5="Alto"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R58">
-    <cfRule type="expression" dxfId="32" priority="36">
+    <cfRule type="expression" dxfId="18" priority="36">
       <formula>$R5="Bajo"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R58">
-    <cfRule type="expression" dxfId="54" priority="37">
+    <cfRule type="expression" dxfId="17" priority="37">
       <formula>$R5="Medio-Bajo"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R58">
-    <cfRule type="expression" dxfId="31" priority="38">
+    <cfRule type="expression" dxfId="16" priority="38">
       <formula>$R5="Medio"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R58">
-    <cfRule type="expression" dxfId="53" priority="39">
+    <cfRule type="expression" dxfId="15" priority="39">
       <formula>$R5="Medio-Alto"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R58">
-    <cfRule type="expression" dxfId="52" priority="40">
+    <cfRule type="expression" dxfId="14" priority="40">
       <formula>$R5="Alto"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S58">
-    <cfRule type="expression" dxfId="38" priority="41">
+    <cfRule type="expression" dxfId="13" priority="41">
       <formula>$S5="Alto"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S58">
-    <cfRule type="expression" dxfId="51" priority="42">
+    <cfRule type="expression" dxfId="12" priority="42">
       <formula>$S5="Medio-Alto"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S58">
-    <cfRule type="expression" dxfId="37" priority="43">
+    <cfRule type="expression" dxfId="11" priority="43">
       <formula>$S5="Medio"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S58">
-    <cfRule type="expression" dxfId="50" priority="44">
+    <cfRule type="expression" dxfId="10" priority="44">
       <formula>$S5="Medio-Bajo"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S58">
-    <cfRule type="expression" dxfId="49" priority="45">
+    <cfRule type="expression" dxfId="9" priority="45">
       <formula>$S5="Bajo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:T58">
-    <cfRule type="expression" dxfId="36" priority="46">
+    <cfRule type="expression" dxfId="8" priority="46">
       <formula>$T5="Alto"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T5:T58">
-    <cfRule type="expression" dxfId="48" priority="47">
+    <cfRule type="expression" dxfId="7" priority="47">
       <formula>$T5="Medio-Alto"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T5:T58">
-    <cfRule type="expression" dxfId="35" priority="48">
+    <cfRule type="expression" dxfId="6" priority="48">
       <formula>$T5="Medio"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T5:T58">
-    <cfRule type="expression" dxfId="47" priority="49">
+    <cfRule type="expression" dxfId="5" priority="49">
       <formula>$T5="Medio-Bajo"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T5:T58">
-    <cfRule type="expression" dxfId="46" priority="50">
+    <cfRule type="expression" dxfId="4" priority="50">
       <formula>$T5="Bajo"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P58">
-    <cfRule type="expression" dxfId="40" priority="51">
-      <formula>$P5="Alto"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P58">
-    <cfRule type="expression" dxfId="45" priority="52">
-      <formula>$P5="Medio-Alto"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P58">
-    <cfRule type="expression" dxfId="39" priority="53">
-      <formula>$P5="Medio"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P58">
-    <cfRule type="expression" dxfId="44" priority="54">
-      <formula>$P5="Medio-Bajo"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P58">
-    <cfRule type="expression" dxfId="43" priority="55">
-      <formula>$P5="Bajo"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -6257,7 +6827,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:W26"/>
+  <dimension ref="B2:AA26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -6266,10 +6836,12 @@
     <col min="4" max="4" width="6.7109375" style="4" customWidth="1"/>
     <col min="5" max="22" width="5.140625" style="4" customWidth="1"/>
     <col min="23" max="25" width="9.140625" style="4" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="4"/>
+    <col min="26" max="26" width="18.7109375" style="4" customWidth="1"/>
+    <col min="27" max="27" width="27.85546875" style="4" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" s="15" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:27" s="15" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="27" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[#All],2,FALSE)</f>
         <v>Coerción y cobros forzosos</v>
@@ -6347,8 +6919,10 @@
         <v>Destino operativo</v>
       </c>
       <c r="W2" s="26"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
     </row>
-    <row r="3" spans="2:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
         <v>189</v>
       </c>
@@ -6413,7 +6987,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Coerción y cobros forzosos</v>
@@ -6498,7 +7072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Contrabando / tráfico / comercio ilícito</v>
@@ -6583,7 +7157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Explotación de recursos naturales</v>
@@ -6668,7 +7242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Autofinanciación lícita / microfinanciación</v>
@@ -6753,7 +7327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Actividades económicas formales / negocios</v>
@@ -6838,7 +7412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Donaciones / crowdfunding / apoyo online</v>
@@ -6923,7 +7497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Efectivo</v>
@@ -7008,7 +7582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Hawala / HOSSP</v>
@@ -7093,7 +7667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>MVTS / remesas</v>
@@ -7178,7 +7752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Dinero móvil</v>
@@ -7263,7 +7837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Pagos online</v>
@@ -7348,7 +7922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Servicios bancarios</v>
@@ -7433,7 +8007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
         <v>Tarjetas prepago / e-wallets</v>
@@ -8029,52 +8603,52 @@
       </c>
     </row>
     <row r="25" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="47"/>
-      <c r="P25" s="47"/>
-      <c r="Q25" s="47"/>
-      <c r="R25" s="47"/>
-      <c r="S25" s="47"/>
-      <c r="T25" s="47"/>
-      <c r="U25" s="47"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="49"/>
+      <c r="K25" s="49"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="49"/>
+      <c r="O25" s="49"/>
+      <c r="P25" s="49"/>
+      <c r="Q25" s="49"/>
+      <c r="R25" s="49"/>
+      <c r="S25" s="49"/>
+      <c r="T25" s="49"/>
+      <c r="U25" s="49"/>
     </row>
     <row r="26" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="47"/>
-      <c r="P26" s="47"/>
-      <c r="Q26" s="47"/>
-      <c r="R26" s="47"/>
-      <c r="S26" s="47"/>
-      <c r="T26" s="47"/>
-      <c r="U26" s="47"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8082,10 +8656,10 @@
     <mergeCell ref="B25:U25"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:V22">
-    <cfRule type="cellIs" dxfId="42" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8094,4 +8668,1971 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{685469CB-FAED-44D8-93CE-1992743709F4}">
+  <dimension ref="B2:AD26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="4" customWidth="1"/>
+    <col min="5" max="22" width="5.140625" style="4" customWidth="1"/>
+    <col min="23" max="24" width="9.140625" style="4" customWidth="1"/>
+    <col min="25" max="25" width="15.28515625" style="4" customWidth="1"/>
+    <col min="26" max="26" width="11.5703125" style="4" customWidth="1"/>
+    <col min="27" max="27" width="9.140625" style="4"/>
+    <col min="28" max="28" width="10.7109375" style="4" customWidth="1"/>
+    <col min="29" max="29" width="10.42578125" style="4" customWidth="1"/>
+    <col min="30" max="30" width="11.28515625" style="4" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" style="4" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:30" s="15" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[O1]],tblNodos[#All],2,FALSE)</f>
+        <v>Coerción y cobros forzosos</v>
+      </c>
+      <c r="E2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[O2]],tblNodos[#All],2,FALSE)</f>
+        <v>Contrabando / tráfico / comercio ilícito</v>
+      </c>
+      <c r="F2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[O3]],tblNodos[#All],2,FALSE)</f>
+        <v>Explotación de recursos naturales</v>
+      </c>
+      <c r="G2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[O4]],tblNodos[#All],2,FALSE)</f>
+        <v>Autofinanciación lícita / microfinanciación</v>
+      </c>
+      <c r="H2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[O5]],tblNodos[#All],2,FALSE)</f>
+        <v>Actividades económicas formales / negocios</v>
+      </c>
+      <c r="I2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[O6]],tblNodos[#All],2,FALSE)</f>
+        <v>Donaciones / crowdfunding / apoyo online</v>
+      </c>
+      <c r="J2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[I1]],tblNodos[#All],2,FALSE)</f>
+        <v>Efectivo</v>
+      </c>
+      <c r="K2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[I2]],tblNodos[#All],2,FALSE)</f>
+        <v>Hawala / HOSSP</v>
+      </c>
+      <c r="L2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[I3]],tblNodos[#All],2,FALSE)</f>
+        <v>MVTS / remesas</v>
+      </c>
+      <c r="M2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[I4]],tblNodos[#All],2,FALSE)</f>
+        <v>Dinero móvil</v>
+      </c>
+      <c r="N2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[I5]],tblNodos[#All],2,FALSE)</f>
+        <v>Pagos online</v>
+      </c>
+      <c r="O2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[I6]],tblNodos[#All],2,FALSE)</f>
+        <v>Servicios bancarios</v>
+      </c>
+      <c r="P2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[I7]],tblNodos[#All],2,FALSE)</f>
+        <v>Tarjetas prepago / e-wallets</v>
+      </c>
+      <c r="Q2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[I8]],tblNodos[#All],2,FALSE)</f>
+        <v>Plataformas digitales</v>
+      </c>
+      <c r="R2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[I9]],tblNodos[#All],2,FALSE)</f>
+        <v>Activos virtuales</v>
+      </c>
+      <c r="S2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[G1]],tblNodos[#All],2,FALSE)</f>
+        <v>Tesorería central</v>
+      </c>
+      <c r="T2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[G2]],tblNodos[#All],2,FALSE)</f>
+        <v>Centro financiero regional / célula</v>
+      </c>
+      <c r="U2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[G3]],tblNodos[#All],2,FALSE)</f>
+        <v>Facilitador externo / entidad instrumental</v>
+      </c>
+      <c r="V2" s="27" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#Headers],[D]],tblNodos[#All],2,FALSE)</f>
+        <v>Destino operativo</v>
+      </c>
+      <c r="W2" s="26"/>
+    </row>
+    <row r="3" spans="2:30" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y3" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="53"/>
+      <c r="AB3" s="53"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="53"/>
+    </row>
+    <row r="4" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Coerción y cobros forzosos</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>23</v>
+      </c>
+      <c r="K4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>21</v>
+      </c>
+      <c r="L4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="M4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>18</v>
+      </c>
+      <c r="N4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>15</v>
+      </c>
+      <c r="S4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V4" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z4" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA4" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB4" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC4" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD4" s="50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Contrabando / tráfico / comercio ilícito</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>22</v>
+      </c>
+      <c r="K5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>22</v>
+      </c>
+      <c r="L5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="M5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z5" s="51">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="51">
+        <v>5</v>
+      </c>
+      <c r="AB5" s="51">
+        <v>5</v>
+      </c>
+      <c r="AC5" s="51">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Explotación de recursos naturales</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>22</v>
+      </c>
+      <c r="K6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>22</v>
+      </c>
+      <c r="L6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>18</v>
+      </c>
+      <c r="M6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z6" s="51">
+        <v>2</v>
+      </c>
+      <c r="AA6" s="51">
+        <v>4</v>
+      </c>
+      <c r="AB6" s="51">
+        <v>4</v>
+      </c>
+      <c r="AC6" s="51">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Autofinanciación lícita / microfinanciación</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>19</v>
+      </c>
+      <c r="N7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="O7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>15</v>
+      </c>
+      <c r="P7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>13</v>
+      </c>
+      <c r="Q7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z7" s="51">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="51">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="51">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="51">
+        <v>3</v>
+      </c>
+      <c r="AD7" s="51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Actividades económicas formales / negocios</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>21</v>
+      </c>
+      <c r="K8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="O8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="P8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z8" s="51">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="51">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="51">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="51">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Donaciones / crowdfunding / apoyo online</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="M9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="O9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>16</v>
+      </c>
+      <c r="R9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>15</v>
+      </c>
+      <c r="S9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U9" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z9" s="51">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="51">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="51">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="51">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Efectivo</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>21</v>
+      </c>
+      <c r="L10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>16</v>
+      </c>
+      <c r="N10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>14</v>
+      </c>
+      <c r="S10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Hawala / HOSSP</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>18</v>
+      </c>
+      <c r="T11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>22</v>
+      </c>
+      <c r="U11" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>MVTS / remesas</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>18</v>
+      </c>
+      <c r="U12" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="V12" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Dinero móvil</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>18</v>
+      </c>
+      <c r="U13" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Pagos online</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="U14" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>16</v>
+      </c>
+      <c r="V14" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Servicios bancarios</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="T15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U15" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="V15" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Tarjetas prepago / e-wallets</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>13</v>
+      </c>
+      <c r="U16" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V16" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Plataformas digitales</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>16</v>
+      </c>
+      <c r="U17" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>15</v>
+      </c>
+      <c r="V17" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Activos virtuales</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>15</v>
+      </c>
+      <c r="U18" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>15</v>
+      </c>
+      <c r="V18" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Tesorería central</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>20</v>
+      </c>
+      <c r="K19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>18</v>
+      </c>
+      <c r="P19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Centro financiero regional / célula</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>21</v>
+      </c>
+      <c r="K20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>21</v>
+      </c>
+      <c r="L20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="M20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>18</v>
+      </c>
+      <c r="N20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U20" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V20" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="15" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Facilitador externo / entidad instrumental</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>16</v>
+      </c>
+      <c r="O21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>17</v>
+      </c>
+      <c r="P21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>15</v>
+      </c>
+      <c r="S21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U21" s="56">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V21" s="57">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="16" t="str">
+        <f>VLOOKUP(tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[#All],2,FALSE)</f>
+        <v>Destino operativo</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[O6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"O6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I4]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I4",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I5]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I5",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I6]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I6",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I7]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I7",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I8]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I8",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[I9]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"I9",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G1]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G1",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G2]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G2",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U22" s="58">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[G3]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"G3",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V22" s="59">
+        <f>IF(tblMatrizDeAdyacencia[[#This Row],[D]]=1,SUMIFS(tblEnlaces[Peso],tblEnlaces[Nodo Origen],tblMatrizPonderada[[#This Row],[NodoOrigen \ NodoDestino]],tblEnlaces[Nodo Destino],"D",tblEnlaces[Activo],1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="48" t="s">
+        <v>191</v>
+      </c>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="49"/>
+      <c r="K25" s="49"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="49"/>
+      <c r="O25" s="49"/>
+      <c r="P25" s="49"/>
+      <c r="Q25" s="49"/>
+      <c r="R25" s="49"/>
+      <c r="S25" s="49"/>
+      <c r="T25" s="49"/>
+      <c r="U25" s="49"/>
+    </row>
+    <row r="26" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B25:U25"/>
+    <mergeCell ref="B26:U26"/>
+    <mergeCell ref="Y3:AD3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D4:V22">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Diseño Red FT.xlsx
+++ b/Diseño Red FT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00_repositorios_GitHub\TFG-AFT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E457293B-C227-4FE7-BBDA-D50133CB5D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8430DBD-BF70-40A7-83D1-E9ACB62C9250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base-Nodos" sheetId="10" r:id="rId1"/>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="211">
   <si>
     <t>GENERADOR DE MODELOS DE REDES SINTÉTICAS DE FINANCIACIÓN DEL TERRORISMO</t>
   </si>
@@ -791,6 +791,9 @@
   <si>
     <t>Matriz de Adyacencia</t>
   </si>
+  <si>
+    <t>Capa</t>
+  </si>
 </sst>
 </file>
 
@@ -1301,7 +1304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1514,11 +1517,37 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1527,32 +1556,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1560,32 +1569,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="246">
+  <dxfs count="247">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="0" tint="-0.1498458815271462"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1615,6 +1685,36 @@
           <color rgb="FFD9D9D9"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1646,6 +1746,36 @@
           <color rgb="FFD9D9D9"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1682,11 +1812,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -1697,8 +1823,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
@@ -1708,7 +1835,9 @@
         <top style="thin">
           <color rgb="FFD9D9D9"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1740,6 +1869,97 @@
           <color rgb="FFD9D9D9"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1777,6 +1997,41 @@
           <color rgb="FFD9D9D9"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1818,6 +2073,7 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1826,6 +2082,7 @@
         <color theme="1" tint="0.34998626667073579"/>
         <name val="Calibri"/>
         <family val="2"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -1834,8 +2091,33 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
@@ -1851,843 +2133,10 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1" tint="0.34998626667073579"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.1498764000366222"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.1498764000366222"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.1498764000366222"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.1498764000366222"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color theme="0" tint="-0.1498458815271462"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.1498764000366222"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.1498764000366222"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.1498764000366222"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FFD9D9D9"/>
         </bottom>
@@ -2720,6 +2169,30 @@
         <right style="thin">
           <color rgb="FFD9D9D9"/>
         </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
         <top style="thin">
           <color rgb="FFD9D9D9"/>
         </top>
@@ -2730,51 +2203,20 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1" tint="0.34998626667073579"/>
+        <sz val="11"/>
+        <color auto="1"/>
         <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
@@ -2790,10 +2232,510 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
         <bottom style="thin">
           <color rgb="FFD9D9D9"/>
         </bottom>
@@ -2826,30 +2768,6 @@
         <right style="thin">
           <color rgb="FFD9D9D9"/>
         </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
         <top style="thin">
           <color rgb="FFD9D9D9"/>
         </top>
@@ -2863,15 +2781,19 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
+        <sz val="8"/>
+        <color theme="1" tint="0.34998626667073579"/>
         <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
@@ -2889,21 +2811,14 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
@@ -2919,480 +2834,10 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FFD9D9D9"/>
         </bottom>
@@ -3425,74 +2870,6 @@
         <right style="thin">
           <color rgb="FFD9D9D9"/>
         </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
         <top/>
         <bottom/>
       </border>
@@ -4063,441 +3440,6 @@
         <bottom style="thin">
           <color rgb="FFD9D9D9"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -5991,6 +4933,537 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6615,376 +6088,23 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6997,28 +6117,912 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
         <right style="thin">
           <color rgb="FFD9D9D9"/>
         </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
         <top style="thin">
           <color rgb="FFD9D9D9"/>
         </top>
         <bottom style="thin">
           <color rgb="FFD9D9D9"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -7027,83 +7031,97 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
+        <sz val="8"/>
+        <color theme="1" tint="0.34998626667073579"/>
         <name val="Calibri"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
+        <b/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <name val="Calibri"/>
-        <family val="2"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -7165,83 +7183,80 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B2FB235A-71F0-400E-A6F0-508799095DA1}" name="tblTiposDeNodo" displayName="tblTiposDeNodo" ref="A4:C8" headerRowDxfId="214" dataDxfId="213" totalsRowDxfId="212">
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2D998733-2F4E-407E-BB96-65EE8D671F3E}" name="Sigla" dataDxfId="211"/>
-    <tableColumn id="2" xr3:uid="{1D05F6E9-EB6D-4FA6-9F98-305486BA8372}" name="Nombre" dataDxfId="210"/>
-    <tableColumn id="3" xr3:uid="{2A05B337-8674-440C-B5E6-EDF2D3E9C7EF}" name="Descripción1" dataDxfId="209"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B2FB235A-71F0-400E-A6F0-508799095DA1}" name="tblTiposDeNodo" displayName="tblTiposDeNodo" ref="A4:D8" headerRowDxfId="203" dataDxfId="202" totalsRowDxfId="201">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{2D998733-2F4E-407E-BB96-65EE8D671F3E}" name="Sigla" dataDxfId="200"/>
+    <tableColumn id="2" xr3:uid="{1D05F6E9-EB6D-4FA6-9F98-305486BA8372}" name="Nombre" dataDxfId="199"/>
+    <tableColumn id="3" xr3:uid="{2A05B337-8674-440C-B5E6-EDF2D3E9C7EF}" name="Descripción1" dataDxfId="198"/>
+    <tableColumn id="4" xr3:uid="{969BC7E1-EE89-4897-8C40-9A8A992E41A8}" name="Capa" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C3763AE3-0C07-44F8-B723-CD50D544B597}" name="tblMatrizPonderadaValorOperativo" displayName="tblMatrizPonderadaValorOperativo" ref="B3:V22" totalsRowShown="0" headerRowDxfId="125" dataDxfId="123" headerRowBorderDxfId="124" tableBorderDxfId="122" totalsRowBorderDxfId="121">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C3763AE3-0C07-44F8-B723-CD50D544B597}" name="tblMatrizPonderadaValorOperativo" displayName="tblMatrizPonderadaValorOperativo" ref="B3:V22" totalsRowShown="0" headerRowDxfId="246" dataDxfId="244" headerRowBorderDxfId="245" tableBorderDxfId="243" totalsRowBorderDxfId="242">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{AB0E4632-ED12-49C5-876A-D0C45597103C}" name="Nombre Nodo" dataDxfId="120">
+    <tableColumn id="21" xr3:uid="{AB0E4632-ED12-49C5-876A-D0C45597103C}" name="Nombre Nodo" dataDxfId="241">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{1F5E2E88-3C78-4615-A934-EA38CE88F1DA}" name="NodoOrigen \ NodoDestino" dataDxfId="119"/>
-    <tableColumn id="2" xr3:uid="{7A66295D-CA43-492F-8775-35115F7A44EA}" name="O1" dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{1F5E2E88-3C78-4615-A934-EA38CE88F1DA}" name="NodoOrigen \ NodoDestino" dataDxfId="240"/>
+    <tableColumn id="2" xr3:uid="{7A66295D-CA43-492F-8775-35115F7A44EA}" name="O1" dataDxfId="239">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!D4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B8A230F9-7293-4177-956A-4E8B8C3CDA07}" name="O2" dataDxfId="25">
+    <tableColumn id="3" xr3:uid="{B8A230F9-7293-4177-956A-4E8B8C3CDA07}" name="O2" dataDxfId="238">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!E4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],E$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{58464D2B-4CD6-441D-AB43-966A10F72197}" name="O3" dataDxfId="24">
+    <tableColumn id="4" xr3:uid="{58464D2B-4CD6-441D-AB43-966A10F72197}" name="O3" dataDxfId="237">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!F4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],F$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B54A5E25-CEE0-4DA6-8517-04ED3BBF73C6}" name="O4" dataDxfId="23">
+    <tableColumn id="5" xr3:uid="{B54A5E25-CEE0-4DA6-8517-04ED3BBF73C6}" name="O4" dataDxfId="236">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!G4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],G$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6A0BB34B-830D-4E04-B8C9-46624641D569}" name="O5" dataDxfId="22">
+    <tableColumn id="6" xr3:uid="{6A0BB34B-830D-4E04-B8C9-46624641D569}" name="O5" dataDxfId="235">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!H4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],H$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00DB80CE-0309-4FD9-950E-24D1DFDD9FFF}" name="O6" dataDxfId="21">
+    <tableColumn id="7" xr3:uid="{00DB80CE-0309-4FD9-950E-24D1DFDD9FFF}" name="O6" dataDxfId="234">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!I4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],I$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7AA5A8CA-1E8D-4093-864B-7D03F5756DC4}" name="C1" dataDxfId="29">
+    <tableColumn id="8" xr3:uid="{7AA5A8CA-1E8D-4093-864B-7D03F5756DC4}" name="C1" dataDxfId="233">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!J4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],J$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{03497B6C-E6A2-42BB-B97E-C56E12C9418F}" name="C2" dataDxfId="20">
+    <tableColumn id="9" xr3:uid="{03497B6C-E6A2-42BB-B97E-C56E12C9418F}" name="C2" dataDxfId="232">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!K4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],K$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{0FA96BFD-FC30-4C99-86C3-1B3F7728768B}" name="C3" dataDxfId="19">
+    <tableColumn id="10" xr3:uid="{0FA96BFD-FC30-4C99-86C3-1B3F7728768B}" name="C3" dataDxfId="231">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!L4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],L$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F3EDBB22-EAE5-496E-8608-9EED6CF8096A}" name="R1" dataDxfId="18">
+    <tableColumn id="11" xr3:uid="{F3EDBB22-EAE5-496E-8608-9EED6CF8096A}" name="R1" dataDxfId="230">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!M4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],M$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EE195140-EF30-4914-AEA7-9A979743FE44}" name="R2" dataDxfId="17">
+    <tableColumn id="12" xr3:uid="{EE195140-EF30-4914-AEA7-9A979743FE44}" name="R2" dataDxfId="229">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!N4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],N$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{940C992B-DC9E-4078-B43B-AD2A2ADF88AA}" name="R3" dataDxfId="16">
+    <tableColumn id="13" xr3:uid="{940C992B-DC9E-4078-B43B-AD2A2ADF88AA}" name="R3" dataDxfId="228">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!O4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],O$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{542FFF8E-DD7B-4C4C-9B1B-C885472540BA}" name="R4" dataDxfId="15">
+    <tableColumn id="14" xr3:uid="{542FFF8E-DD7B-4C4C-9B1B-C885472540BA}" name="R4" dataDxfId="227">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!P4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],P$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{054CF94A-1A1E-4D9F-8BA6-8813EF51323B}" name="R5" dataDxfId="14">
+    <tableColumn id="15" xr3:uid="{054CF94A-1A1E-4D9F-8BA6-8813EF51323B}" name="R5" dataDxfId="226">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!Q4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],Q$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{7ED93D8E-5836-4A3E-9935-FBC89CD3F932}" name="R6" dataDxfId="13">
+    <tableColumn id="16" xr3:uid="{7ED93D8E-5836-4A3E-9935-FBC89CD3F932}" name="R6" dataDxfId="225">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!R4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],R$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{164A5867-1655-4663-992A-899F25195899}" name="R7" dataDxfId="12">
+    <tableColumn id="17" xr3:uid="{164A5867-1655-4663-992A-899F25195899}" name="R7" dataDxfId="224">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!S4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],S$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{E33E9D43-CAE7-4043-AE20-D5AC6983C7DD}" name="R8" dataDxfId="11">
+    <tableColumn id="18" xr3:uid="{E33E9D43-CAE7-4043-AE20-D5AC6983C7DD}" name="R8" dataDxfId="223">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!T4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],T$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{5758BF82-052C-40CF-8505-1FBCD9CE2809}" name="R9" dataDxfId="10">
+    <tableColumn id="19" xr3:uid="{5758BF82-052C-40CF-8505-1FBCD9CE2809}" name="R9" dataDxfId="222">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!U4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],U$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{B734CB8C-660E-449E-8793-5B1787F00081}" name="D1" dataDxfId="9">
+    <tableColumn id="20" xr3:uid="{B734CB8C-660E-449E-8793-5B1787F00081}" name="D1" dataDxfId="221">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!V4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7250,94 +7265,94 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5D156EC0-C7DA-458D-93D7-E916A2987C0A}" name="tblPesosValorOperativo" displayName="tblPesosValorOperativo" ref="Y4:AC9" totalsRowShown="0" headerRowDxfId="118" dataDxfId="116" headerRowBorderDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5D156EC0-C7DA-458D-93D7-E916A2987C0A}" name="tblPesosValorOperativo" displayName="tblPesosValorOperativo" ref="Y4:AC9" totalsRowShown="0" headerRowDxfId="220" dataDxfId="218" headerRowBorderDxfId="219">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B21AD536-482D-4B9A-AB5E-37E015551681}" name="Valor" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{F200399A-6022-47BF-9665-7A71F541FDA5}" name="Eficiencia" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{FF663B4E-11C8-434F-A1B1-0562E8F7FB14}" name="Exposición" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{D5B0977C-E15F-4467-A561-675FCAB097AB}" name="Capacidad" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{A82F60D0-C02D-4214-9AB5-F7EDAD97FCF6}" name="Resiliencia" dataDxfId="111"/>
+    <tableColumn id="1" xr3:uid="{B21AD536-482D-4B9A-AB5E-37E015551681}" name="Valor" dataDxfId="217"/>
+    <tableColumn id="2" xr3:uid="{F200399A-6022-47BF-9665-7A71F541FDA5}" name="Eficiencia" dataDxfId="216"/>
+    <tableColumn id="3" xr3:uid="{FF663B4E-11C8-434F-A1B1-0562E8F7FB14}" name="Exposición" dataDxfId="215"/>
+    <tableColumn id="4" xr3:uid="{D5B0977C-E15F-4467-A561-675FCAB097AB}" name="Capacidad" dataDxfId="214"/>
+    <tableColumn id="5" xr3:uid="{A82F60D0-C02D-4214-9AB5-F7EDAD97FCF6}" name="Resiliencia" dataDxfId="213"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9318777C-0265-4E44-A0BA-CFC469B6C744}" name="tblRangoEnlace1ValorOpertivo" displayName="tblRangoEnlace1ValorOpertivo" ref="Y12:AD14" totalsRowShown="0" headerRowDxfId="110" dataDxfId="108" headerRowBorderDxfId="109">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9318777C-0265-4E44-A0BA-CFC469B6C744}" name="tblRangoEnlace1ValorOpertivo" displayName="tblRangoEnlace1ValorOpertivo" ref="Y12:AD14" totalsRowShown="0" headerRowDxfId="212" dataDxfId="210" headerRowBorderDxfId="211">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{753333F3-816E-431E-BB43-7A7927A7163F}" name="Rango del Enlace" dataDxfId="107"/>
-    <tableColumn id="2" xr3:uid="{72E9BB48-4FA1-4371-A282-0262F904FF9A}" name="Eficiencia" dataDxfId="106"/>
-    <tableColumn id="3" xr3:uid="{87F86AC7-35A2-437C-87BC-FB7CF221D935}" name="Exposición" dataDxfId="105"/>
-    <tableColumn id="4" xr3:uid="{3BA6459E-1C77-4D92-88F9-A4DA307EB1FF}" name="Capacidad" dataDxfId="104"/>
-    <tableColumn id="5" xr3:uid="{CED3CA81-A959-4820-A212-1AB6D2F76092}" name="Resiliencia" dataDxfId="103"/>
-    <tableColumn id="6" xr3:uid="{AFD0E7F4-AEB0-480B-BEDB-0D56FC9A258D}" name="Total" dataDxfId="102"/>
+    <tableColumn id="1" xr3:uid="{753333F3-816E-431E-BB43-7A7927A7163F}" name="Rango del Enlace" dataDxfId="209"/>
+    <tableColumn id="2" xr3:uid="{72E9BB48-4FA1-4371-A282-0262F904FF9A}" name="Eficiencia" dataDxfId="208"/>
+    <tableColumn id="3" xr3:uid="{87F86AC7-35A2-437C-87BC-FB7CF221D935}" name="Exposición" dataDxfId="207"/>
+    <tableColumn id="4" xr3:uid="{3BA6459E-1C77-4D92-88F9-A4DA307EB1FF}" name="Capacidad" dataDxfId="206"/>
+    <tableColumn id="5" xr3:uid="{CED3CA81-A959-4820-A212-1AB6D2F76092}" name="Resiliencia" dataDxfId="205"/>
+    <tableColumn id="6" xr3:uid="{AFD0E7F4-AEB0-480B-BEDB-0D56FC9A258D}" name="Total" dataDxfId="204"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DCB388D3-5907-4F27-B1F2-50F7C3CEFD03}" name="tblMatrizTradeOff" displayName="tblMatrizTradeOff" ref="B3:V22" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" totalsRowBorderDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DCB388D3-5907-4F27-B1F2-50F7C3CEFD03}" name="tblMatrizTradeOff" displayName="tblMatrizTradeOff" ref="B3:V22" totalsRowShown="0" headerRowDxfId="80" dataDxfId="78" headerRowBorderDxfId="79" tableBorderDxfId="77" totalsRowBorderDxfId="76">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{AA1E6080-4E20-4F11-BF7D-BCF3B7198FDD}" name="Nombre Nodo" dataDxfId="8">
+    <tableColumn id="21" xr3:uid="{AA1E6080-4E20-4F11-BF7D-BCF3B7198FDD}" name="Nombre Nodo" dataDxfId="75">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{894C4500-CF7B-4D11-8AA7-3C7C1BD512C6}" name="NodoOrigen \ NodoDestino" dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{9F705910-1DB5-40FC-A6DE-98805525ACF0}" name="O1" dataDxfId="95">
+    <tableColumn id="1" xr3:uid="{894C4500-CF7B-4D11-8AA7-3C7C1BD512C6}" name="NodoOrigen \ NodoDestino" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{9F705910-1DB5-40FC-A6DE-98805525ACF0}" name="O1" dataDxfId="73">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!D4=0,MatrizPonderadaValorOperativo!D4=0),0,MatrizPonderadaValorOperativo!D4/MatrizPonderadaCostes!D4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{50058AD6-7468-4AC7-97C5-05F954228EC1}" name="O2" dataDxfId="94">
+    <tableColumn id="3" xr3:uid="{50058AD6-7468-4AC7-97C5-05F954228EC1}" name="O2" dataDxfId="72">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!E4=0,MatrizPonderadaValorOperativo!E4=0),0,MatrizPonderadaValorOperativo!E4/MatrizPonderadaCostes!E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7C94D72A-7710-415D-86F3-659E59F93C96}" name="O3" dataDxfId="93">
+    <tableColumn id="4" xr3:uid="{7C94D72A-7710-415D-86F3-659E59F93C96}" name="O3" dataDxfId="71">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!F4=0,MatrizPonderadaValorOperativo!F4=0),0,MatrizPonderadaValorOperativo!F4/MatrizPonderadaCostes!F4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{532BA85E-D317-4F75-A439-3A5B03302C28}" name="O4" dataDxfId="92">
+    <tableColumn id="5" xr3:uid="{532BA85E-D317-4F75-A439-3A5B03302C28}" name="O4" dataDxfId="70">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!G4=0,MatrizPonderadaValorOperativo!G4=0),0,MatrizPonderadaValorOperativo!G4/MatrizPonderadaCostes!G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{063CA99D-B02A-474E-BF88-15CCC8190E67}" name="O5" dataDxfId="91">
+    <tableColumn id="6" xr3:uid="{063CA99D-B02A-474E-BF88-15CCC8190E67}" name="O5" dataDxfId="69">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!H4=0,MatrizPonderadaValorOperativo!H4=0),0,MatrizPonderadaValorOperativo!H4/MatrizPonderadaCostes!H4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{7BAB99D6-E0DD-44E8-812E-F31B042D5A8F}" name="O6" dataDxfId="90">
+    <tableColumn id="7" xr3:uid="{7BAB99D6-E0DD-44E8-812E-F31B042D5A8F}" name="O6" dataDxfId="68">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!I4=0,MatrizPonderadaValorOperativo!I4=0),0,MatrizPonderadaValorOperativo!I4/MatrizPonderadaCostes!I4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7A6532A5-C6A7-497A-9950-E4CF326FB1D0}" name="I1" dataDxfId="89">
+    <tableColumn id="8" xr3:uid="{7A6532A5-C6A7-497A-9950-E4CF326FB1D0}" name="I1" dataDxfId="67">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!J4=0,MatrizPonderadaValorOperativo!J4=0),0,MatrizPonderadaValorOperativo!J4/MatrizPonderadaCostes!J4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{7D782904-1F98-40F1-90DB-B287194DD5EC}" name="I2" dataDxfId="88">
+    <tableColumn id="9" xr3:uid="{7D782904-1F98-40F1-90DB-B287194DD5EC}" name="I2" dataDxfId="66">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!K4=0,MatrizPonderadaValorOperativo!K4=0),0,MatrizPonderadaValorOperativo!K4/MatrizPonderadaCostes!K4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F8DFA04B-3F58-4A4C-84F2-C08ECA18C8D0}" name="I3" dataDxfId="87">
+    <tableColumn id="10" xr3:uid="{F8DFA04B-3F58-4A4C-84F2-C08ECA18C8D0}" name="I3" dataDxfId="65">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!L4=0,MatrizPonderadaValorOperativo!L4=0),0,MatrizPonderadaValorOperativo!L4/MatrizPonderadaCostes!L4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{BEE1D8C4-0249-4AEB-85C7-3C1964171690}" name="I4" dataDxfId="86">
+    <tableColumn id="11" xr3:uid="{BEE1D8C4-0249-4AEB-85C7-3C1964171690}" name="I4" dataDxfId="64">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!M4=0,MatrizPonderadaValorOperativo!M4=0),0,MatrizPonderadaValorOperativo!M4/MatrizPonderadaCostes!M4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5E8D8652-5E54-4316-9F7E-FE077E7F3845}" name="I5" dataDxfId="85">
+    <tableColumn id="12" xr3:uid="{5E8D8652-5E54-4316-9F7E-FE077E7F3845}" name="I5" dataDxfId="63">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!N4=0,MatrizPonderadaValorOperativo!N4=0),0,MatrizPonderadaValorOperativo!N4/MatrizPonderadaCostes!N4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{19070E8B-9ED0-4B66-9707-071DEBF3C994}" name="I6" dataDxfId="84">
+    <tableColumn id="13" xr3:uid="{19070E8B-9ED0-4B66-9707-071DEBF3C994}" name="I6" dataDxfId="62">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!O4=0,MatrizPonderadaValorOperativo!O4=0),0,MatrizPonderadaValorOperativo!O4/MatrizPonderadaCostes!O4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{76F2DA9F-DAF7-439A-84BF-1733FA9657FD}" name="I7" dataDxfId="83">
+    <tableColumn id="14" xr3:uid="{76F2DA9F-DAF7-439A-84BF-1733FA9657FD}" name="I7" dataDxfId="61">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!P4=0,MatrizPonderadaValorOperativo!P4=0),0,MatrizPonderadaValorOperativo!P4/MatrizPonderadaCostes!P4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7D6FF674-D8C7-4CDC-B88A-E9A853759EB2}" name="I8" dataDxfId="82">
+    <tableColumn id="15" xr3:uid="{7D6FF674-D8C7-4CDC-B88A-E9A853759EB2}" name="I8" dataDxfId="60">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!Q4=0,MatrizPonderadaValorOperativo!Q4=0),0,MatrizPonderadaValorOperativo!Q4/MatrizPonderadaCostes!Q4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{4874BEF7-C26F-4D06-BE1E-88E85D5250AC}" name="I9" dataDxfId="81">
+    <tableColumn id="16" xr3:uid="{4874BEF7-C26F-4D06-BE1E-88E85D5250AC}" name="I9" dataDxfId="59">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!R4=0,MatrizPonderadaValorOperativo!R4=0),0,MatrizPonderadaValorOperativo!R4/MatrizPonderadaCostes!R4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{A372A997-A44F-44EB-AAED-77C0B6E13538}" name="G1" dataDxfId="80">
+    <tableColumn id="17" xr3:uid="{A372A997-A44F-44EB-AAED-77C0B6E13538}" name="G1" dataDxfId="58">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!S4=0,MatrizPonderadaValorOperativo!S4=0),0,MatrizPonderadaValorOperativo!S4/MatrizPonderadaCostes!S4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{0F8CF6FF-ABAA-4A01-AD38-A32A28F3744E}" name="G2" dataDxfId="79">
+    <tableColumn id="18" xr3:uid="{0F8CF6FF-ABAA-4A01-AD38-A32A28F3744E}" name="G2" dataDxfId="57">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!T4=0,MatrizPonderadaValorOperativo!T4=0),0,MatrizPonderadaValorOperativo!T4/MatrizPonderadaCostes!T4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{AB7C5AA0-D767-454C-BA7B-5A2B55F42FB8}" name="G3" dataDxfId="78">
+    <tableColumn id="19" xr3:uid="{AB7C5AA0-D767-454C-BA7B-5A2B55F42FB8}" name="G3" dataDxfId="56">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!U4=0,MatrizPonderadaValorOperativo!U4=0),0,MatrizPonderadaValorOperativo!U4/MatrizPonderadaCostes!U4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{23B65986-1386-4DD0-B9E1-CF1D12F9896F}" name="D" dataDxfId="77">
+    <tableColumn id="20" xr3:uid="{23B65986-1386-4DD0-B9E1-CF1D12F9896F}" name="D" dataDxfId="55">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!V4=0,MatrizPonderadaValorOperativo!V4=0),0,MatrizPonderadaValorOperativo!V4/MatrizPonderadaCostes!V4)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7346,67 +7361,67 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5873A7B6-81FB-4D79-A0FB-9D6FB64CE88D}" name="tblMatrizDistancias" displayName="tblMatrizDistancias" ref="X3:AR22" totalsRowShown="0" headerRowDxfId="76" dataDxfId="74" headerRowBorderDxfId="75" tableBorderDxfId="73" totalsRowBorderDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5873A7B6-81FB-4D79-A0FB-9D6FB64CE88D}" name="tblMatrizDistancias" displayName="tblMatrizDistancias" ref="X3:AR22" totalsRowShown="0" headerRowDxfId="54" dataDxfId="52" headerRowBorderDxfId="53" tableBorderDxfId="51" totalsRowBorderDxfId="50">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{1BAD8E49-23F7-4BE2-B973-AA604F8B446D}" name="Nombre Nodo" dataDxfId="7">
+    <tableColumn id="21" xr3:uid="{1BAD8E49-23F7-4BE2-B973-AA604F8B446D}" name="Nombre Nodo" dataDxfId="49">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{CCA43D7E-3A02-4B90-B8B1-A5C2C1770B89}" name="NodoOrigen \ NodoDestino" dataDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{258A9219-735F-4D5E-96CD-61C2192DE988}" name="O1" dataDxfId="70">
+    <tableColumn id="1" xr3:uid="{CCA43D7E-3A02-4B90-B8B1-A5C2C1770B89}" name="NodoOrigen \ NodoDestino" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{258A9219-735F-4D5E-96CD-61C2192DE988}" name="O1" dataDxfId="47">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O1",0,IF(tblMatrizTradeOff[[#This Row],[O1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A742D52A-B21E-494D-9BEC-A3E5CC2D1787}" name="O2" dataDxfId="69">
+    <tableColumn id="3" xr3:uid="{A742D52A-B21E-494D-9BEC-A3E5CC2D1787}" name="O2" dataDxfId="46">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O2",0,IF(tblMatrizTradeOff[[#This Row],[O2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E3462037-DD10-4D8C-B6A1-5ADBA379FEB1}" name="O3" dataDxfId="68">
+    <tableColumn id="4" xr3:uid="{E3462037-DD10-4D8C-B6A1-5ADBA379FEB1}" name="O3" dataDxfId="45">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O3",0,IF(tblMatrizTradeOff[[#This Row],[O3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E48B988C-DC5A-4772-9E34-F71B68D92DCB}" name="O4" dataDxfId="67">
+    <tableColumn id="5" xr3:uid="{E48B988C-DC5A-4772-9E34-F71B68D92DCB}" name="O4" dataDxfId="44">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O4",0,IF(tblMatrizTradeOff[[#This Row],[O4]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O4]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{43CEAEF6-D25A-41BD-B40B-81780EA42997}" name="O5" dataDxfId="66">
+    <tableColumn id="6" xr3:uid="{43CEAEF6-D25A-41BD-B40B-81780EA42997}" name="O5" dataDxfId="43">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O5",0,IF(tblMatrizTradeOff[[#This Row],[O5]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O5]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3924F7A5-FD83-43F2-A080-29822934E0BE}" name="O6" dataDxfId="65">
+    <tableColumn id="7" xr3:uid="{3924F7A5-FD83-43F2-A080-29822934E0BE}" name="O6" dataDxfId="42">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O6",0,IF(tblMatrizTradeOff[[#This Row],[O6]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O6]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7547ECC7-C391-409A-A35D-75672D9B0DFF}" name="I1" dataDxfId="64">
+    <tableColumn id="8" xr3:uid="{7547ECC7-C391-409A-A35D-75672D9B0DFF}" name="I1" dataDxfId="41">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I1",0,IF(tblMatrizTradeOff[[#This Row],[I1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{10E4BD07-2311-4179-8574-4C902D93606E}" name="I2" dataDxfId="63">
+    <tableColumn id="9" xr3:uid="{10E4BD07-2311-4179-8574-4C902D93606E}" name="I2" dataDxfId="40">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I2",0,IF(tblMatrizTradeOff[[#This Row],[I2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C7634E23-202A-42C0-8E82-749F13342982}" name="I3" dataDxfId="62">
+    <tableColumn id="10" xr3:uid="{C7634E23-202A-42C0-8E82-749F13342982}" name="I3" dataDxfId="39">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I3",0,IF(tblMatrizTradeOff[[#This Row],[I3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{80F89DAB-DC38-4E1B-8C6E-ABAE0670FA4C}" name="I4" dataDxfId="61">
+    <tableColumn id="11" xr3:uid="{80F89DAB-DC38-4E1B-8C6E-ABAE0670FA4C}" name="I4" dataDxfId="38">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I4",0,IF(tblMatrizTradeOff[[#This Row],[I4]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I4]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{1690E7CA-C688-4A77-B2E4-78675EA5F6AF}" name="I5" dataDxfId="60">
+    <tableColumn id="12" xr3:uid="{1690E7CA-C688-4A77-B2E4-78675EA5F6AF}" name="I5" dataDxfId="37">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I5",0,IF(tblMatrizTradeOff[[#This Row],[I5]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I5]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{3A1E36E4-69D3-406F-91FA-CE9683D234A1}" name="I6" dataDxfId="59">
+    <tableColumn id="13" xr3:uid="{3A1E36E4-69D3-406F-91FA-CE9683D234A1}" name="I6" dataDxfId="36">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I6",0,IF(tblMatrizTradeOff[[#This Row],[I6]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I6]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{37A3FAD7-64EF-4C10-A216-8F4121D763FE}" name="I7" dataDxfId="58">
+    <tableColumn id="14" xr3:uid="{37A3FAD7-64EF-4C10-A216-8F4121D763FE}" name="I7" dataDxfId="35">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I7",0,IF(tblMatrizTradeOff[[#This Row],[I7]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I7]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{C79CE9F5-E392-4C54-A368-4072A211349B}" name="I8" dataDxfId="57">
+    <tableColumn id="15" xr3:uid="{C79CE9F5-E392-4C54-A368-4072A211349B}" name="I8" dataDxfId="34">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I8",0,IF(tblMatrizTradeOff[[#This Row],[I8]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I8]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{AF9AF109-E8FC-499B-B541-D049A2CD781D}" name="I9" dataDxfId="56">
+    <tableColumn id="16" xr3:uid="{AF9AF109-E8FC-499B-B541-D049A2CD781D}" name="I9" dataDxfId="33">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I9",0,IF(tblMatrizTradeOff[[#This Row],[I9]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I9]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C49A9B94-D73C-40C2-9773-A0B40E4AAC62}" name="G1" dataDxfId="55">
+    <tableColumn id="17" xr3:uid="{C49A9B94-D73C-40C2-9773-A0B40E4AAC62}" name="G1" dataDxfId="32">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G1",0,IF(tblMatrizTradeOff[[#This Row],[G1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[G1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{37DF13C5-7088-4645-80B8-632B4668B1C6}" name="G2" dataDxfId="54">
+    <tableColumn id="18" xr3:uid="{37DF13C5-7088-4645-80B8-632B4668B1C6}" name="G2" dataDxfId="31">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G2",0,IF(tblMatrizTradeOff[[#This Row],[G2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[G2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{0C6F5759-0A04-44DB-ABD3-792D0DD2FD39}" name="G3" dataDxfId="53">
+    <tableColumn id="19" xr3:uid="{0C6F5759-0A04-44DB-ABD3-792D0DD2FD39}" name="G3" dataDxfId="30">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G3",0,IF(tblMatrizTradeOff[[#This Row],[G3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[G3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{08ECC6AD-B105-48DC-B6EF-5213E3FB7C76}" name="D" dataDxfId="52">
+    <tableColumn id="20" xr3:uid="{08ECC6AD-B105-48DC-B6EF-5213E3FB7C76}" name="D" dataDxfId="29">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="D",0,IF(tblMatrizTradeOff[[#This Row],[D]]=0,9999,1/tblMatrizTradeOff[[#This Row],[D]]))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7415,25 +7430,25 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7B2B6549-1979-4B25-A35A-52BA4A0A39EE}" name="tblGradoPonderado" displayName="tblGradoPonderado" ref="B3:H23" totalsRowCount="1" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7B2B6549-1979-4B25-A35A-52BA4A0A39EE}" name="tblGradoPonderado" displayName="tblGradoPonderado" ref="B3:H23" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <tableColumns count="7">
-    <tableColumn id="21" xr3:uid="{77F6B8A9-151C-415D-A901-35466078EF18}" name="Nombre Nodo" totalsRowLabel="Totales / Máximos / Mínimos" dataDxfId="46" totalsRowDxfId="6">
+    <tableColumn id="21" xr3:uid="{77F6B8A9-151C-415D-A901-35466078EF18}" name="Nombre Nodo" totalsRowLabel="Totales / Máximos / Mínimos" dataDxfId="23" totalsRowDxfId="22">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{253666FE-A069-4260-AC52-8AE7DE9B8F38}" name="Nodo" dataDxfId="45" totalsRowDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{AA42A750-6BE0-4870-A26E-410A2BC2C73B}" name="Grado Ponderado de Entrada" dataDxfId="44" totalsRowDxfId="4">
+    <tableColumn id="1" xr3:uid="{253666FE-A069-4260-AC52-8AE7DE9B8F38}" name="Nodo" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{AA42A750-6BE0-4870-A26E-410A2BC2C73B}" name="Grado Ponderado de Entrada" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.n,tblGradoPonderado[[#This Row],[Nodo]],_xlpm.col,_xlfn.XLOOKUP(_xlpm.n,tblMatrizTradeOff[#Headers],tblMatrizTradeOff[#Data]),SUM(_xlpm.col))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{378B0278-AE86-49A4-8668-271111E0777E}" name="Grado Ponderado de Salida" dataDxfId="43" totalsRowDxfId="3">
+    <tableColumn id="3" xr3:uid="{378B0278-AE86-49A4-8668-271111E0777E}" name="Grado Ponderado de Salida" dataDxfId="17" totalsRowDxfId="16">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.n,tblGradoPonderado[[#This Row],[Nodo]],_xlpm.row,_xlfn.XLOOKUP(_xlpm.n,tblMatrizTradeOff[NodoOrigen \ NodoDestino],tblMatrizTradeOff[[O1]:[D]]),SUM(_xlpm.row))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3C52036B-2CF5-484C-8203-C94636D157F9}" name="Grado Ponderado Total" totalsRowFunction="max" dataDxfId="42" totalsRowDxfId="2">
+    <tableColumn id="4" xr3:uid="{3C52036B-2CF5-484C-8203-C94636D157F9}" name="Grado Ponderado Total" totalsRowFunction="max" dataDxfId="15" totalsRowDxfId="14">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado de Entrada]]+tblGradoPonderado[[#This Row],[Grado Ponderado de Salida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FFBA1243-72FC-40D4-AE6E-AE5864D502FB}" name="Balance Neto" dataDxfId="41" totalsRowDxfId="1">
+    <tableColumn id="5" xr3:uid="{FFBA1243-72FC-40D4-AE6E-AE5864D502FB}" name="Balance Neto" dataDxfId="13" totalsRowDxfId="12">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado de Salida]]-tblGradoPonderado[[#This Row],[Grado Ponderado de Entrada]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{94B10867-99D5-439C-B33C-5612EB83F5A4}" name="Grado Normalizado" dataDxfId="40" totalsRowDxfId="0">
+    <tableColumn id="6" xr3:uid="{94B10867-99D5-439C-B33C-5612EB83F5A4}" name="Grado Normalizado" dataDxfId="11" totalsRowDxfId="10">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado Total]]/tblGradoPonderado[[#Totals],[Grado Ponderado Total]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7442,77 +7457,77 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{684D43B5-10F8-42CD-A78F-0A2D7790FEBB}" name="tblPropiedadesCanales" displayName="tblPropiedadesCanales" ref="B4:C9" totalsRowShown="0" headerRowDxfId="208" dataDxfId="206" headerRowBorderDxfId="207" tableBorderDxfId="205">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{684D43B5-10F8-42CD-A78F-0A2D7790FEBB}" name="tblPropiedadesCanales" displayName="tblPropiedadesCanales" ref="B4:C9" totalsRowShown="0" headerRowDxfId="197" dataDxfId="195" headerRowBorderDxfId="196" tableBorderDxfId="194">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AE28D037-8200-4290-B185-521BE4E5D98F}" name="Variable" dataDxfId="204"/>
-    <tableColumn id="2" xr3:uid="{6EBF46F3-2102-4B98-9EA7-E0EC740C287C}" name="Definición recomendada" dataDxfId="203"/>
+    <tableColumn id="1" xr3:uid="{AE28D037-8200-4290-B185-521BE4E5D98F}" name="Variable" dataDxfId="193"/>
+    <tableColumn id="2" xr3:uid="{6EBF46F3-2102-4B98-9EA7-E0EC740C287C}" name="Definición recomendada" dataDxfId="192"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{A4F8E1C4-8F10-4A16-A363-66F29C756757}" name="tblCanales" displayName="tblCanales" ref="E4:N13" totalsRowShown="0" headerRowDxfId="202" dataDxfId="200" headerRowBorderDxfId="201" tableBorderDxfId="199" totalsRowBorderDxfId="198">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{A4F8E1C4-8F10-4A16-A363-66F29C756757}" name="tblCanales" displayName="tblCanales" ref="E4:N13" totalsRowShown="0" headerRowDxfId="191" dataDxfId="189" headerRowBorderDxfId="190" tableBorderDxfId="188" totalsRowBorderDxfId="187">
   <tableColumns count="10">
-    <tableColumn id="2" xr3:uid="{EC47E1C1-969B-40D7-A166-5065044FE8EE}" name="Nombre" dataDxfId="197"/>
-    <tableColumn id="4" xr3:uid="{C51CDB64-59EA-4881-B723-18B95E872D00}" name="Descripción" dataDxfId="196"/>
-    <tableColumn id="3" xr3:uid="{1CBE7731-79F9-40FF-82B5-B5E44A771838}" name="Tipo" dataDxfId="195"/>
-    <tableColumn id="5" xr3:uid="{E8249A44-897D-4018-B0CA-C983252BCFC8}" name="Coste" dataDxfId="194"/>
-    <tableColumn id="6" xr3:uid="{CE3CC37C-5B67-40F0-93BA-BA26DF959A93}" name="Eficiencia" dataDxfId="193"/>
-    <tableColumn id="7" xr3:uid="{C41E7A4D-CE1C-4D71-B522-398A7272A699}" name="Exposición" dataDxfId="192"/>
-    <tableColumn id="8" xr3:uid="{7AB4DB4D-AE68-4160-A03A-FCDB4E7546E5}" name="Capacidad" dataDxfId="191"/>
-    <tableColumn id="9" xr3:uid="{1354059D-8430-454F-87FD-5887F9F6B688}" name="Resiliencia" dataDxfId="190"/>
-    <tableColumn id="10" xr3:uid="{BC196392-856A-4221-9F76-9E4E7BC1F726}" name="GAFI" dataDxfId="189"/>
-    <tableColumn id="11" xr3:uid="{1CE9226F-8F31-4975-BF4A-078BB1C41195}" name="MODELO" dataDxfId="188"/>
+    <tableColumn id="2" xr3:uid="{EC47E1C1-969B-40D7-A166-5065044FE8EE}" name="Nombre" dataDxfId="186"/>
+    <tableColumn id="4" xr3:uid="{C51CDB64-59EA-4881-B723-18B95E872D00}" name="Descripción" dataDxfId="185"/>
+    <tableColumn id="3" xr3:uid="{1CBE7731-79F9-40FF-82B5-B5E44A771838}" name="Tipo" dataDxfId="184"/>
+    <tableColumn id="5" xr3:uid="{E8249A44-897D-4018-B0CA-C983252BCFC8}" name="Coste" dataDxfId="183"/>
+    <tableColumn id="6" xr3:uid="{CE3CC37C-5B67-40F0-93BA-BA26DF959A93}" name="Eficiencia" dataDxfId="182"/>
+    <tableColumn id="7" xr3:uid="{C41E7A4D-CE1C-4D71-B522-398A7272A699}" name="Exposición" dataDxfId="181"/>
+    <tableColumn id="8" xr3:uid="{7AB4DB4D-AE68-4160-A03A-FCDB4E7546E5}" name="Capacidad" dataDxfId="180"/>
+    <tableColumn id="9" xr3:uid="{1354059D-8430-454F-87FD-5887F9F6B688}" name="Resiliencia" dataDxfId="179"/>
+    <tableColumn id="10" xr3:uid="{BC196392-856A-4221-9F76-9E4E7BC1F726}" name="GAFI" dataDxfId="178"/>
+    <tableColumn id="11" xr3:uid="{1CE9226F-8F31-4975-BF4A-078BB1C41195}" name="MODELO" dataDxfId="177"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="F4:W30" headerRowDxfId="245" dataDxfId="244" totalsRowDxfId="243">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="F4:W30" headerRowDxfId="176" dataDxfId="175" totalsRowDxfId="174">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F5:Q30">
     <sortCondition ref="F4:F30"/>
   </sortState>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="242"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="241"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="240"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="239"/>
-    <tableColumn id="21" xr3:uid="{9EA0CAA5-0A23-473B-943E-3CC802BE75BA}" name="Canal" dataDxfId="238"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="237"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="236"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="235">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="173"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="172"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="171"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="170"/>
+    <tableColumn id="21" xr3:uid="{9EA0CAA5-0A23-473B-943E-3CC802BE75BA}" name="Canal" dataDxfId="169"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="168"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="167"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="166">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="234">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="165">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],5,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="233">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="164">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],6,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="232">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="163">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],7,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="231">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="162">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],8,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{D5ECEEAB-319C-416C-A120-BD842AFC8541}" name="Coste (peso)" dataDxfId="230" totalsRowDxfId="229">
+    <tableColumn id="23" xr3:uid="{D5ECEEAB-319C-416C-A120-BD842AFC8541}" name="Coste (peso)" dataDxfId="161" totalsRowDxfId="160">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesosCoste[Valor],tblPesosCoste[Coste],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{38505D25-3830-4BBB-8DCF-E8583124C910}" name="Eficiencia (peso)" dataDxfId="228" totalsRowDxfId="227">
+    <tableColumn id="24" xr3:uid="{38505D25-3830-4BBB-8DCF-E8583124C910}" name="Eficiencia (peso)" dataDxfId="159" totalsRowDxfId="158">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Eficiencia],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{8E52D89B-D169-4F48-AD66-44B1E56CB633}" name="Exposición (peso)" dataDxfId="33" totalsRowDxfId="226">
+    <tableColumn id="25" xr3:uid="{8E52D89B-D169-4F48-AD66-44B1E56CB633}" name="Exposición (peso)" dataDxfId="157" totalsRowDxfId="156">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Exposición],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{1F2413A4-A4B8-4902-8061-3A60A70F9F2F}" name="Capacidad (peso)" dataDxfId="32" totalsRowDxfId="225">
+    <tableColumn id="26" xr3:uid="{1F2413A4-A4B8-4902-8061-3A60A70F9F2F}" name="Capacidad (peso)" dataDxfId="155" totalsRowDxfId="154">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Capacidad],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{67FAA096-3D2B-4E91-9E1F-AEE59F7A690B}" name="Resiliencia (peso)" dataDxfId="31" totalsRowDxfId="224">
+    <tableColumn id="27" xr3:uid="{67FAA096-3D2B-4E91-9E1F-AEE59F7A690B}" name="Resiliencia (peso)" dataDxfId="153" totalsRowDxfId="152">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Resiliencia],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{378FBC0C-D6D1-4CC5-A688-4AE8E0EEFF15}" name="Valor Operativo (peso)" dataDxfId="223" totalsRowDxfId="222">
+    <tableColumn id="28" xr3:uid="{378FBC0C-D6D1-4CC5-A688-4AE8E0EEFF15}" name="Valor Operativo (peso)" dataDxfId="151" totalsRowDxfId="150">
       <calculatedColumnFormula>tblEnlaces[[#This Row],[Eficiencia (peso)]]+tblEnlaces[[#This Row],[Resiliencia (peso)]]+tblEnlaces[[#This Row],[Capacidad (peso)]]+tblEnlaces[[#This Row],[Exposición (peso)]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7521,80 +7536,80 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}" name="tblNodos" displayName="tblNodos" ref="A4:D23" headerRowDxfId="221" dataDxfId="220" totalsRowDxfId="219">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}" name="tblNodos" displayName="tblNodos" ref="A4:D23" headerRowDxfId="149" dataDxfId="148" totalsRowDxfId="147">
   <autoFilter ref="A4:D23" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C216D4B9-76C9-4611-A97A-027837B07F56}" name="NodoID" dataDxfId="218"/>
-    <tableColumn id="2" xr3:uid="{425384C0-D0A9-4E9A-A93C-65C1B3B77DB1}" name="Nombre" dataDxfId="217"/>
-    <tableColumn id="3" xr3:uid="{434558A9-CDA8-4827-AF85-9621517F0875}" name="Tipo" dataDxfId="216"/>
-    <tableColumn id="4" xr3:uid="{B0504143-65F8-445A-9B1A-9CA91BFF8129}" name="Activo" dataDxfId="215"/>
+    <tableColumn id="1" xr3:uid="{C216D4B9-76C9-4611-A97A-027837B07F56}" name="NodoID" dataDxfId="146"/>
+    <tableColumn id="2" xr3:uid="{425384C0-D0A9-4E9A-A93C-65C1B3B77DB1}" name="Nombre" dataDxfId="145"/>
+    <tableColumn id="3" xr3:uid="{434558A9-CDA8-4827-AF85-9621517F0875}" name="Tipo" dataDxfId="144"/>
+    <tableColumn id="4" xr3:uid="{B0504143-65F8-445A-9B1A-9CA91BFF8129}" name="Activo" dataDxfId="143"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="187" dataDxfId="185" headerRowBorderDxfId="186" tableBorderDxfId="184" totalsRowBorderDxfId="183">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="142" dataDxfId="140" headerRowBorderDxfId="141" tableBorderDxfId="139" totalsRowBorderDxfId="138">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="182">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="137">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="181"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="180">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="136"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="135">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="179">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="134">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,E$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="178">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="133">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,F$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="177">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="132">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,G$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="176">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="131">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,H$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="175">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="130">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,I$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="C1" dataDxfId="174">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="C1" dataDxfId="129">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,J$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="C2" dataDxfId="173">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="C2" dataDxfId="128">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,K$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="C3" dataDxfId="172">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="C3" dataDxfId="127">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,L$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="R1" dataDxfId="171">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="R1" dataDxfId="126">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,M$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="R2" dataDxfId="170">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="R2" dataDxfId="125">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,N$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="R3" dataDxfId="169">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="R3" dataDxfId="124">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,O$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="R4" dataDxfId="168">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="R4" dataDxfId="123">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,P$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="R5" dataDxfId="167">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="R5" dataDxfId="122">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,Q$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="R6" dataDxfId="166">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="R6" dataDxfId="121">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,R$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="R7" dataDxfId="165">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="R7" dataDxfId="120">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,S$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="R8" dataDxfId="164">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="R8" dataDxfId="119">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,T$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="R9" dataDxfId="163">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="R9" dataDxfId="118">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,U$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D1" dataDxfId="162">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D1" dataDxfId="117">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,V$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7603,67 +7618,67 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{619F938E-46CC-49F1-9A1F-6017755965D1}" name="tblMatrizPonderadaCostes" displayName="tblMatrizPonderadaCostes" ref="B3:V22" totalsRowShown="0" headerRowDxfId="161" dataDxfId="159" headerRowBorderDxfId="160" tableBorderDxfId="158" totalsRowBorderDxfId="157">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{619F938E-46CC-49F1-9A1F-6017755965D1}" name="tblMatrizPonderadaCostes" displayName="tblMatrizPonderadaCostes" ref="B3:V22" totalsRowShown="0" headerRowDxfId="116" dataDxfId="114" headerRowBorderDxfId="115" tableBorderDxfId="113" totalsRowBorderDxfId="112">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{2A9AC9D7-CC14-4058-8CF2-7CDFEC15F78F}" name="Nombre Nodo" dataDxfId="156">
+    <tableColumn id="21" xr3:uid="{2A9AC9D7-CC14-4058-8CF2-7CDFEC15F78F}" name="Nombre Nodo" dataDxfId="111">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{3A911174-7F39-43D0-8D1B-0D1A251C78CF}" name="NodoOrigen \ NodoDestino" dataDxfId="155"/>
-    <tableColumn id="2" xr3:uid="{79E6108F-3B54-4663-83BD-0E9A6288B0A8}" name="O1" dataDxfId="154">
+    <tableColumn id="1" xr3:uid="{3A911174-7F39-43D0-8D1B-0D1A251C78CF}" name="NodoOrigen \ NodoDestino" dataDxfId="110"/>
+    <tableColumn id="2" xr3:uid="{79E6108F-3B54-4663-83BD-0E9A6288B0A8}" name="O1" dataDxfId="109">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!D4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{74BBA163-10F6-4D74-863C-C4517633500F}" name="O2" dataDxfId="153">
+    <tableColumn id="3" xr3:uid="{74BBA163-10F6-4D74-863C-C4517633500F}" name="O2" dataDxfId="108">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!E4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],E$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5D6ADA5C-E165-41EC-803D-18F7A270611C}" name="O3" dataDxfId="152">
+    <tableColumn id="4" xr3:uid="{5D6ADA5C-E165-41EC-803D-18F7A270611C}" name="O3" dataDxfId="107">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!F4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],F$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{035B34FA-1623-4B86-B0EE-0CC6694FFD7C}" name="O4" dataDxfId="151">
+    <tableColumn id="5" xr3:uid="{035B34FA-1623-4B86-B0EE-0CC6694FFD7C}" name="O4" dataDxfId="106">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!G4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],G$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{27739639-E082-4698-9A4C-15EDA8612A83}" name="O5" dataDxfId="150">
+    <tableColumn id="6" xr3:uid="{27739639-E082-4698-9A4C-15EDA8612A83}" name="O5" dataDxfId="105">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!H4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],H$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{ED768978-7E7B-49CD-A202-FE8EBE9E64E0}" name="O6" dataDxfId="149">
+    <tableColumn id="7" xr3:uid="{ED768978-7E7B-49CD-A202-FE8EBE9E64E0}" name="O6" dataDxfId="104">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!I4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],I$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{37684012-4DC0-48DA-8E67-185403ABB81C}" name="C1" dataDxfId="148">
+    <tableColumn id="8" xr3:uid="{37684012-4DC0-48DA-8E67-185403ABB81C}" name="C1" dataDxfId="103">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!J4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],J$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E3684910-7769-4AEF-8800-33DC2F8D7ABC}" name="C2" dataDxfId="147">
+    <tableColumn id="9" xr3:uid="{E3684910-7769-4AEF-8800-33DC2F8D7ABC}" name="C2" dataDxfId="102">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!K4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],K$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A095B3C4-5019-4082-93A5-E12BDE733061}" name="C3" dataDxfId="146">
+    <tableColumn id="10" xr3:uid="{A095B3C4-5019-4082-93A5-E12BDE733061}" name="C3" dataDxfId="101">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!L4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],L$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{C5072B89-856A-4694-9D8B-17C4DB67DFF8}" name="R1" dataDxfId="145">
+    <tableColumn id="11" xr3:uid="{C5072B89-856A-4694-9D8B-17C4DB67DFF8}" name="R1" dataDxfId="100">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!M4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],M$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{0BD76649-1EE0-46D9-8718-F9A6F67BE379}" name="R2" dataDxfId="144">
+    <tableColumn id="12" xr3:uid="{0BD76649-1EE0-46D9-8718-F9A6F67BE379}" name="R2" dataDxfId="99">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!N4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],N$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{263255E9-BE7D-4E45-A463-5AD358998CB9}" name="R3" dataDxfId="143">
+    <tableColumn id="13" xr3:uid="{263255E9-BE7D-4E45-A463-5AD358998CB9}" name="R3" dataDxfId="98">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!O4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],O$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{7AF510BB-CB1B-461F-8746-C7133DC25996}" name="R4" dataDxfId="142">
+    <tableColumn id="14" xr3:uid="{7AF510BB-CB1B-461F-8746-C7133DC25996}" name="R4" dataDxfId="97">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!P4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],P$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{42A7B19E-8A6C-4FA9-A2E9-2B83EC8917D4}" name="R5" dataDxfId="141">
+    <tableColumn id="15" xr3:uid="{42A7B19E-8A6C-4FA9-A2E9-2B83EC8917D4}" name="R5" dataDxfId="96">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!Q4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],Q$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C9AE28B0-4117-4A3D-8381-F7E9417F1616}" name="R6" dataDxfId="140">
+    <tableColumn id="16" xr3:uid="{C9AE28B0-4117-4A3D-8381-F7E9417F1616}" name="R6" dataDxfId="95">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!R4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],R$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{92A0B734-1347-429D-A2CB-8D857E4CD34E}" name="R7" dataDxfId="139">
+    <tableColumn id="17" xr3:uid="{92A0B734-1347-429D-A2CB-8D857E4CD34E}" name="R7" dataDxfId="94">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!S4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],S$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{667134D2-C221-4A4D-9FB1-909ACDC0DDB5}" name="R8" dataDxfId="138">
+    <tableColumn id="18" xr3:uid="{667134D2-C221-4A4D-9FB1-909ACDC0DDB5}" name="R8" dataDxfId="93">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!T4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],T$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{338C87EB-B9DD-49EE-9C5C-4BCE63EF4744}" name="R9" dataDxfId="137">
+    <tableColumn id="19" xr3:uid="{338C87EB-B9DD-49EE-9C5C-4BCE63EF4744}" name="R9" dataDxfId="92">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!U4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],U$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{6E3807F5-486A-4D01-9C7A-D8CBDABFB157}" name="D1" dataDxfId="136">
+    <tableColumn id="20" xr3:uid="{6E3807F5-486A-4D01-9C7A-D8CBDABFB157}" name="D1" dataDxfId="91">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!V4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7672,24 +7687,24 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}" name="tblPesosCoste" displayName="tblPesosCoste" ref="Y4:Z9" totalsRowShown="0" headerRowDxfId="135" dataDxfId="133" headerRowBorderDxfId="134" tableBorderDxfId="132">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}" name="tblPesosCoste" displayName="tblPesosCoste" ref="Y4:Z9" totalsRowShown="0" headerRowDxfId="90" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87">
   <autoFilter ref="Y4:Z9" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E1E6CBAC-71D7-49B4-97B4-D7CD1992E449}" name="Valor" dataDxfId="131"/>
-    <tableColumn id="4" xr3:uid="{5D97B706-55F4-46C7-B8B4-663F39805E8B}" name="Coste" dataDxfId="130"/>
+    <tableColumn id="1" xr3:uid="{E1E6CBAC-71D7-49B4-97B4-D7CD1992E449}" name="Valor" dataDxfId="86"/>
+    <tableColumn id="4" xr3:uid="{5D97B706-55F4-46C7-B8B4-663F39805E8B}" name="Coste" dataDxfId="85"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66EEA98C-81AE-44A3-B7B7-DDC02BD7FDF3}" name="tblRangoEnlace" displayName="tblRangoEnlace" ref="Y12:Z14" totalsRowShown="0" headerRowDxfId="129" headerRowBorderDxfId="128">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66EEA98C-81AE-44A3-B7B7-DDC02BD7FDF3}" name="tblRangoEnlace" displayName="tblRangoEnlace" ref="Y12:Z14" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{241E10B4-3B7B-4E19-92EA-AA4D53964641}" name="Rango del Enlace" dataDxfId="127"/>
-    <tableColumn id="2" xr3:uid="{20B4E6FB-3DB7-4113-AD20-5780FA4D1775}" name="Coste" dataDxfId="126"/>
+    <tableColumn id="1" xr3:uid="{241E10B4-3B7B-4E19-92EA-AA4D53964641}" name="Rango del Enlace" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{20B4E6FB-3DB7-4113-AD20-5780FA4D1775}" name="Coste" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -7983,7 +7998,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="16" customWidth="1"/>
@@ -7992,22 +8007,23 @@
     <col min="4" max="16384" width="11.42578125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-    </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
+    <row r="1" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+    </row>
+    <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-    </row>
-    <row r="4" spans="1:3" s="17" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+    </row>
+    <row r="4" spans="1:4" s="17" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>124</v>
       </c>
@@ -8017,8 +8033,11 @@
       <c r="C4" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -8028,8 +8047,11 @@
       <c r="C5" s="55" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>117</v>
       </c>
@@ -8039,8 +8061,11 @@
       <c r="C6" s="55" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>120</v>
       </c>
@@ -8050,8 +8075,11 @@
       <c r="C7" s="55" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>37</v>
       </c>
@@ -8061,23 +8089,26 @@
       <c r="C8" s="55" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:3" ht="64.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:3" ht="64.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:3" ht="64.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="D8" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="64.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="64.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="64.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" ht="64.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:D3"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -8131,23 +8162,23 @@
     </row>
     <row r="2" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="78" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="82"/>
+      <c r="C3" s="78"/>
       <c r="D3" s="70"/>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="83" t="s">
         <v>182</v>
       </c>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
       <c r="O3" s="17"/>
     </row>
     <row r="4" spans="2:15" s="17" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -8599,34 +8630,34 @@
       <c r="L37" s="25"/>
     </row>
     <row r="38" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="83" t="s">
+      <c r="B38" s="79" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="78"/>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="78"/>
-      <c r="H38" s="78"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="78"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="78"/>
+      <c r="C38" s="80"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="80"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="80"/>
     </row>
     <row r="39" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="84" t="s">
+      <c r="B39" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="85"/>
-      <c r="D39" s="85"/>
-      <c r="E39" s="85"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="85"/>
-      <c r="H39" s="85"/>
-      <c r="I39" s="85"/>
-      <c r="J39" s="85"/>
-      <c r="K39" s="85"/>
-      <c r="L39" s="85"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
+      <c r="K39" s="82"/>
+      <c r="L39" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8674,55 +8705,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="77" t="s">
+      <c r="A1" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
     </row>
     <row r="3" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="F3" s="75" t="s">
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="F3" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="W3" s="76"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="84"/>
+      <c r="V3" s="84"/>
+      <c r="W3" s="84"/>
     </row>
     <row r="4" spans="1:24" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -10840,10 +10871,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:27" s="14" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="75" t="s">
         <v>209</v>
       </c>
-      <c r="C2" s="89"/>
+      <c r="C2" s="76"/>
       <c r="D2" s="24" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -12605,52 +12636,52 @@
       </c>
     </row>
     <row r="25" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="86" t="s">
+      <c r="B25" s="88" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="87"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="K25" s="87"/>
-      <c r="L25" s="87"/>
-      <c r="M25" s="87"/>
-      <c r="N25" s="87"/>
-      <c r="O25" s="87"/>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="89"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="89"/>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="89"/>
+      <c r="N25" s="89"/>
+      <c r="O25" s="89"/>
+      <c r="P25" s="89"/>
+      <c r="Q25" s="89"/>
+      <c r="R25" s="89"/>
+      <c r="S25" s="89"/>
+      <c r="T25" s="89"/>
+      <c r="U25" s="89"/>
     </row>
     <row r="26" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="86" t="s">
+      <c r="B26" s="88" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="87"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="87"/>
-      <c r="N26" s="87"/>
-      <c r="O26" s="87"/>
-      <c r="P26" s="87"/>
-      <c r="Q26" s="87"/>
-      <c r="R26" s="87"/>
-      <c r="S26" s="87"/>
-      <c r="T26" s="87"/>
-      <c r="U26" s="87"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="89"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="89"/>
+      <c r="K26" s="89"/>
+      <c r="L26" s="89"/>
+      <c r="M26" s="89"/>
+      <c r="N26" s="89"/>
+      <c r="O26" s="89"/>
+      <c r="P26" s="89"/>
+      <c r="Q26" s="89"/>
+      <c r="R26" s="89"/>
+      <c r="S26" s="89"/>
+      <c r="T26" s="89"/>
+      <c r="U26" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -12659,10 +12690,10 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:V22">
-    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12691,10 +12722,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:27" s="14" customFormat="1" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="89"/>
+      <c r="C2" s="76"/>
       <c r="D2" s="24" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -12837,10 +12868,10 @@
       <c r="V3" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="Y3" s="91" t="s">
+      <c r="Y3" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="Z3" s="92"/>
+      <c r="Z3" s="74"/>
     </row>
     <row r="4" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="str">
@@ -14537,7 +14568,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14573,10 +14604,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" s="14" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="89"/>
+      <c r="C2" s="76"/>
       <c r="D2" s="24" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -14730,13 +14761,13 @@
       <c r="V3" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="Y3" s="91" t="s">
+      <c r="Y3" s="73" t="s">
         <v>86</v>
       </c>
-      <c r="Z3" s="92"/>
-      <c r="AA3" s="92"/>
-      <c r="AB3" s="92"/>
-      <c r="AC3" s="92"/>
+      <c r="Z3" s="74"/>
+      <c r="AA3" s="74"/>
+      <c r="AB3" s="74"/>
+      <c r="AC3" s="74"/>
       <c r="AD3" s="40"/>
       <c r="AF3"/>
       <c r="AG3"/>
@@ -16742,6 +16773,11 @@
     <mergeCell ref="Y3:AC3"/>
     <mergeCell ref="B2:C2"/>
   </mergeCells>
+  <conditionalFormatting sqref="D4:I4 L4:V4 D5:V22">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D5:V22 D4:I4 L4:V4">
     <cfRule type="colorScale" priority="5">
       <colorScale>
@@ -16752,9 +16788,6 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
       </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
-      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:K4">
@@ -16768,7 +16801,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16801,10 +16834,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:44" s="14" customFormat="1" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="75" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="89"/>
+      <c r="C2" s="76"/>
       <c r="D2" s="24" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -16882,10 +16915,10 @@
         <v>Destino operativo final</v>
       </c>
       <c r="W2"/>
-      <c r="X2" s="88" t="s">
+      <c r="X2" s="75" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="89"/>
+      <c r="Y2" s="76"/>
       <c r="Z2" s="24" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -27974,7 +28007,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="66" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27987,7 +28020,7 @@
         <color rgb="FFFCFCFF"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>9999</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28017,15 +28050,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" s="14" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="89"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="76"/>
       <c r="I2" s="24"/>
       <c r="J2" s="24"/>
       <c r="K2" s="24"/>
@@ -28996,7 +29029,7 @@
       <c r="Z22"/>
     </row>
     <row r="23" spans="2:42" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="72" t="s">
         <v>108</v>
       </c>
       <c r="C23" s="50"/>
@@ -36645,7 +36678,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="64" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Diseño Red FT.xlsx
+++ b/Diseño Red FT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00_repositorios_GitHub\TFG-AFT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8430DBD-BF70-40A7-83D1-E9ACB62C9250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC822DF8-58CC-4A9E-893D-E2D6F658506E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1520,19 +1520,13 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1556,9 +1550,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1569,46 +1560,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="247">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <color theme="0" tint="-0.1498764000366222"/>
@@ -1658,6 +1632,46 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -3426,6 +3440,1043 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
@@ -6086,1043 +7137,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1" tint="0.34998626667073579"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -7184,79 +7198,79 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B2FB235A-71F0-400E-A6F0-508799095DA1}" name="tblTiposDeNodo" displayName="tblTiposDeNodo" ref="A4:D8" headerRowDxfId="203" dataDxfId="202" totalsRowDxfId="201">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B2FB235A-71F0-400E-A6F0-508799095DA1}" name="tblTiposDeNodo" displayName="tblTiposDeNodo" ref="A4:D8" headerRowDxfId="246" dataDxfId="245" totalsRowDxfId="244">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2D998733-2F4E-407E-BB96-65EE8D671F3E}" name="Sigla" dataDxfId="200"/>
-    <tableColumn id="2" xr3:uid="{1D05F6E9-EB6D-4FA6-9F98-305486BA8372}" name="Nombre" dataDxfId="199"/>
-    <tableColumn id="3" xr3:uid="{2A05B337-8674-440C-B5E6-EDF2D3E9C7EF}" name="Descripción1" dataDxfId="198"/>
-    <tableColumn id="4" xr3:uid="{969BC7E1-EE89-4897-8C40-9A8A992E41A8}" name="Capa" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{2D998733-2F4E-407E-BB96-65EE8D671F3E}" name="Sigla" dataDxfId="243"/>
+    <tableColumn id="2" xr3:uid="{1D05F6E9-EB6D-4FA6-9F98-305486BA8372}" name="Nombre" dataDxfId="242"/>
+    <tableColumn id="4" xr3:uid="{969BC7E1-EE89-4897-8C40-9A8A992E41A8}" name="Capa" dataDxfId="8" totalsRowDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{2A05B337-8674-440C-B5E6-EDF2D3E9C7EF}" name="Descripción1" dataDxfId="241"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C3763AE3-0C07-44F8-B723-CD50D544B597}" name="tblMatrizPonderadaValorOperativo" displayName="tblMatrizPonderadaValorOperativo" ref="B3:V22" totalsRowShown="0" headerRowDxfId="246" dataDxfId="244" headerRowBorderDxfId="245" tableBorderDxfId="243" totalsRowBorderDxfId="242">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C3763AE3-0C07-44F8-B723-CD50D544B597}" name="tblMatrizPonderadaValorOperativo" displayName="tblMatrizPonderadaValorOperativo" ref="B3:V22" totalsRowShown="0" headerRowDxfId="123" dataDxfId="121" headerRowBorderDxfId="122" tableBorderDxfId="120" totalsRowBorderDxfId="119">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{AB0E4632-ED12-49C5-876A-D0C45597103C}" name="Nombre Nodo" dataDxfId="241">
+    <tableColumn id="21" xr3:uid="{AB0E4632-ED12-49C5-876A-D0C45597103C}" name="Nombre Nodo" dataDxfId="118">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{1F5E2E88-3C78-4615-A934-EA38CE88F1DA}" name="NodoOrigen \ NodoDestino" dataDxfId="240"/>
-    <tableColumn id="2" xr3:uid="{7A66295D-CA43-492F-8775-35115F7A44EA}" name="O1" dataDxfId="239">
+    <tableColumn id="1" xr3:uid="{1F5E2E88-3C78-4615-A934-EA38CE88F1DA}" name="NodoOrigen \ NodoDestino" dataDxfId="117"/>
+    <tableColumn id="2" xr3:uid="{7A66295D-CA43-492F-8775-35115F7A44EA}" name="O1" dataDxfId="116">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!D4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B8A230F9-7293-4177-956A-4E8B8C3CDA07}" name="O2" dataDxfId="238">
+    <tableColumn id="3" xr3:uid="{B8A230F9-7293-4177-956A-4E8B8C3CDA07}" name="O2" dataDxfId="115">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!E4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],E$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{58464D2B-4CD6-441D-AB43-966A10F72197}" name="O3" dataDxfId="237">
+    <tableColumn id="4" xr3:uid="{58464D2B-4CD6-441D-AB43-966A10F72197}" name="O3" dataDxfId="114">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!F4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],F$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B54A5E25-CEE0-4DA6-8517-04ED3BBF73C6}" name="O4" dataDxfId="236">
+    <tableColumn id="5" xr3:uid="{B54A5E25-CEE0-4DA6-8517-04ED3BBF73C6}" name="O4" dataDxfId="113">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!G4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],G$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6A0BB34B-830D-4E04-B8C9-46624641D569}" name="O5" dataDxfId="235">
+    <tableColumn id="6" xr3:uid="{6A0BB34B-830D-4E04-B8C9-46624641D569}" name="O5" dataDxfId="112">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!H4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],H$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00DB80CE-0309-4FD9-950E-24D1DFDD9FFF}" name="O6" dataDxfId="234">
+    <tableColumn id="7" xr3:uid="{00DB80CE-0309-4FD9-950E-24D1DFDD9FFF}" name="O6" dataDxfId="111">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!I4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],I$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7AA5A8CA-1E8D-4093-864B-7D03F5756DC4}" name="C1" dataDxfId="233">
+    <tableColumn id="8" xr3:uid="{7AA5A8CA-1E8D-4093-864B-7D03F5756DC4}" name="C1" dataDxfId="110">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!J4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],J$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{03497B6C-E6A2-42BB-B97E-C56E12C9418F}" name="C2" dataDxfId="232">
+    <tableColumn id="9" xr3:uid="{03497B6C-E6A2-42BB-B97E-C56E12C9418F}" name="C2" dataDxfId="109">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!K4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],K$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{0FA96BFD-FC30-4C99-86C3-1B3F7728768B}" name="C3" dataDxfId="231">
+    <tableColumn id="10" xr3:uid="{0FA96BFD-FC30-4C99-86C3-1B3F7728768B}" name="C3" dataDxfId="108">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!L4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],L$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F3EDBB22-EAE5-496E-8608-9EED6CF8096A}" name="R1" dataDxfId="230">
+    <tableColumn id="11" xr3:uid="{F3EDBB22-EAE5-496E-8608-9EED6CF8096A}" name="R1" dataDxfId="107">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!M4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],M$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EE195140-EF30-4914-AEA7-9A979743FE44}" name="R2" dataDxfId="229">
+    <tableColumn id="12" xr3:uid="{EE195140-EF30-4914-AEA7-9A979743FE44}" name="R2" dataDxfId="106">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!N4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],N$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{940C992B-DC9E-4078-B43B-AD2A2ADF88AA}" name="R3" dataDxfId="228">
+    <tableColumn id="13" xr3:uid="{940C992B-DC9E-4078-B43B-AD2A2ADF88AA}" name="R3" dataDxfId="105">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!O4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],O$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{542FFF8E-DD7B-4C4C-9B1B-C885472540BA}" name="R4" dataDxfId="227">
+    <tableColumn id="14" xr3:uid="{542FFF8E-DD7B-4C4C-9B1B-C885472540BA}" name="R4" dataDxfId="104">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!P4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],P$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{054CF94A-1A1E-4D9F-8BA6-8813EF51323B}" name="R5" dataDxfId="226">
+    <tableColumn id="15" xr3:uid="{054CF94A-1A1E-4D9F-8BA6-8813EF51323B}" name="R5" dataDxfId="103">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!Q4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],Q$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{7ED93D8E-5836-4A3E-9935-FBC89CD3F932}" name="R6" dataDxfId="225">
+    <tableColumn id="16" xr3:uid="{7ED93D8E-5836-4A3E-9935-FBC89CD3F932}" name="R6" dataDxfId="102">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!R4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],R$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{164A5867-1655-4663-992A-899F25195899}" name="R7" dataDxfId="224">
+    <tableColumn id="17" xr3:uid="{164A5867-1655-4663-992A-899F25195899}" name="R7" dataDxfId="101">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!S4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],S$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{E33E9D43-CAE7-4043-AE20-D5AC6983C7DD}" name="R8" dataDxfId="223">
+    <tableColumn id="18" xr3:uid="{E33E9D43-CAE7-4043-AE20-D5AC6983C7DD}" name="R8" dataDxfId="100">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!T4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],T$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{5758BF82-052C-40CF-8505-1FBCD9CE2809}" name="R9" dataDxfId="222">
+    <tableColumn id="19" xr3:uid="{5758BF82-052C-40CF-8505-1FBCD9CE2809}" name="R9" dataDxfId="99">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!U4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],U$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{B734CB8C-660E-449E-8793-5B1787F00081}" name="D1" dataDxfId="221">
+    <tableColumn id="20" xr3:uid="{B734CB8C-660E-449E-8793-5B1787F00081}" name="D1" dataDxfId="98">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!V4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7265,27 +7279,27 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5D156EC0-C7DA-458D-93D7-E916A2987C0A}" name="tblPesosValorOperativo" displayName="tblPesosValorOperativo" ref="Y4:AC9" totalsRowShown="0" headerRowDxfId="220" dataDxfId="218" headerRowBorderDxfId="219">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5D156EC0-C7DA-458D-93D7-E916A2987C0A}" name="tblPesosValorOperativo" displayName="tblPesosValorOperativo" ref="Y4:AC9" totalsRowShown="0" headerRowDxfId="97" dataDxfId="95" headerRowBorderDxfId="96">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B21AD536-482D-4B9A-AB5E-37E015551681}" name="Valor" dataDxfId="217"/>
-    <tableColumn id="2" xr3:uid="{F200399A-6022-47BF-9665-7A71F541FDA5}" name="Eficiencia" dataDxfId="216"/>
-    <tableColumn id="3" xr3:uid="{FF663B4E-11C8-434F-A1B1-0562E8F7FB14}" name="Exposición" dataDxfId="215"/>
-    <tableColumn id="4" xr3:uid="{D5B0977C-E15F-4467-A561-675FCAB097AB}" name="Capacidad" dataDxfId="214"/>
-    <tableColumn id="5" xr3:uid="{A82F60D0-C02D-4214-9AB5-F7EDAD97FCF6}" name="Resiliencia" dataDxfId="213"/>
+    <tableColumn id="1" xr3:uid="{B21AD536-482D-4B9A-AB5E-37E015551681}" name="Valor" dataDxfId="94"/>
+    <tableColumn id="2" xr3:uid="{F200399A-6022-47BF-9665-7A71F541FDA5}" name="Eficiencia" dataDxfId="93"/>
+    <tableColumn id="3" xr3:uid="{FF663B4E-11C8-434F-A1B1-0562E8F7FB14}" name="Exposición" dataDxfId="92"/>
+    <tableColumn id="4" xr3:uid="{D5B0977C-E15F-4467-A561-675FCAB097AB}" name="Capacidad" dataDxfId="91"/>
+    <tableColumn id="5" xr3:uid="{A82F60D0-C02D-4214-9AB5-F7EDAD97FCF6}" name="Resiliencia" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9318777C-0265-4E44-A0BA-CFC469B6C744}" name="tblRangoEnlace1ValorOpertivo" displayName="tblRangoEnlace1ValorOpertivo" ref="Y12:AD14" totalsRowShown="0" headerRowDxfId="212" dataDxfId="210" headerRowBorderDxfId="211">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9318777C-0265-4E44-A0BA-CFC469B6C744}" name="tblRangoEnlace1ValorOpertivo" displayName="tblRangoEnlace1ValorOpertivo" ref="Y12:AD14" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{753333F3-816E-431E-BB43-7A7927A7163F}" name="Rango del Enlace" dataDxfId="209"/>
-    <tableColumn id="2" xr3:uid="{72E9BB48-4FA1-4371-A282-0262F904FF9A}" name="Eficiencia" dataDxfId="208"/>
-    <tableColumn id="3" xr3:uid="{87F86AC7-35A2-437C-87BC-FB7CF221D935}" name="Exposición" dataDxfId="207"/>
-    <tableColumn id="4" xr3:uid="{3BA6459E-1C77-4D92-88F9-A4DA307EB1FF}" name="Capacidad" dataDxfId="206"/>
-    <tableColumn id="5" xr3:uid="{CED3CA81-A959-4820-A212-1AB6D2F76092}" name="Resiliencia" dataDxfId="205"/>
-    <tableColumn id="6" xr3:uid="{AFD0E7F4-AEB0-480B-BEDB-0D56FC9A258D}" name="Total" dataDxfId="204"/>
+    <tableColumn id="1" xr3:uid="{753333F3-816E-431E-BB43-7A7927A7163F}" name="Rango del Enlace" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{72E9BB48-4FA1-4371-A282-0262F904FF9A}" name="Eficiencia" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{87F86AC7-35A2-437C-87BC-FB7CF221D935}" name="Exposición" dataDxfId="84"/>
+    <tableColumn id="4" xr3:uid="{3BA6459E-1C77-4D92-88F9-A4DA307EB1FF}" name="Capacidad" dataDxfId="83"/>
+    <tableColumn id="5" xr3:uid="{CED3CA81-A959-4820-A212-1AB6D2F76092}" name="Resiliencia" dataDxfId="82"/>
+    <tableColumn id="6" xr3:uid="{AFD0E7F4-AEB0-480B-BEDB-0D56FC9A258D}" name="Total" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7457,77 +7471,77 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{684D43B5-10F8-42CD-A78F-0A2D7790FEBB}" name="tblPropiedadesCanales" displayName="tblPropiedadesCanales" ref="B4:C9" totalsRowShown="0" headerRowDxfId="197" dataDxfId="195" headerRowBorderDxfId="196" tableBorderDxfId="194">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{684D43B5-10F8-42CD-A78F-0A2D7790FEBB}" name="tblPropiedadesCanales" displayName="tblPropiedadesCanales" ref="B4:C9" totalsRowShown="0" headerRowDxfId="240" dataDxfId="238" headerRowBorderDxfId="239" tableBorderDxfId="237">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AE28D037-8200-4290-B185-521BE4E5D98F}" name="Variable" dataDxfId="193"/>
-    <tableColumn id="2" xr3:uid="{6EBF46F3-2102-4B98-9EA7-E0EC740C287C}" name="Definición recomendada" dataDxfId="192"/>
+    <tableColumn id="1" xr3:uid="{AE28D037-8200-4290-B185-521BE4E5D98F}" name="Variable" dataDxfId="236"/>
+    <tableColumn id="2" xr3:uid="{6EBF46F3-2102-4B98-9EA7-E0EC740C287C}" name="Definición recomendada" dataDxfId="235"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{A4F8E1C4-8F10-4A16-A363-66F29C756757}" name="tblCanales" displayName="tblCanales" ref="E4:N13" totalsRowShown="0" headerRowDxfId="191" dataDxfId="189" headerRowBorderDxfId="190" tableBorderDxfId="188" totalsRowBorderDxfId="187">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{A4F8E1C4-8F10-4A16-A363-66F29C756757}" name="tblCanales" displayName="tblCanales" ref="E4:N13" totalsRowShown="0" headerRowDxfId="234" dataDxfId="232" headerRowBorderDxfId="233" tableBorderDxfId="231" totalsRowBorderDxfId="230">
   <tableColumns count="10">
-    <tableColumn id="2" xr3:uid="{EC47E1C1-969B-40D7-A166-5065044FE8EE}" name="Nombre" dataDxfId="186"/>
-    <tableColumn id="4" xr3:uid="{C51CDB64-59EA-4881-B723-18B95E872D00}" name="Descripción" dataDxfId="185"/>
-    <tableColumn id="3" xr3:uid="{1CBE7731-79F9-40FF-82B5-B5E44A771838}" name="Tipo" dataDxfId="184"/>
-    <tableColumn id="5" xr3:uid="{E8249A44-897D-4018-B0CA-C983252BCFC8}" name="Coste" dataDxfId="183"/>
-    <tableColumn id="6" xr3:uid="{CE3CC37C-5B67-40F0-93BA-BA26DF959A93}" name="Eficiencia" dataDxfId="182"/>
-    <tableColumn id="7" xr3:uid="{C41E7A4D-CE1C-4D71-B522-398A7272A699}" name="Exposición" dataDxfId="181"/>
-    <tableColumn id="8" xr3:uid="{7AB4DB4D-AE68-4160-A03A-FCDB4E7546E5}" name="Capacidad" dataDxfId="180"/>
-    <tableColumn id="9" xr3:uid="{1354059D-8430-454F-87FD-5887F9F6B688}" name="Resiliencia" dataDxfId="179"/>
-    <tableColumn id="10" xr3:uid="{BC196392-856A-4221-9F76-9E4E7BC1F726}" name="GAFI" dataDxfId="178"/>
-    <tableColumn id="11" xr3:uid="{1CE9226F-8F31-4975-BF4A-078BB1C41195}" name="MODELO" dataDxfId="177"/>
+    <tableColumn id="2" xr3:uid="{EC47E1C1-969B-40D7-A166-5065044FE8EE}" name="Nombre" dataDxfId="229"/>
+    <tableColumn id="4" xr3:uid="{C51CDB64-59EA-4881-B723-18B95E872D00}" name="Descripción" dataDxfId="228"/>
+    <tableColumn id="3" xr3:uid="{1CBE7731-79F9-40FF-82B5-B5E44A771838}" name="Tipo" dataDxfId="227"/>
+    <tableColumn id="5" xr3:uid="{E8249A44-897D-4018-B0CA-C983252BCFC8}" name="Coste" dataDxfId="226"/>
+    <tableColumn id="6" xr3:uid="{CE3CC37C-5B67-40F0-93BA-BA26DF959A93}" name="Eficiencia" dataDxfId="225"/>
+    <tableColumn id="7" xr3:uid="{C41E7A4D-CE1C-4D71-B522-398A7272A699}" name="Exposición" dataDxfId="224"/>
+    <tableColumn id="8" xr3:uid="{7AB4DB4D-AE68-4160-A03A-FCDB4E7546E5}" name="Capacidad" dataDxfId="223"/>
+    <tableColumn id="9" xr3:uid="{1354059D-8430-454F-87FD-5887F9F6B688}" name="Resiliencia" dataDxfId="222"/>
+    <tableColumn id="10" xr3:uid="{BC196392-856A-4221-9F76-9E4E7BC1F726}" name="GAFI" dataDxfId="221"/>
+    <tableColumn id="11" xr3:uid="{1CE9226F-8F31-4975-BF4A-078BB1C41195}" name="MODELO" dataDxfId="220"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="F4:W30" headerRowDxfId="176" dataDxfId="175" totalsRowDxfId="174">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="F4:W30" headerRowDxfId="219" dataDxfId="218" totalsRowDxfId="217">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F5:Q30">
     <sortCondition ref="F4:F30"/>
   </sortState>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="173"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="172"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="171"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="170"/>
-    <tableColumn id="21" xr3:uid="{9EA0CAA5-0A23-473B-943E-3CC802BE75BA}" name="Canal" dataDxfId="169"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="168"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="167"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="166">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="216"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="215"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="214"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="213"/>
+    <tableColumn id="21" xr3:uid="{9EA0CAA5-0A23-473B-943E-3CC802BE75BA}" name="Canal" dataDxfId="212"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="211"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="210"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="209">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="165">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="208">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],5,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="164">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="207">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],6,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="163">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="206">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],7,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="162">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="205">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],8,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{D5ECEEAB-319C-416C-A120-BD842AFC8541}" name="Coste (peso)" dataDxfId="161" totalsRowDxfId="160">
+    <tableColumn id="23" xr3:uid="{D5ECEEAB-319C-416C-A120-BD842AFC8541}" name="Coste (peso)" dataDxfId="204" totalsRowDxfId="203">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesosCoste[Valor],tblPesosCoste[Coste],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{38505D25-3830-4BBB-8DCF-E8583124C910}" name="Eficiencia (peso)" dataDxfId="159" totalsRowDxfId="158">
+    <tableColumn id="24" xr3:uid="{38505D25-3830-4BBB-8DCF-E8583124C910}" name="Eficiencia (peso)" dataDxfId="202" totalsRowDxfId="201">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Eficiencia],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{8E52D89B-D169-4F48-AD66-44B1E56CB633}" name="Exposición (peso)" dataDxfId="157" totalsRowDxfId="156">
+    <tableColumn id="25" xr3:uid="{8E52D89B-D169-4F48-AD66-44B1E56CB633}" name="Exposición (peso)" dataDxfId="200" totalsRowDxfId="199">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Exposición],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{1F2413A4-A4B8-4902-8061-3A60A70F9F2F}" name="Capacidad (peso)" dataDxfId="155" totalsRowDxfId="154">
+    <tableColumn id="26" xr3:uid="{1F2413A4-A4B8-4902-8061-3A60A70F9F2F}" name="Capacidad (peso)" dataDxfId="198" totalsRowDxfId="197">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Capacidad],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{67FAA096-3D2B-4E91-9E1F-AEE59F7A690B}" name="Resiliencia (peso)" dataDxfId="153" totalsRowDxfId="152">
+    <tableColumn id="27" xr3:uid="{67FAA096-3D2B-4E91-9E1F-AEE59F7A690B}" name="Resiliencia (peso)" dataDxfId="196" totalsRowDxfId="195">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Resiliencia],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{378FBC0C-D6D1-4CC5-A688-4AE8E0EEFF15}" name="Valor Operativo (peso)" dataDxfId="151" totalsRowDxfId="150">
+    <tableColumn id="28" xr3:uid="{378FBC0C-D6D1-4CC5-A688-4AE8E0EEFF15}" name="Valor Operativo (peso)" dataDxfId="194" totalsRowDxfId="193">
       <calculatedColumnFormula>tblEnlaces[[#This Row],[Eficiencia (peso)]]+tblEnlaces[[#This Row],[Resiliencia (peso)]]+tblEnlaces[[#This Row],[Capacidad (peso)]]+tblEnlaces[[#This Row],[Exposición (peso)]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7536,80 +7550,80 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}" name="tblNodos" displayName="tblNodos" ref="A4:D23" headerRowDxfId="149" dataDxfId="148" totalsRowDxfId="147">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}" name="tblNodos" displayName="tblNodos" ref="A4:D23" headerRowDxfId="192" dataDxfId="191" totalsRowDxfId="190">
   <autoFilter ref="A4:D23" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C216D4B9-76C9-4611-A97A-027837B07F56}" name="NodoID" dataDxfId="146"/>
-    <tableColumn id="2" xr3:uid="{425384C0-D0A9-4E9A-A93C-65C1B3B77DB1}" name="Nombre" dataDxfId="145"/>
-    <tableColumn id="3" xr3:uid="{434558A9-CDA8-4827-AF85-9621517F0875}" name="Tipo" dataDxfId="144"/>
-    <tableColumn id="4" xr3:uid="{B0504143-65F8-445A-9B1A-9CA91BFF8129}" name="Activo" dataDxfId="143"/>
+    <tableColumn id="1" xr3:uid="{C216D4B9-76C9-4611-A97A-027837B07F56}" name="NodoID" dataDxfId="189"/>
+    <tableColumn id="2" xr3:uid="{425384C0-D0A9-4E9A-A93C-65C1B3B77DB1}" name="Nombre" dataDxfId="188"/>
+    <tableColumn id="3" xr3:uid="{434558A9-CDA8-4827-AF85-9621517F0875}" name="Tipo" dataDxfId="187"/>
+    <tableColumn id="4" xr3:uid="{B0504143-65F8-445A-9B1A-9CA91BFF8129}" name="Activo" dataDxfId="186"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="142" dataDxfId="140" headerRowBorderDxfId="141" tableBorderDxfId="139" totalsRowBorderDxfId="138">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="185" dataDxfId="183" headerRowBorderDxfId="184" tableBorderDxfId="182" totalsRowBorderDxfId="181">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="137">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="180">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="136"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="135">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="179"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="178">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="134">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="177">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,E$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="133">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="176">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,F$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="132">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="175">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,G$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="131">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="174">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,H$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="130">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="173">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,I$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="C1" dataDxfId="129">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="C1" dataDxfId="172">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,J$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="C2" dataDxfId="128">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="C2" dataDxfId="171">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,K$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="C3" dataDxfId="127">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="C3" dataDxfId="170">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,L$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="R1" dataDxfId="126">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="R1" dataDxfId="169">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,M$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="R2" dataDxfId="125">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="R2" dataDxfId="168">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,N$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="R3" dataDxfId="124">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="R3" dataDxfId="167">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,O$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="R4" dataDxfId="123">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="R4" dataDxfId="166">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,P$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="R5" dataDxfId="122">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="R5" dataDxfId="165">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,Q$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="R6" dataDxfId="121">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="R6" dataDxfId="164">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,R$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="R7" dataDxfId="120">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="R7" dataDxfId="163">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,S$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="R8" dataDxfId="119">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="R8" dataDxfId="162">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,T$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="R9" dataDxfId="118">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="R9" dataDxfId="161">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,U$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D1" dataDxfId="117">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D1" dataDxfId="160">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,V$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7618,67 +7632,67 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{619F938E-46CC-49F1-9A1F-6017755965D1}" name="tblMatrizPonderadaCostes" displayName="tblMatrizPonderadaCostes" ref="B3:V22" totalsRowShown="0" headerRowDxfId="116" dataDxfId="114" headerRowBorderDxfId="115" tableBorderDxfId="113" totalsRowBorderDxfId="112">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{619F938E-46CC-49F1-9A1F-6017755965D1}" name="tblMatrizPonderadaCostes" displayName="tblMatrizPonderadaCostes" ref="B3:V22" totalsRowShown="0" headerRowDxfId="159" dataDxfId="157" headerRowBorderDxfId="158" tableBorderDxfId="156" totalsRowBorderDxfId="155">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{2A9AC9D7-CC14-4058-8CF2-7CDFEC15F78F}" name="Nombre Nodo" dataDxfId="111">
+    <tableColumn id="21" xr3:uid="{2A9AC9D7-CC14-4058-8CF2-7CDFEC15F78F}" name="Nombre Nodo" dataDxfId="154">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{3A911174-7F39-43D0-8D1B-0D1A251C78CF}" name="NodoOrigen \ NodoDestino" dataDxfId="110"/>
-    <tableColumn id="2" xr3:uid="{79E6108F-3B54-4663-83BD-0E9A6288B0A8}" name="O1" dataDxfId="109">
+    <tableColumn id="1" xr3:uid="{3A911174-7F39-43D0-8D1B-0D1A251C78CF}" name="NodoOrigen \ NodoDestino" dataDxfId="153"/>
+    <tableColumn id="2" xr3:uid="{79E6108F-3B54-4663-83BD-0E9A6288B0A8}" name="O1" dataDxfId="152">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!D4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{74BBA163-10F6-4D74-863C-C4517633500F}" name="O2" dataDxfId="108">
+    <tableColumn id="3" xr3:uid="{74BBA163-10F6-4D74-863C-C4517633500F}" name="O2" dataDxfId="151">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!E4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],E$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5D6ADA5C-E165-41EC-803D-18F7A270611C}" name="O3" dataDxfId="107">
+    <tableColumn id="4" xr3:uid="{5D6ADA5C-E165-41EC-803D-18F7A270611C}" name="O3" dataDxfId="150">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!F4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],F$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{035B34FA-1623-4B86-B0EE-0CC6694FFD7C}" name="O4" dataDxfId="106">
+    <tableColumn id="5" xr3:uid="{035B34FA-1623-4B86-B0EE-0CC6694FFD7C}" name="O4" dataDxfId="149">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!G4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],G$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{27739639-E082-4698-9A4C-15EDA8612A83}" name="O5" dataDxfId="105">
+    <tableColumn id="6" xr3:uid="{27739639-E082-4698-9A4C-15EDA8612A83}" name="O5" dataDxfId="148">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!H4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],H$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{ED768978-7E7B-49CD-A202-FE8EBE9E64E0}" name="O6" dataDxfId="104">
+    <tableColumn id="7" xr3:uid="{ED768978-7E7B-49CD-A202-FE8EBE9E64E0}" name="O6" dataDxfId="147">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!I4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],I$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{37684012-4DC0-48DA-8E67-185403ABB81C}" name="C1" dataDxfId="103">
+    <tableColumn id="8" xr3:uid="{37684012-4DC0-48DA-8E67-185403ABB81C}" name="C1" dataDxfId="146">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!J4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],J$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E3684910-7769-4AEF-8800-33DC2F8D7ABC}" name="C2" dataDxfId="102">
+    <tableColumn id="9" xr3:uid="{E3684910-7769-4AEF-8800-33DC2F8D7ABC}" name="C2" dataDxfId="145">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!K4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],K$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A095B3C4-5019-4082-93A5-E12BDE733061}" name="C3" dataDxfId="101">
+    <tableColumn id="10" xr3:uid="{A095B3C4-5019-4082-93A5-E12BDE733061}" name="C3" dataDxfId="144">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!L4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],L$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{C5072B89-856A-4694-9D8B-17C4DB67DFF8}" name="R1" dataDxfId="100">
+    <tableColumn id="11" xr3:uid="{C5072B89-856A-4694-9D8B-17C4DB67DFF8}" name="R1" dataDxfId="143">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!M4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],M$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{0BD76649-1EE0-46D9-8718-F9A6F67BE379}" name="R2" dataDxfId="99">
+    <tableColumn id="12" xr3:uid="{0BD76649-1EE0-46D9-8718-F9A6F67BE379}" name="R2" dataDxfId="142">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!N4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],N$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{263255E9-BE7D-4E45-A463-5AD358998CB9}" name="R3" dataDxfId="98">
+    <tableColumn id="13" xr3:uid="{263255E9-BE7D-4E45-A463-5AD358998CB9}" name="R3" dataDxfId="141">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!O4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],O$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{7AF510BB-CB1B-461F-8746-C7133DC25996}" name="R4" dataDxfId="97">
+    <tableColumn id="14" xr3:uid="{7AF510BB-CB1B-461F-8746-C7133DC25996}" name="R4" dataDxfId="140">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!P4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],P$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{42A7B19E-8A6C-4FA9-A2E9-2B83EC8917D4}" name="R5" dataDxfId="96">
+    <tableColumn id="15" xr3:uid="{42A7B19E-8A6C-4FA9-A2E9-2B83EC8917D4}" name="R5" dataDxfId="139">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!Q4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],Q$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C9AE28B0-4117-4A3D-8381-F7E9417F1616}" name="R6" dataDxfId="95">
+    <tableColumn id="16" xr3:uid="{C9AE28B0-4117-4A3D-8381-F7E9417F1616}" name="R6" dataDxfId="138">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!R4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],R$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{92A0B734-1347-429D-A2CB-8D857E4CD34E}" name="R7" dataDxfId="94">
+    <tableColumn id="17" xr3:uid="{92A0B734-1347-429D-A2CB-8D857E4CD34E}" name="R7" dataDxfId="137">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!S4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],S$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{667134D2-C221-4A4D-9FB1-909ACDC0DDB5}" name="R8" dataDxfId="93">
+    <tableColumn id="18" xr3:uid="{667134D2-C221-4A4D-9FB1-909ACDC0DDB5}" name="R8" dataDxfId="136">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!T4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],T$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{338C87EB-B9DD-49EE-9C5C-4BCE63EF4744}" name="R9" dataDxfId="92">
+    <tableColumn id="19" xr3:uid="{338C87EB-B9DD-49EE-9C5C-4BCE63EF4744}" name="R9" dataDxfId="135">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!U4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],U$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{6E3807F5-486A-4D01-9C7A-D8CBDABFB157}" name="D1" dataDxfId="91">
+    <tableColumn id="20" xr3:uid="{6E3807F5-486A-4D01-9C7A-D8CBDABFB157}" name="D1" dataDxfId="134">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!V4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7687,24 +7701,24 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}" name="tblPesosCoste" displayName="tblPesosCoste" ref="Y4:Z9" totalsRowShown="0" headerRowDxfId="90" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}" name="tblPesosCoste" displayName="tblPesosCoste" ref="Y4:Z9" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130">
   <autoFilter ref="Y4:Z9" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E1E6CBAC-71D7-49B4-97B4-D7CD1992E449}" name="Valor" dataDxfId="86"/>
-    <tableColumn id="4" xr3:uid="{5D97B706-55F4-46C7-B8B4-663F39805E8B}" name="Coste" dataDxfId="85"/>
+    <tableColumn id="1" xr3:uid="{E1E6CBAC-71D7-49B4-97B4-D7CD1992E449}" name="Valor" dataDxfId="129"/>
+    <tableColumn id="4" xr3:uid="{5D97B706-55F4-46C7-B8B4-663F39805E8B}" name="Coste" dataDxfId="128"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66EEA98C-81AE-44A3-B7B7-DDC02BD7FDF3}" name="tblRangoEnlace" displayName="tblRangoEnlace" ref="Y12:Z14" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66EEA98C-81AE-44A3-B7B7-DDC02BD7FDF3}" name="tblRangoEnlace" displayName="tblRangoEnlace" ref="Y12:Z14" totalsRowShown="0" headerRowDxfId="127" headerRowBorderDxfId="126">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{241E10B4-3B7B-4E19-92EA-AA4D53964641}" name="Rango del Enlace" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{20B4E6FB-3DB7-4113-AD20-5780FA4D1775}" name="Coste" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{241E10B4-3B7B-4E19-92EA-AA4D53964641}" name="Rango del Enlace" dataDxfId="125"/>
+    <tableColumn id="2" xr3:uid="{20B4E6FB-3DB7-4113-AD20-5780FA4D1775}" name="Coste" dataDxfId="124"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -8003,25 +8017,26 @@
   <cols>
     <col min="1" max="1" width="11.42578125" style="16" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" style="16" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="16" customWidth="1"/>
-    <col min="4" max="16384" width="11.42578125" style="16"/>
+    <col min="3" max="3" width="10.7109375" style="16" customWidth="1"/>
+    <col min="4" max="4" width="66.85546875" style="16" customWidth="1"/>
+    <col min="5" max="16384" width="11.42578125" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
     </row>
     <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="85" t="s">
+      <c r="A3" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
     </row>
     <row r="4" spans="1:4" s="17" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -8031,10 +8046,10 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8044,11 +8059,11 @@
       <c r="B5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="16">
+        <v>1</v>
+      </c>
+      <c r="D5" s="55" t="s">
         <v>116</v>
-      </c>
-      <c r="D5" s="16">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8058,11 +8073,11 @@
       <c r="B6" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="16">
+        <v>2</v>
+      </c>
+      <c r="D6" s="55" t="s">
         <v>119</v>
-      </c>
-      <c r="D6" s="16">
-        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8072,11 +8087,11 @@
       <c r="B7" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="16">
+        <v>3</v>
+      </c>
+      <c r="D7" s="55" t="s">
         <v>122</v>
-      </c>
-      <c r="D7" s="16">
-        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8086,11 +8101,11 @@
       <c r="B8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="16">
+        <v>4</v>
+      </c>
+      <c r="D8" s="55" t="s">
         <v>123</v>
-      </c>
-      <c r="D8" s="16">
-        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8162,23 +8177,23 @@
     </row>
     <row r="2" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="76" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="78"/>
+      <c r="C3" s="76"/>
       <c r="D3" s="70"/>
-      <c r="E3" s="83" t="s">
+      <c r="E3" s="81" t="s">
         <v>182</v>
       </c>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
       <c r="O3" s="17"/>
     </row>
     <row r="4" spans="2:15" s="17" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -8630,34 +8645,34 @@
       <c r="L37" s="25"/>
     </row>
     <row r="38" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="79" t="s">
+      <c r="B38" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="80"/>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="80"/>
-      <c r="G38" s="80"/>
-      <c r="H38" s="80"/>
-      <c r="I38" s="80"/>
-      <c r="J38" s="80"/>
-      <c r="K38" s="80"/>
-      <c r="L38" s="80"/>
+      <c r="C38" s="78"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="78"/>
+      <c r="G38" s="78"/>
+      <c r="H38" s="78"/>
+      <c r="I38" s="78"/>
+      <c r="J38" s="78"/>
+      <c r="K38" s="78"/>
+      <c r="L38" s="78"/>
     </row>
     <row r="39" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="81" t="s">
+      <c r="B39" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="82"/>
-      <c r="D39" s="82"/>
-      <c r="E39" s="82"/>
-      <c r="F39" s="82"/>
-      <c r="G39" s="82"/>
-      <c r="H39" s="82"/>
-      <c r="I39" s="82"/>
-      <c r="J39" s="82"/>
-      <c r="K39" s="82"/>
-      <c r="L39" s="82"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8705,55 +8720,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="87" t="s">
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
     </row>
     <row r="3" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="85" t="s">
+      <c r="A3" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="F3" s="83" t="s">
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="F3" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="84"/>
-      <c r="S3" s="84"/>
-      <c r="T3" s="84"/>
-      <c r="U3" s="84"/>
-      <c r="V3" s="84"/>
-      <c r="W3" s="84"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
     </row>
     <row r="4" spans="1:24" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -10871,10 +10886,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:27" s="14" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="87" t="s">
         <v>209</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="88"/>
       <c r="D2" s="24" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -12636,52 +12651,52 @@
       </c>
     </row>
     <row r="25" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="88" t="s">
+      <c r="B25" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="89"/>
-      <c r="D25" s="89"/>
-      <c r="E25" s="89"/>
-      <c r="F25" s="89"/>
-      <c r="G25" s="89"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="89"/>
-      <c r="J25" s="89"/>
-      <c r="K25" s="89"/>
-      <c r="L25" s="89"/>
-      <c r="M25" s="89"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="89"/>
-      <c r="P25" s="89"/>
-      <c r="Q25" s="89"/>
-      <c r="R25" s="89"/>
-      <c r="S25" s="89"/>
-      <c r="T25" s="89"/>
-      <c r="U25" s="89"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="86"/>
+      <c r="O25" s="86"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="86"/>
+      <c r="R25" s="86"/>
+      <c r="S25" s="86"/>
+      <c r="T25" s="86"/>
+      <c r="U25" s="86"/>
     </row>
     <row r="26" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="88" t="s">
+      <c r="B26" s="85" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="89"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="89"/>
-      <c r="K26" s="89"/>
-      <c r="L26" s="89"/>
-      <c r="M26" s="89"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="89"/>
-      <c r="P26" s="89"/>
-      <c r="Q26" s="89"/>
-      <c r="R26" s="89"/>
-      <c r="S26" s="89"/>
-      <c r="T26" s="89"/>
-      <c r="U26" s="89"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
+      <c r="L26" s="86"/>
+      <c r="M26" s="86"/>
+      <c r="N26" s="86"/>
+      <c r="O26" s="86"/>
+      <c r="P26" s="86"/>
+      <c r="Q26" s="86"/>
+      <c r="R26" s="86"/>
+      <c r="S26" s="86"/>
+      <c r="T26" s="86"/>
+      <c r="U26" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -12690,10 +12705,10 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:V22">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12722,10 +12737,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:27" s="14" customFormat="1" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="88"/>
       <c r="D2" s="24" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -12868,10 +12883,10 @@
       <c r="V3" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="Y3" s="73" t="s">
+      <c r="Y3" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="Z3" s="74"/>
+      <c r="Z3" s="91"/>
     </row>
     <row r="4" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="str">
@@ -13590,10 +13605,10 @@
         <f>IF(MatrizDeAdyacencia!V11=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C11,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</f>
         <v>0</v>
       </c>
-      <c r="Y11" s="90" t="s">
+      <c r="Y11" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="Z11" s="90"/>
+      <c r="Z11" s="89"/>
       <c r="AA11" s="33"/>
     </row>
     <row r="12" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14568,7 +14583,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14604,10 +14619,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" s="14" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="88"/>
       <c r="D2" s="24" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -14761,13 +14776,13 @@
       <c r="V3" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="Y3" s="73" t="s">
+      <c r="Y3" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="Z3" s="74"/>
-      <c r="AA3" s="74"/>
-      <c r="AB3" s="74"/>
-      <c r="AC3" s="74"/>
+      <c r="Z3" s="91"/>
+      <c r="AA3" s="91"/>
+      <c r="AB3" s="91"/>
+      <c r="AC3" s="91"/>
       <c r="AD3" s="40"/>
       <c r="AF3"/>
       <c r="AG3"/>
@@ -16774,7 +16789,7 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:I4 L4:V4 D5:V22">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16801,7 +16816,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16834,10 +16849,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:44" s="14" customFormat="1" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="88"/>
       <c r="D2" s="24" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -16915,10 +16930,10 @@
         <v>Destino operativo final</v>
       </c>
       <c r="W2"/>
-      <c r="X2" s="75" t="s">
+      <c r="X2" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="76"/>
+      <c r="Y2" s="88"/>
       <c r="Z2" s="24" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -28007,7 +28022,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="66" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28020,7 +28035,7 @@
         <color rgb="FFFCFCFF"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>9999</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28050,15 +28065,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" s="14" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="76"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="88"/>
       <c r="I2" s="24"/>
       <c r="J2" s="24"/>
       <c r="K2" s="24"/>
@@ -36678,7 +36693,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="64" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Diseño Red FT.xlsx
+++ b/Diseño Red FT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00_repositorios_GitHub\TFG-AFT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC822DF8-58CC-4A9E-893D-E2D6F658506E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A988F7-F920-40DA-AE7B-121A40476E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="210">
   <si>
     <t>GENERADOR DE MODELOS DE REDES SINTÉTICAS DE FINANCIACIÓN DEL TERRORISMO</t>
   </si>
@@ -480,12 +480,6 @@
     <t>Uso final de los fondos en actividades operativas o logísticas</t>
   </si>
   <si>
-    <t>Sigla</t>
-  </si>
-  <si>
-    <t>Descripción1</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
@@ -793,6 +787,9 @@
   </si>
   <si>
     <t>Capa</t>
+  </si>
+  <si>
+    <t>Notas</t>
   </si>
 </sst>
 </file>
@@ -1632,46 +1629,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -7079,6 +7036,46 @@
         <family val="2"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border outline="0">
         <right style="thin">
           <color rgb="FFD9D9D9"/>
@@ -7200,77 +7197,77 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B2FB235A-71F0-400E-A6F0-508799095DA1}" name="tblTiposDeNodo" displayName="tblTiposDeNodo" ref="A4:D8" headerRowDxfId="246" dataDxfId="245" totalsRowDxfId="244">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2D998733-2F4E-407E-BB96-65EE8D671F3E}" name="Sigla" dataDxfId="243"/>
-    <tableColumn id="2" xr3:uid="{1D05F6E9-EB6D-4FA6-9F98-305486BA8372}" name="Nombre" dataDxfId="242"/>
-    <tableColumn id="4" xr3:uid="{969BC7E1-EE89-4897-8C40-9A8A992E41A8}" name="Capa" dataDxfId="8" totalsRowDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{2A05B337-8674-440C-B5E6-EDF2D3E9C7EF}" name="Descripción1" dataDxfId="241"/>
+    <tableColumn id="1" xr3:uid="{2D998733-2F4E-407E-BB96-65EE8D671F3E}" name="Tipo" dataDxfId="243"/>
+    <tableColumn id="2" xr3:uid="{1D05F6E9-EB6D-4FA6-9F98-305486BA8372}" name="Descripción" dataDxfId="242"/>
+    <tableColumn id="4" xr3:uid="{969BC7E1-EE89-4897-8C40-9A8A992E41A8}" name="Capa" dataDxfId="241" totalsRowDxfId="240"/>
+    <tableColumn id="3" xr3:uid="{2A05B337-8674-440C-B5E6-EDF2D3E9C7EF}" name="Notas" dataDxfId="239"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C3763AE3-0C07-44F8-B723-CD50D544B597}" name="tblMatrizPonderadaValorOperativo" displayName="tblMatrizPonderadaValorOperativo" ref="B3:V22" totalsRowShown="0" headerRowDxfId="123" dataDxfId="121" headerRowBorderDxfId="122" tableBorderDxfId="120" totalsRowBorderDxfId="119">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C3763AE3-0C07-44F8-B723-CD50D544B597}" name="tblMatrizPonderadaValorOperativo" displayName="tblMatrizPonderadaValorOperativo" ref="B3:V22" totalsRowShown="0" headerRowDxfId="121" dataDxfId="119" headerRowBorderDxfId="120" tableBorderDxfId="118" totalsRowBorderDxfId="117">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{AB0E4632-ED12-49C5-876A-D0C45597103C}" name="Nombre Nodo" dataDxfId="118">
+    <tableColumn id="21" xr3:uid="{AB0E4632-ED12-49C5-876A-D0C45597103C}" name="Nombre Nodo" dataDxfId="116">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{1F5E2E88-3C78-4615-A934-EA38CE88F1DA}" name="NodoOrigen \ NodoDestino" dataDxfId="117"/>
-    <tableColumn id="2" xr3:uid="{7A66295D-CA43-492F-8775-35115F7A44EA}" name="O1" dataDxfId="116">
+    <tableColumn id="1" xr3:uid="{1F5E2E88-3C78-4615-A934-EA38CE88F1DA}" name="NodoOrigen \ NodoDestino" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{7A66295D-CA43-492F-8775-35115F7A44EA}" name="O1" dataDxfId="114">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!D4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B8A230F9-7293-4177-956A-4E8B8C3CDA07}" name="O2" dataDxfId="115">
+    <tableColumn id="3" xr3:uid="{B8A230F9-7293-4177-956A-4E8B8C3CDA07}" name="O2" dataDxfId="113">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!E4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],E$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{58464D2B-4CD6-441D-AB43-966A10F72197}" name="O3" dataDxfId="114">
+    <tableColumn id="4" xr3:uid="{58464D2B-4CD6-441D-AB43-966A10F72197}" name="O3" dataDxfId="112">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!F4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],F$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B54A5E25-CEE0-4DA6-8517-04ED3BBF73C6}" name="O4" dataDxfId="113">
+    <tableColumn id="5" xr3:uid="{B54A5E25-CEE0-4DA6-8517-04ED3BBF73C6}" name="O4" dataDxfId="111">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!G4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],G$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6A0BB34B-830D-4E04-B8C9-46624641D569}" name="O5" dataDxfId="112">
+    <tableColumn id="6" xr3:uid="{6A0BB34B-830D-4E04-B8C9-46624641D569}" name="O5" dataDxfId="110">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!H4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],H$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00DB80CE-0309-4FD9-950E-24D1DFDD9FFF}" name="O6" dataDxfId="111">
+    <tableColumn id="7" xr3:uid="{00DB80CE-0309-4FD9-950E-24D1DFDD9FFF}" name="O6" dataDxfId="109">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!I4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],I$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7AA5A8CA-1E8D-4093-864B-7D03F5756DC4}" name="C1" dataDxfId="110">
+    <tableColumn id="8" xr3:uid="{7AA5A8CA-1E8D-4093-864B-7D03F5756DC4}" name="C1" dataDxfId="108">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!J4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],J$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{03497B6C-E6A2-42BB-B97E-C56E12C9418F}" name="C2" dataDxfId="109">
+    <tableColumn id="9" xr3:uid="{03497B6C-E6A2-42BB-B97E-C56E12C9418F}" name="C2" dataDxfId="107">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!K4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],K$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{0FA96BFD-FC30-4C99-86C3-1B3F7728768B}" name="C3" dataDxfId="108">
+    <tableColumn id="10" xr3:uid="{0FA96BFD-FC30-4C99-86C3-1B3F7728768B}" name="C3" dataDxfId="106">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!L4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],L$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F3EDBB22-EAE5-496E-8608-9EED6CF8096A}" name="R1" dataDxfId="107">
+    <tableColumn id="11" xr3:uid="{F3EDBB22-EAE5-496E-8608-9EED6CF8096A}" name="R1" dataDxfId="105">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!M4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],M$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EE195140-EF30-4914-AEA7-9A979743FE44}" name="R2" dataDxfId="106">
+    <tableColumn id="12" xr3:uid="{EE195140-EF30-4914-AEA7-9A979743FE44}" name="R2" dataDxfId="104">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!N4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],N$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{940C992B-DC9E-4078-B43B-AD2A2ADF88AA}" name="R3" dataDxfId="105">
+    <tableColumn id="13" xr3:uid="{940C992B-DC9E-4078-B43B-AD2A2ADF88AA}" name="R3" dataDxfId="103">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!O4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],O$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{542FFF8E-DD7B-4C4C-9B1B-C885472540BA}" name="R4" dataDxfId="104">
+    <tableColumn id="14" xr3:uid="{542FFF8E-DD7B-4C4C-9B1B-C885472540BA}" name="R4" dataDxfId="102">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!P4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],P$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{054CF94A-1A1E-4D9F-8BA6-8813EF51323B}" name="R5" dataDxfId="103">
+    <tableColumn id="15" xr3:uid="{054CF94A-1A1E-4D9F-8BA6-8813EF51323B}" name="R5" dataDxfId="101">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!Q4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],Q$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{7ED93D8E-5836-4A3E-9935-FBC89CD3F932}" name="R6" dataDxfId="102">
+    <tableColumn id="16" xr3:uid="{7ED93D8E-5836-4A3E-9935-FBC89CD3F932}" name="R6" dataDxfId="100">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!R4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],R$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{164A5867-1655-4663-992A-899F25195899}" name="R7" dataDxfId="101">
+    <tableColumn id="17" xr3:uid="{164A5867-1655-4663-992A-899F25195899}" name="R7" dataDxfId="99">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!S4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],S$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{E33E9D43-CAE7-4043-AE20-D5AC6983C7DD}" name="R8" dataDxfId="100">
+    <tableColumn id="18" xr3:uid="{E33E9D43-CAE7-4043-AE20-D5AC6983C7DD}" name="R8" dataDxfId="98">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!T4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],T$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{5758BF82-052C-40CF-8505-1FBCD9CE2809}" name="R9" dataDxfId="99">
+    <tableColumn id="19" xr3:uid="{5758BF82-052C-40CF-8505-1FBCD9CE2809}" name="R9" dataDxfId="97">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!U4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],U$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{B734CB8C-660E-449E-8793-5B1787F00081}" name="D1" dataDxfId="98">
+    <tableColumn id="20" xr3:uid="{B734CB8C-660E-449E-8793-5B1787F00081}" name="D1" dataDxfId="96">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!V4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7279,94 +7276,94 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5D156EC0-C7DA-458D-93D7-E916A2987C0A}" name="tblPesosValorOperativo" displayName="tblPesosValorOperativo" ref="Y4:AC9" totalsRowShown="0" headerRowDxfId="97" dataDxfId="95" headerRowBorderDxfId="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5D156EC0-C7DA-458D-93D7-E916A2987C0A}" name="tblPesosValorOperativo" displayName="tblPesosValorOperativo" ref="Y4:AC9" totalsRowShown="0" headerRowDxfId="95" dataDxfId="93" headerRowBorderDxfId="94">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B21AD536-482D-4B9A-AB5E-37E015551681}" name="Valor" dataDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{F200399A-6022-47BF-9665-7A71F541FDA5}" name="Eficiencia" dataDxfId="93"/>
-    <tableColumn id="3" xr3:uid="{FF663B4E-11C8-434F-A1B1-0562E8F7FB14}" name="Exposición" dataDxfId="92"/>
-    <tableColumn id="4" xr3:uid="{D5B0977C-E15F-4467-A561-675FCAB097AB}" name="Capacidad" dataDxfId="91"/>
-    <tableColumn id="5" xr3:uid="{A82F60D0-C02D-4214-9AB5-F7EDAD97FCF6}" name="Resiliencia" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{B21AD536-482D-4B9A-AB5E-37E015551681}" name="Valor" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{F200399A-6022-47BF-9665-7A71F541FDA5}" name="Eficiencia" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{FF663B4E-11C8-434F-A1B1-0562E8F7FB14}" name="Exposición" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{D5B0977C-E15F-4467-A561-675FCAB097AB}" name="Capacidad" dataDxfId="89"/>
+    <tableColumn id="5" xr3:uid="{A82F60D0-C02D-4214-9AB5-F7EDAD97FCF6}" name="Resiliencia" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9318777C-0265-4E44-A0BA-CFC469B6C744}" name="tblRangoEnlace1ValorOpertivo" displayName="tblRangoEnlace1ValorOpertivo" ref="Y12:AD14" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9318777C-0265-4E44-A0BA-CFC469B6C744}" name="tblRangoEnlace1ValorOpertivo" displayName="tblRangoEnlace1ValorOpertivo" ref="Y12:AD14" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{753333F3-816E-431E-BB43-7A7927A7163F}" name="Rango del Enlace" dataDxfId="86"/>
-    <tableColumn id="2" xr3:uid="{72E9BB48-4FA1-4371-A282-0262F904FF9A}" name="Eficiencia" dataDxfId="85"/>
-    <tableColumn id="3" xr3:uid="{87F86AC7-35A2-437C-87BC-FB7CF221D935}" name="Exposición" dataDxfId="84"/>
-    <tableColumn id="4" xr3:uid="{3BA6459E-1C77-4D92-88F9-A4DA307EB1FF}" name="Capacidad" dataDxfId="83"/>
-    <tableColumn id="5" xr3:uid="{CED3CA81-A959-4820-A212-1AB6D2F76092}" name="Resiliencia" dataDxfId="82"/>
-    <tableColumn id="6" xr3:uid="{AFD0E7F4-AEB0-480B-BEDB-0D56FC9A258D}" name="Total" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{753333F3-816E-431E-BB43-7A7927A7163F}" name="Rango del Enlace" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{72E9BB48-4FA1-4371-A282-0262F904FF9A}" name="Eficiencia" dataDxfId="83"/>
+    <tableColumn id="3" xr3:uid="{87F86AC7-35A2-437C-87BC-FB7CF221D935}" name="Exposición" dataDxfId="82"/>
+    <tableColumn id="4" xr3:uid="{3BA6459E-1C77-4D92-88F9-A4DA307EB1FF}" name="Capacidad" dataDxfId="81"/>
+    <tableColumn id="5" xr3:uid="{CED3CA81-A959-4820-A212-1AB6D2F76092}" name="Resiliencia" dataDxfId="80"/>
+    <tableColumn id="6" xr3:uid="{AFD0E7F4-AEB0-480B-BEDB-0D56FC9A258D}" name="Total" dataDxfId="79"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DCB388D3-5907-4F27-B1F2-50F7C3CEFD03}" name="tblMatrizTradeOff" displayName="tblMatrizTradeOff" ref="B3:V22" totalsRowShown="0" headerRowDxfId="80" dataDxfId="78" headerRowBorderDxfId="79" tableBorderDxfId="77" totalsRowBorderDxfId="76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DCB388D3-5907-4F27-B1F2-50F7C3CEFD03}" name="tblMatrizTradeOff" displayName="tblMatrizTradeOff" ref="B3:V22" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{AA1E6080-4E20-4F11-BF7D-BCF3B7198FDD}" name="Nombre Nodo" dataDxfId="75">
+    <tableColumn id="21" xr3:uid="{AA1E6080-4E20-4F11-BF7D-BCF3B7198FDD}" name="Nombre Nodo" dataDxfId="73">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{894C4500-CF7B-4D11-8AA7-3C7C1BD512C6}" name="NodoOrigen \ NodoDestino" dataDxfId="74"/>
-    <tableColumn id="2" xr3:uid="{9F705910-1DB5-40FC-A6DE-98805525ACF0}" name="O1" dataDxfId="73">
+    <tableColumn id="1" xr3:uid="{894C4500-CF7B-4D11-8AA7-3C7C1BD512C6}" name="NodoOrigen \ NodoDestino" dataDxfId="72"/>
+    <tableColumn id="2" xr3:uid="{9F705910-1DB5-40FC-A6DE-98805525ACF0}" name="O1" dataDxfId="71">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!D4=0,MatrizPonderadaValorOperativo!D4=0),0,MatrizPonderadaValorOperativo!D4/MatrizPonderadaCostes!D4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{50058AD6-7468-4AC7-97C5-05F954228EC1}" name="O2" dataDxfId="72">
+    <tableColumn id="3" xr3:uid="{50058AD6-7468-4AC7-97C5-05F954228EC1}" name="O2" dataDxfId="70">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!E4=0,MatrizPonderadaValorOperativo!E4=0),0,MatrizPonderadaValorOperativo!E4/MatrizPonderadaCostes!E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7C94D72A-7710-415D-86F3-659E59F93C96}" name="O3" dataDxfId="71">
+    <tableColumn id="4" xr3:uid="{7C94D72A-7710-415D-86F3-659E59F93C96}" name="O3" dataDxfId="69">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!F4=0,MatrizPonderadaValorOperativo!F4=0),0,MatrizPonderadaValorOperativo!F4/MatrizPonderadaCostes!F4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{532BA85E-D317-4F75-A439-3A5B03302C28}" name="O4" dataDxfId="70">
+    <tableColumn id="5" xr3:uid="{532BA85E-D317-4F75-A439-3A5B03302C28}" name="O4" dataDxfId="68">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!G4=0,MatrizPonderadaValorOperativo!G4=0),0,MatrizPonderadaValorOperativo!G4/MatrizPonderadaCostes!G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{063CA99D-B02A-474E-BF88-15CCC8190E67}" name="O5" dataDxfId="69">
+    <tableColumn id="6" xr3:uid="{063CA99D-B02A-474E-BF88-15CCC8190E67}" name="O5" dataDxfId="67">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!H4=0,MatrizPonderadaValorOperativo!H4=0),0,MatrizPonderadaValorOperativo!H4/MatrizPonderadaCostes!H4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{7BAB99D6-E0DD-44E8-812E-F31B042D5A8F}" name="O6" dataDxfId="68">
+    <tableColumn id="7" xr3:uid="{7BAB99D6-E0DD-44E8-812E-F31B042D5A8F}" name="O6" dataDxfId="66">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!I4=0,MatrizPonderadaValorOperativo!I4=0),0,MatrizPonderadaValorOperativo!I4/MatrizPonderadaCostes!I4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7A6532A5-C6A7-497A-9950-E4CF326FB1D0}" name="I1" dataDxfId="67">
+    <tableColumn id="8" xr3:uid="{7A6532A5-C6A7-497A-9950-E4CF326FB1D0}" name="I1" dataDxfId="65">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!J4=0,MatrizPonderadaValorOperativo!J4=0),0,MatrizPonderadaValorOperativo!J4/MatrizPonderadaCostes!J4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{7D782904-1F98-40F1-90DB-B287194DD5EC}" name="I2" dataDxfId="66">
+    <tableColumn id="9" xr3:uid="{7D782904-1F98-40F1-90DB-B287194DD5EC}" name="I2" dataDxfId="64">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!K4=0,MatrizPonderadaValorOperativo!K4=0),0,MatrizPonderadaValorOperativo!K4/MatrizPonderadaCostes!K4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F8DFA04B-3F58-4A4C-84F2-C08ECA18C8D0}" name="I3" dataDxfId="65">
+    <tableColumn id="10" xr3:uid="{F8DFA04B-3F58-4A4C-84F2-C08ECA18C8D0}" name="I3" dataDxfId="63">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!L4=0,MatrizPonderadaValorOperativo!L4=0),0,MatrizPonderadaValorOperativo!L4/MatrizPonderadaCostes!L4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{BEE1D8C4-0249-4AEB-85C7-3C1964171690}" name="I4" dataDxfId="64">
+    <tableColumn id="11" xr3:uid="{BEE1D8C4-0249-4AEB-85C7-3C1964171690}" name="I4" dataDxfId="62">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!M4=0,MatrizPonderadaValorOperativo!M4=0),0,MatrizPonderadaValorOperativo!M4/MatrizPonderadaCostes!M4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5E8D8652-5E54-4316-9F7E-FE077E7F3845}" name="I5" dataDxfId="63">
+    <tableColumn id="12" xr3:uid="{5E8D8652-5E54-4316-9F7E-FE077E7F3845}" name="I5" dataDxfId="61">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!N4=0,MatrizPonderadaValorOperativo!N4=0),0,MatrizPonderadaValorOperativo!N4/MatrizPonderadaCostes!N4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{19070E8B-9ED0-4B66-9707-071DEBF3C994}" name="I6" dataDxfId="62">
+    <tableColumn id="13" xr3:uid="{19070E8B-9ED0-4B66-9707-071DEBF3C994}" name="I6" dataDxfId="60">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!O4=0,MatrizPonderadaValorOperativo!O4=0),0,MatrizPonderadaValorOperativo!O4/MatrizPonderadaCostes!O4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{76F2DA9F-DAF7-439A-84BF-1733FA9657FD}" name="I7" dataDxfId="61">
+    <tableColumn id="14" xr3:uid="{76F2DA9F-DAF7-439A-84BF-1733FA9657FD}" name="I7" dataDxfId="59">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!P4=0,MatrizPonderadaValorOperativo!P4=0),0,MatrizPonderadaValorOperativo!P4/MatrizPonderadaCostes!P4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7D6FF674-D8C7-4CDC-B88A-E9A853759EB2}" name="I8" dataDxfId="60">
+    <tableColumn id="15" xr3:uid="{7D6FF674-D8C7-4CDC-B88A-E9A853759EB2}" name="I8" dataDxfId="58">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!Q4=0,MatrizPonderadaValorOperativo!Q4=0),0,MatrizPonderadaValorOperativo!Q4/MatrizPonderadaCostes!Q4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{4874BEF7-C26F-4D06-BE1E-88E85D5250AC}" name="I9" dataDxfId="59">
+    <tableColumn id="16" xr3:uid="{4874BEF7-C26F-4D06-BE1E-88E85D5250AC}" name="I9" dataDxfId="57">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!R4=0,MatrizPonderadaValorOperativo!R4=0),0,MatrizPonderadaValorOperativo!R4/MatrizPonderadaCostes!R4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{A372A997-A44F-44EB-AAED-77C0B6E13538}" name="G1" dataDxfId="58">
+    <tableColumn id="17" xr3:uid="{A372A997-A44F-44EB-AAED-77C0B6E13538}" name="G1" dataDxfId="56">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!S4=0,MatrizPonderadaValorOperativo!S4=0),0,MatrizPonderadaValorOperativo!S4/MatrizPonderadaCostes!S4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{0F8CF6FF-ABAA-4A01-AD38-A32A28F3744E}" name="G2" dataDxfId="57">
+    <tableColumn id="18" xr3:uid="{0F8CF6FF-ABAA-4A01-AD38-A32A28F3744E}" name="G2" dataDxfId="55">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!T4=0,MatrizPonderadaValorOperativo!T4=0),0,MatrizPonderadaValorOperativo!T4/MatrizPonderadaCostes!T4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{AB7C5AA0-D767-454C-BA7B-5A2B55F42FB8}" name="G3" dataDxfId="56">
+    <tableColumn id="19" xr3:uid="{AB7C5AA0-D767-454C-BA7B-5A2B55F42FB8}" name="G3" dataDxfId="54">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!U4=0,MatrizPonderadaValorOperativo!U4=0),0,MatrizPonderadaValorOperativo!U4/MatrizPonderadaCostes!U4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{23B65986-1386-4DD0-B9E1-CF1D12F9896F}" name="D" dataDxfId="55">
+    <tableColumn id="20" xr3:uid="{23B65986-1386-4DD0-B9E1-CF1D12F9896F}" name="D" dataDxfId="53">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!V4=0,MatrizPonderadaValorOperativo!V4=0),0,MatrizPonderadaValorOperativo!V4/MatrizPonderadaCostes!V4)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7375,67 +7372,67 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5873A7B6-81FB-4D79-A0FB-9D6FB64CE88D}" name="tblMatrizDistancias" displayName="tblMatrizDistancias" ref="X3:AR22" totalsRowShown="0" headerRowDxfId="54" dataDxfId="52" headerRowBorderDxfId="53" tableBorderDxfId="51" totalsRowBorderDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5873A7B6-81FB-4D79-A0FB-9D6FB64CE88D}" name="tblMatrizDistancias" displayName="tblMatrizDistancias" ref="X3:AR22" totalsRowShown="0" headerRowDxfId="52" dataDxfId="50" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="48">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{1BAD8E49-23F7-4BE2-B973-AA604F8B446D}" name="Nombre Nodo" dataDxfId="49">
+    <tableColumn id="21" xr3:uid="{1BAD8E49-23F7-4BE2-B973-AA604F8B446D}" name="Nombre Nodo" dataDxfId="47">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{CCA43D7E-3A02-4B90-B8B1-A5C2C1770B89}" name="NodoOrigen \ NodoDestino" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{258A9219-735F-4D5E-96CD-61C2192DE988}" name="O1" dataDxfId="47">
+    <tableColumn id="1" xr3:uid="{CCA43D7E-3A02-4B90-B8B1-A5C2C1770B89}" name="NodoOrigen \ NodoDestino" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{258A9219-735F-4D5E-96CD-61C2192DE988}" name="O1" dataDxfId="45">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O1",0,IF(tblMatrizTradeOff[[#This Row],[O1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A742D52A-B21E-494D-9BEC-A3E5CC2D1787}" name="O2" dataDxfId="46">
+    <tableColumn id="3" xr3:uid="{A742D52A-B21E-494D-9BEC-A3E5CC2D1787}" name="O2" dataDxfId="44">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O2",0,IF(tblMatrizTradeOff[[#This Row],[O2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E3462037-DD10-4D8C-B6A1-5ADBA379FEB1}" name="O3" dataDxfId="45">
+    <tableColumn id="4" xr3:uid="{E3462037-DD10-4D8C-B6A1-5ADBA379FEB1}" name="O3" dataDxfId="43">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O3",0,IF(tblMatrizTradeOff[[#This Row],[O3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E48B988C-DC5A-4772-9E34-F71B68D92DCB}" name="O4" dataDxfId="44">
+    <tableColumn id="5" xr3:uid="{E48B988C-DC5A-4772-9E34-F71B68D92DCB}" name="O4" dataDxfId="42">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O4",0,IF(tblMatrizTradeOff[[#This Row],[O4]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O4]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{43CEAEF6-D25A-41BD-B40B-81780EA42997}" name="O5" dataDxfId="43">
+    <tableColumn id="6" xr3:uid="{43CEAEF6-D25A-41BD-B40B-81780EA42997}" name="O5" dataDxfId="41">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O5",0,IF(tblMatrizTradeOff[[#This Row],[O5]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O5]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3924F7A5-FD83-43F2-A080-29822934E0BE}" name="O6" dataDxfId="42">
+    <tableColumn id="7" xr3:uid="{3924F7A5-FD83-43F2-A080-29822934E0BE}" name="O6" dataDxfId="40">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O6",0,IF(tblMatrizTradeOff[[#This Row],[O6]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O6]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7547ECC7-C391-409A-A35D-75672D9B0DFF}" name="I1" dataDxfId="41">
+    <tableColumn id="8" xr3:uid="{7547ECC7-C391-409A-A35D-75672D9B0DFF}" name="I1" dataDxfId="39">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I1",0,IF(tblMatrizTradeOff[[#This Row],[I1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{10E4BD07-2311-4179-8574-4C902D93606E}" name="I2" dataDxfId="40">
+    <tableColumn id="9" xr3:uid="{10E4BD07-2311-4179-8574-4C902D93606E}" name="I2" dataDxfId="38">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I2",0,IF(tblMatrizTradeOff[[#This Row],[I2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C7634E23-202A-42C0-8E82-749F13342982}" name="I3" dataDxfId="39">
+    <tableColumn id="10" xr3:uid="{C7634E23-202A-42C0-8E82-749F13342982}" name="I3" dataDxfId="37">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I3",0,IF(tblMatrizTradeOff[[#This Row],[I3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{80F89DAB-DC38-4E1B-8C6E-ABAE0670FA4C}" name="I4" dataDxfId="38">
+    <tableColumn id="11" xr3:uid="{80F89DAB-DC38-4E1B-8C6E-ABAE0670FA4C}" name="I4" dataDxfId="36">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I4",0,IF(tblMatrizTradeOff[[#This Row],[I4]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I4]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{1690E7CA-C688-4A77-B2E4-78675EA5F6AF}" name="I5" dataDxfId="37">
+    <tableColumn id="12" xr3:uid="{1690E7CA-C688-4A77-B2E4-78675EA5F6AF}" name="I5" dataDxfId="35">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I5",0,IF(tblMatrizTradeOff[[#This Row],[I5]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I5]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{3A1E36E4-69D3-406F-91FA-CE9683D234A1}" name="I6" dataDxfId="36">
+    <tableColumn id="13" xr3:uid="{3A1E36E4-69D3-406F-91FA-CE9683D234A1}" name="I6" dataDxfId="34">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I6",0,IF(tblMatrizTradeOff[[#This Row],[I6]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I6]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{37A3FAD7-64EF-4C10-A216-8F4121D763FE}" name="I7" dataDxfId="35">
+    <tableColumn id="14" xr3:uid="{37A3FAD7-64EF-4C10-A216-8F4121D763FE}" name="I7" dataDxfId="33">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I7",0,IF(tblMatrizTradeOff[[#This Row],[I7]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I7]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{C79CE9F5-E392-4C54-A368-4072A211349B}" name="I8" dataDxfId="34">
+    <tableColumn id="15" xr3:uid="{C79CE9F5-E392-4C54-A368-4072A211349B}" name="I8" dataDxfId="32">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I8",0,IF(tblMatrizTradeOff[[#This Row],[I8]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I8]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{AF9AF109-E8FC-499B-B541-D049A2CD781D}" name="I9" dataDxfId="33">
+    <tableColumn id="16" xr3:uid="{AF9AF109-E8FC-499B-B541-D049A2CD781D}" name="I9" dataDxfId="31">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I9",0,IF(tblMatrizTradeOff[[#This Row],[I9]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I9]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C49A9B94-D73C-40C2-9773-A0B40E4AAC62}" name="G1" dataDxfId="32">
+    <tableColumn id="17" xr3:uid="{C49A9B94-D73C-40C2-9773-A0B40E4AAC62}" name="G1" dataDxfId="30">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G1",0,IF(tblMatrizTradeOff[[#This Row],[G1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[G1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{37DF13C5-7088-4645-80B8-632B4668B1C6}" name="G2" dataDxfId="31">
+    <tableColumn id="18" xr3:uid="{37DF13C5-7088-4645-80B8-632B4668B1C6}" name="G2" dataDxfId="29">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G2",0,IF(tblMatrizTradeOff[[#This Row],[G2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[G2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{0C6F5759-0A04-44DB-ABD3-792D0DD2FD39}" name="G3" dataDxfId="30">
+    <tableColumn id="19" xr3:uid="{0C6F5759-0A04-44DB-ABD3-792D0DD2FD39}" name="G3" dataDxfId="28">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G3",0,IF(tblMatrizTradeOff[[#This Row],[G3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[G3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{08ECC6AD-B105-48DC-B6EF-5213E3FB7C76}" name="D" dataDxfId="29">
+    <tableColumn id="20" xr3:uid="{08ECC6AD-B105-48DC-B6EF-5213E3FB7C76}" name="D" dataDxfId="27">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="D",0,IF(tblMatrizTradeOff[[#This Row],[D]]=0,9999,1/tblMatrizTradeOff[[#This Row],[D]]))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7444,25 +7441,25 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7B2B6549-1979-4B25-A35A-52BA4A0A39EE}" name="tblGradoPonderado" displayName="tblGradoPonderado" ref="B3:H23" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7B2B6549-1979-4B25-A35A-52BA4A0A39EE}" name="tblGradoPonderado" displayName="tblGradoPonderado" ref="B3:H23" totalsRowCount="1" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="22">
   <tableColumns count="7">
-    <tableColumn id="21" xr3:uid="{77F6B8A9-151C-415D-A901-35466078EF18}" name="Nombre Nodo" totalsRowLabel="Totales / Máximos / Mínimos" dataDxfId="23" totalsRowDxfId="22">
+    <tableColumn id="21" xr3:uid="{77F6B8A9-151C-415D-A901-35466078EF18}" name="Nombre Nodo" totalsRowLabel="Totales / Máximos / Mínimos" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{253666FE-A069-4260-AC52-8AE7DE9B8F38}" name="Nodo" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{AA42A750-6BE0-4870-A26E-410A2BC2C73B}" name="Grado Ponderado de Entrada" dataDxfId="19" totalsRowDxfId="18">
+    <tableColumn id="1" xr3:uid="{253666FE-A069-4260-AC52-8AE7DE9B8F38}" name="Nodo" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{AA42A750-6BE0-4870-A26E-410A2BC2C73B}" name="Grado Ponderado de Entrada" dataDxfId="17" totalsRowDxfId="16">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.n,tblGradoPonderado[[#This Row],[Nodo]],_xlpm.col,_xlfn.XLOOKUP(_xlpm.n,tblMatrizTradeOff[#Headers],tblMatrizTradeOff[#Data]),SUM(_xlpm.col))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{378B0278-AE86-49A4-8668-271111E0777E}" name="Grado Ponderado de Salida" dataDxfId="17" totalsRowDxfId="16">
+    <tableColumn id="3" xr3:uid="{378B0278-AE86-49A4-8668-271111E0777E}" name="Grado Ponderado de Salida" dataDxfId="15" totalsRowDxfId="14">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.n,tblGradoPonderado[[#This Row],[Nodo]],_xlpm.row,_xlfn.XLOOKUP(_xlpm.n,tblMatrizTradeOff[NodoOrigen \ NodoDestino],tblMatrizTradeOff[[O1]:[D]]),SUM(_xlpm.row))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3C52036B-2CF5-484C-8203-C94636D157F9}" name="Grado Ponderado Total" totalsRowFunction="max" dataDxfId="15" totalsRowDxfId="14">
+    <tableColumn id="4" xr3:uid="{3C52036B-2CF5-484C-8203-C94636D157F9}" name="Grado Ponderado Total" totalsRowFunction="max" dataDxfId="13" totalsRowDxfId="12">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado de Entrada]]+tblGradoPonderado[[#This Row],[Grado Ponderado de Salida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FFBA1243-72FC-40D4-AE6E-AE5864D502FB}" name="Balance Neto" dataDxfId="13" totalsRowDxfId="12">
+    <tableColumn id="5" xr3:uid="{FFBA1243-72FC-40D4-AE6E-AE5864D502FB}" name="Balance Neto" dataDxfId="11" totalsRowDxfId="10">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado de Salida]]-tblGradoPonderado[[#This Row],[Grado Ponderado de Entrada]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{94B10867-99D5-439C-B33C-5612EB83F5A4}" name="Grado Normalizado" dataDxfId="11" totalsRowDxfId="10">
+    <tableColumn id="6" xr3:uid="{94B10867-99D5-439C-B33C-5612EB83F5A4}" name="Grado Normalizado" dataDxfId="9" totalsRowDxfId="8">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado Total]]/tblGradoPonderado[[#Totals],[Grado Ponderado Total]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7471,77 +7468,77 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{684D43B5-10F8-42CD-A78F-0A2D7790FEBB}" name="tblPropiedadesCanales" displayName="tblPropiedadesCanales" ref="B4:C9" totalsRowShown="0" headerRowDxfId="240" dataDxfId="238" headerRowBorderDxfId="239" tableBorderDxfId="237">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{684D43B5-10F8-42CD-A78F-0A2D7790FEBB}" name="tblPropiedadesCanales" displayName="tblPropiedadesCanales" ref="B4:C9" totalsRowShown="0" headerRowDxfId="238" dataDxfId="236" headerRowBorderDxfId="237" tableBorderDxfId="235">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AE28D037-8200-4290-B185-521BE4E5D98F}" name="Variable" dataDxfId="236"/>
-    <tableColumn id="2" xr3:uid="{6EBF46F3-2102-4B98-9EA7-E0EC740C287C}" name="Definición recomendada" dataDxfId="235"/>
+    <tableColumn id="1" xr3:uid="{AE28D037-8200-4290-B185-521BE4E5D98F}" name="Variable" dataDxfId="234"/>
+    <tableColumn id="2" xr3:uid="{6EBF46F3-2102-4B98-9EA7-E0EC740C287C}" name="Definición recomendada" dataDxfId="233"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{A4F8E1C4-8F10-4A16-A363-66F29C756757}" name="tblCanales" displayName="tblCanales" ref="E4:N13" totalsRowShown="0" headerRowDxfId="234" dataDxfId="232" headerRowBorderDxfId="233" tableBorderDxfId="231" totalsRowBorderDxfId="230">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{A4F8E1C4-8F10-4A16-A363-66F29C756757}" name="tblCanales" displayName="tblCanales" ref="E4:N13" totalsRowShown="0" headerRowDxfId="232" dataDxfId="230" headerRowBorderDxfId="231" tableBorderDxfId="229" totalsRowBorderDxfId="228">
   <tableColumns count="10">
-    <tableColumn id="2" xr3:uid="{EC47E1C1-969B-40D7-A166-5065044FE8EE}" name="Nombre" dataDxfId="229"/>
-    <tableColumn id="4" xr3:uid="{C51CDB64-59EA-4881-B723-18B95E872D00}" name="Descripción" dataDxfId="228"/>
-    <tableColumn id="3" xr3:uid="{1CBE7731-79F9-40FF-82B5-B5E44A771838}" name="Tipo" dataDxfId="227"/>
-    <tableColumn id="5" xr3:uid="{E8249A44-897D-4018-B0CA-C983252BCFC8}" name="Coste" dataDxfId="226"/>
-    <tableColumn id="6" xr3:uid="{CE3CC37C-5B67-40F0-93BA-BA26DF959A93}" name="Eficiencia" dataDxfId="225"/>
-    <tableColumn id="7" xr3:uid="{C41E7A4D-CE1C-4D71-B522-398A7272A699}" name="Exposición" dataDxfId="224"/>
-    <tableColumn id="8" xr3:uid="{7AB4DB4D-AE68-4160-A03A-FCDB4E7546E5}" name="Capacidad" dataDxfId="223"/>
-    <tableColumn id="9" xr3:uid="{1354059D-8430-454F-87FD-5887F9F6B688}" name="Resiliencia" dataDxfId="222"/>
-    <tableColumn id="10" xr3:uid="{BC196392-856A-4221-9F76-9E4E7BC1F726}" name="GAFI" dataDxfId="221"/>
-    <tableColumn id="11" xr3:uid="{1CE9226F-8F31-4975-BF4A-078BB1C41195}" name="MODELO" dataDxfId="220"/>
+    <tableColumn id="2" xr3:uid="{EC47E1C1-969B-40D7-A166-5065044FE8EE}" name="Nombre" dataDxfId="227"/>
+    <tableColumn id="4" xr3:uid="{C51CDB64-59EA-4881-B723-18B95E872D00}" name="Descripción" dataDxfId="226"/>
+    <tableColumn id="3" xr3:uid="{1CBE7731-79F9-40FF-82B5-B5E44A771838}" name="Tipo" dataDxfId="225"/>
+    <tableColumn id="5" xr3:uid="{E8249A44-897D-4018-B0CA-C983252BCFC8}" name="Coste" dataDxfId="224"/>
+    <tableColumn id="6" xr3:uid="{CE3CC37C-5B67-40F0-93BA-BA26DF959A93}" name="Eficiencia" dataDxfId="223"/>
+    <tableColumn id="7" xr3:uid="{C41E7A4D-CE1C-4D71-B522-398A7272A699}" name="Exposición" dataDxfId="222"/>
+    <tableColumn id="8" xr3:uid="{7AB4DB4D-AE68-4160-A03A-FCDB4E7546E5}" name="Capacidad" dataDxfId="221"/>
+    <tableColumn id="9" xr3:uid="{1354059D-8430-454F-87FD-5887F9F6B688}" name="Resiliencia" dataDxfId="220"/>
+    <tableColumn id="10" xr3:uid="{BC196392-856A-4221-9F76-9E4E7BC1F726}" name="GAFI" dataDxfId="219"/>
+    <tableColumn id="11" xr3:uid="{1CE9226F-8F31-4975-BF4A-078BB1C41195}" name="MODELO" dataDxfId="218"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="F4:W30" headerRowDxfId="219" dataDxfId="218" totalsRowDxfId="217">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="F4:W30" headerRowDxfId="217" dataDxfId="216" totalsRowDxfId="215">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F5:Q30">
     <sortCondition ref="F4:F30"/>
   </sortState>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="216"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="215"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="214"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="213"/>
-    <tableColumn id="21" xr3:uid="{9EA0CAA5-0A23-473B-943E-3CC802BE75BA}" name="Canal" dataDxfId="212"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="211"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="210"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="209">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="214"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="213"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="212"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="211"/>
+    <tableColumn id="21" xr3:uid="{9EA0CAA5-0A23-473B-943E-3CC802BE75BA}" name="Canal" dataDxfId="210"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="209"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="208"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="207">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="208">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="206">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],5,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="207">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="205">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],6,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="206">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="204">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],7,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="205">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="203">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],8,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{D5ECEEAB-319C-416C-A120-BD842AFC8541}" name="Coste (peso)" dataDxfId="204" totalsRowDxfId="203">
+    <tableColumn id="23" xr3:uid="{D5ECEEAB-319C-416C-A120-BD842AFC8541}" name="Coste (peso)" dataDxfId="202" totalsRowDxfId="201">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesosCoste[Valor],tblPesosCoste[Coste],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{38505D25-3830-4BBB-8DCF-E8583124C910}" name="Eficiencia (peso)" dataDxfId="202" totalsRowDxfId="201">
+    <tableColumn id="24" xr3:uid="{38505D25-3830-4BBB-8DCF-E8583124C910}" name="Eficiencia (peso)" dataDxfId="200" totalsRowDxfId="199">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Eficiencia],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{8E52D89B-D169-4F48-AD66-44B1E56CB633}" name="Exposición (peso)" dataDxfId="200" totalsRowDxfId="199">
+    <tableColumn id="25" xr3:uid="{8E52D89B-D169-4F48-AD66-44B1E56CB633}" name="Exposición (peso)" dataDxfId="198" totalsRowDxfId="197">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Exposición],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{1F2413A4-A4B8-4902-8061-3A60A70F9F2F}" name="Capacidad (peso)" dataDxfId="198" totalsRowDxfId="197">
+    <tableColumn id="26" xr3:uid="{1F2413A4-A4B8-4902-8061-3A60A70F9F2F}" name="Capacidad (peso)" dataDxfId="196" totalsRowDxfId="195">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Capacidad],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{67FAA096-3D2B-4E91-9E1F-AEE59F7A690B}" name="Resiliencia (peso)" dataDxfId="196" totalsRowDxfId="195">
+    <tableColumn id="27" xr3:uid="{67FAA096-3D2B-4E91-9E1F-AEE59F7A690B}" name="Resiliencia (peso)" dataDxfId="194" totalsRowDxfId="193">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Resiliencia],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{378FBC0C-D6D1-4CC5-A688-4AE8E0EEFF15}" name="Valor Operativo (peso)" dataDxfId="194" totalsRowDxfId="193">
+    <tableColumn id="28" xr3:uid="{378FBC0C-D6D1-4CC5-A688-4AE8E0EEFF15}" name="Valor Operativo (peso)" dataDxfId="192" totalsRowDxfId="191">
       <calculatedColumnFormula>tblEnlaces[[#This Row],[Eficiencia (peso)]]+tblEnlaces[[#This Row],[Resiliencia (peso)]]+tblEnlaces[[#This Row],[Capacidad (peso)]]+tblEnlaces[[#This Row],[Exposición (peso)]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7550,80 +7547,80 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}" name="tblNodos" displayName="tblNodos" ref="A4:D23" headerRowDxfId="192" dataDxfId="191" totalsRowDxfId="190">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}" name="tblNodos" displayName="tblNodos" ref="A4:D23" headerRowDxfId="190" dataDxfId="189" totalsRowDxfId="188">
   <autoFilter ref="A4:D23" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C216D4B9-76C9-4611-A97A-027837B07F56}" name="NodoID" dataDxfId="189"/>
-    <tableColumn id="2" xr3:uid="{425384C0-D0A9-4E9A-A93C-65C1B3B77DB1}" name="Nombre" dataDxfId="188"/>
-    <tableColumn id="3" xr3:uid="{434558A9-CDA8-4827-AF85-9621517F0875}" name="Tipo" dataDxfId="187"/>
-    <tableColumn id="4" xr3:uid="{B0504143-65F8-445A-9B1A-9CA91BFF8129}" name="Activo" dataDxfId="186"/>
+    <tableColumn id="1" xr3:uid="{C216D4B9-76C9-4611-A97A-027837B07F56}" name="NodoID" dataDxfId="187"/>
+    <tableColumn id="2" xr3:uid="{425384C0-D0A9-4E9A-A93C-65C1B3B77DB1}" name="Nombre" dataDxfId="186"/>
+    <tableColumn id="3" xr3:uid="{434558A9-CDA8-4827-AF85-9621517F0875}" name="Tipo" dataDxfId="185"/>
+    <tableColumn id="4" xr3:uid="{B0504143-65F8-445A-9B1A-9CA91BFF8129}" name="Activo" dataDxfId="184"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="185" dataDxfId="183" headerRowBorderDxfId="184" tableBorderDxfId="182" totalsRowBorderDxfId="181">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="183" dataDxfId="181" headerRowBorderDxfId="182" tableBorderDxfId="180" totalsRowBorderDxfId="179">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="180">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="178">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="179"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="178">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="177"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="176">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="177">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="175">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,E$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="176">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="174">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,F$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="175">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="173">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,G$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="174">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="172">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,H$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="173">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="171">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,I$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="C1" dataDxfId="172">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="C1" dataDxfId="170">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,J$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="C2" dataDxfId="171">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="C2" dataDxfId="169">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,K$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="C3" dataDxfId="170">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="C3" dataDxfId="168">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,L$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="R1" dataDxfId="169">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="R1" dataDxfId="167">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,M$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="R2" dataDxfId="168">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="R2" dataDxfId="166">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,N$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="R3" dataDxfId="167">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="R3" dataDxfId="165">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,O$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="R4" dataDxfId="166">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="R4" dataDxfId="164">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,P$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="R5" dataDxfId="165">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="R5" dataDxfId="163">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,Q$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="R6" dataDxfId="164">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="R6" dataDxfId="162">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,R$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="R7" dataDxfId="163">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="R7" dataDxfId="161">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,S$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="R8" dataDxfId="162">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="R8" dataDxfId="160">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,T$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="R9" dataDxfId="161">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="R9" dataDxfId="159">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,U$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D1" dataDxfId="160">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D1" dataDxfId="158">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,V$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7632,67 +7629,67 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{619F938E-46CC-49F1-9A1F-6017755965D1}" name="tblMatrizPonderadaCostes" displayName="tblMatrizPonderadaCostes" ref="B3:V22" totalsRowShown="0" headerRowDxfId="159" dataDxfId="157" headerRowBorderDxfId="158" tableBorderDxfId="156" totalsRowBorderDxfId="155">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{619F938E-46CC-49F1-9A1F-6017755965D1}" name="tblMatrizPonderadaCostes" displayName="tblMatrizPonderadaCostes" ref="B3:V22" totalsRowShown="0" headerRowDxfId="157" dataDxfId="155" headerRowBorderDxfId="156" tableBorderDxfId="154" totalsRowBorderDxfId="153">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{2A9AC9D7-CC14-4058-8CF2-7CDFEC15F78F}" name="Nombre Nodo" dataDxfId="154">
+    <tableColumn id="21" xr3:uid="{2A9AC9D7-CC14-4058-8CF2-7CDFEC15F78F}" name="Nombre Nodo" dataDxfId="152">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{3A911174-7F39-43D0-8D1B-0D1A251C78CF}" name="NodoOrigen \ NodoDestino" dataDxfId="153"/>
-    <tableColumn id="2" xr3:uid="{79E6108F-3B54-4663-83BD-0E9A6288B0A8}" name="O1" dataDxfId="152">
+    <tableColumn id="1" xr3:uid="{3A911174-7F39-43D0-8D1B-0D1A251C78CF}" name="NodoOrigen \ NodoDestino" dataDxfId="151"/>
+    <tableColumn id="2" xr3:uid="{79E6108F-3B54-4663-83BD-0E9A6288B0A8}" name="O1" dataDxfId="150">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!D4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{74BBA163-10F6-4D74-863C-C4517633500F}" name="O2" dataDxfId="151">
+    <tableColumn id="3" xr3:uid="{74BBA163-10F6-4D74-863C-C4517633500F}" name="O2" dataDxfId="149">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!E4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],E$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5D6ADA5C-E165-41EC-803D-18F7A270611C}" name="O3" dataDxfId="150">
+    <tableColumn id="4" xr3:uid="{5D6ADA5C-E165-41EC-803D-18F7A270611C}" name="O3" dataDxfId="148">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!F4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],F$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{035B34FA-1623-4B86-B0EE-0CC6694FFD7C}" name="O4" dataDxfId="149">
+    <tableColumn id="5" xr3:uid="{035B34FA-1623-4B86-B0EE-0CC6694FFD7C}" name="O4" dataDxfId="147">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!G4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],G$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{27739639-E082-4698-9A4C-15EDA8612A83}" name="O5" dataDxfId="148">
+    <tableColumn id="6" xr3:uid="{27739639-E082-4698-9A4C-15EDA8612A83}" name="O5" dataDxfId="146">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!H4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],H$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{ED768978-7E7B-49CD-A202-FE8EBE9E64E0}" name="O6" dataDxfId="147">
+    <tableColumn id="7" xr3:uid="{ED768978-7E7B-49CD-A202-FE8EBE9E64E0}" name="O6" dataDxfId="145">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!I4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],I$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{37684012-4DC0-48DA-8E67-185403ABB81C}" name="C1" dataDxfId="146">
+    <tableColumn id="8" xr3:uid="{37684012-4DC0-48DA-8E67-185403ABB81C}" name="C1" dataDxfId="144">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!J4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],J$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E3684910-7769-4AEF-8800-33DC2F8D7ABC}" name="C2" dataDxfId="145">
+    <tableColumn id="9" xr3:uid="{E3684910-7769-4AEF-8800-33DC2F8D7ABC}" name="C2" dataDxfId="143">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!K4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],K$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A095B3C4-5019-4082-93A5-E12BDE733061}" name="C3" dataDxfId="144">
+    <tableColumn id="10" xr3:uid="{A095B3C4-5019-4082-93A5-E12BDE733061}" name="C3" dataDxfId="142">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!L4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],L$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{C5072B89-856A-4694-9D8B-17C4DB67DFF8}" name="R1" dataDxfId="143">
+    <tableColumn id="11" xr3:uid="{C5072B89-856A-4694-9D8B-17C4DB67DFF8}" name="R1" dataDxfId="141">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!M4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],M$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{0BD76649-1EE0-46D9-8718-F9A6F67BE379}" name="R2" dataDxfId="142">
+    <tableColumn id="12" xr3:uid="{0BD76649-1EE0-46D9-8718-F9A6F67BE379}" name="R2" dataDxfId="140">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!N4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],N$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{263255E9-BE7D-4E45-A463-5AD358998CB9}" name="R3" dataDxfId="141">
+    <tableColumn id="13" xr3:uid="{263255E9-BE7D-4E45-A463-5AD358998CB9}" name="R3" dataDxfId="139">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!O4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],O$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{7AF510BB-CB1B-461F-8746-C7133DC25996}" name="R4" dataDxfId="140">
+    <tableColumn id="14" xr3:uid="{7AF510BB-CB1B-461F-8746-C7133DC25996}" name="R4" dataDxfId="138">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!P4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],P$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{42A7B19E-8A6C-4FA9-A2E9-2B83EC8917D4}" name="R5" dataDxfId="139">
+    <tableColumn id="15" xr3:uid="{42A7B19E-8A6C-4FA9-A2E9-2B83EC8917D4}" name="R5" dataDxfId="137">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!Q4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],Q$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C9AE28B0-4117-4A3D-8381-F7E9417F1616}" name="R6" dataDxfId="138">
+    <tableColumn id="16" xr3:uid="{C9AE28B0-4117-4A3D-8381-F7E9417F1616}" name="R6" dataDxfId="136">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!R4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],R$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{92A0B734-1347-429D-A2CB-8D857E4CD34E}" name="R7" dataDxfId="137">
+    <tableColumn id="17" xr3:uid="{92A0B734-1347-429D-A2CB-8D857E4CD34E}" name="R7" dataDxfId="135">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!S4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],S$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{667134D2-C221-4A4D-9FB1-909ACDC0DDB5}" name="R8" dataDxfId="136">
+    <tableColumn id="18" xr3:uid="{667134D2-C221-4A4D-9FB1-909ACDC0DDB5}" name="R8" dataDxfId="134">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!T4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],T$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{338C87EB-B9DD-49EE-9C5C-4BCE63EF4744}" name="R9" dataDxfId="135">
+    <tableColumn id="19" xr3:uid="{338C87EB-B9DD-49EE-9C5C-4BCE63EF4744}" name="R9" dataDxfId="133">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!U4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],U$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{6E3807F5-486A-4D01-9C7A-D8CBDABFB157}" name="D1" dataDxfId="134">
+    <tableColumn id="20" xr3:uid="{6E3807F5-486A-4D01-9C7A-D8CBDABFB157}" name="D1" dataDxfId="132">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!V4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7701,24 +7698,24 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}" name="tblPesosCoste" displayName="tblPesosCoste" ref="Y4:Z9" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}" name="tblPesosCoste" displayName="tblPesosCoste" ref="Y4:Z9" totalsRowShown="0" headerRowDxfId="131" dataDxfId="129" headerRowBorderDxfId="130" tableBorderDxfId="128">
   <autoFilter ref="Y4:Z9" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E1E6CBAC-71D7-49B4-97B4-D7CD1992E449}" name="Valor" dataDxfId="129"/>
-    <tableColumn id="4" xr3:uid="{5D97B706-55F4-46C7-B8B4-663F39805E8B}" name="Coste" dataDxfId="128"/>
+    <tableColumn id="1" xr3:uid="{E1E6CBAC-71D7-49B4-97B4-D7CD1992E449}" name="Valor" dataDxfId="127"/>
+    <tableColumn id="4" xr3:uid="{5D97B706-55F4-46C7-B8B4-663F39805E8B}" name="Coste" dataDxfId="126"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66EEA98C-81AE-44A3-B7B7-DDC02BD7FDF3}" name="tblRangoEnlace" displayName="tblRangoEnlace" ref="Y12:Z14" totalsRowShown="0" headerRowDxfId="127" headerRowBorderDxfId="126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66EEA98C-81AE-44A3-B7B7-DDC02BD7FDF3}" name="tblRangoEnlace" displayName="tblRangoEnlace" ref="Y12:Z14" totalsRowShown="0" headerRowDxfId="125" headerRowBorderDxfId="124">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{241E10B4-3B7B-4E19-92EA-AA4D53964641}" name="Rango del Enlace" dataDxfId="125"/>
-    <tableColumn id="2" xr3:uid="{20B4E6FB-3DB7-4113-AD20-5780FA4D1775}" name="Coste" dataDxfId="124"/>
+    <tableColumn id="1" xr3:uid="{241E10B4-3B7B-4E19-92EA-AA4D53964641}" name="Rango del Enlace" dataDxfId="123"/>
+    <tableColumn id="2" xr3:uid="{20B4E6FB-3DB7-4113-AD20-5780FA4D1775}" name="Coste" dataDxfId="122"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -8040,16 +8037,16 @@
     </row>
     <row r="4" spans="1:4" s="17" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>125</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8178,12 +8175,12 @@
     <row r="2" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="76" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C3" s="76"/>
       <c r="D3" s="70"/>
       <c r="E3" s="81" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F3" s="82"/>
       <c r="G3" s="82"/>
@@ -8198,10 +8195,10 @@
     </row>
     <row r="4" spans="2:15" s="17" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="62" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C4" s="62" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D4" s="70"/>
       <c r="E4" s="56" t="s">
@@ -8229,10 +8226,10 @@
         <v>19</v>
       </c>
       <c r="M4" s="64" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N4" s="64" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8240,17 +8237,17 @@
         <v>15</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D5" s="70"/>
       <c r="E5" s="58" t="s">
         <v>48</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H5" s="58" t="s">
         <v>27</v>
@@ -8268,10 +8265,10 @@
         <v>29</v>
       </c>
       <c r="M5" s="63" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="N5" s="63" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8279,17 +8276,17 @@
         <v>16</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D6" s="70"/>
       <c r="E6" s="58" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H6" s="58" t="s">
         <v>28</v>
@@ -8307,10 +8304,10 @@
         <v>28</v>
       </c>
       <c r="M6" s="58" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N6" s="58" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8318,17 +8315,17 @@
         <v>17</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D7" s="70"/>
       <c r="E7" s="58" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="F7" s="58" t="s">
-        <v>168</v>
-      </c>
       <c r="G7" s="58" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H7" s="58" t="s">
         <v>27</v>
@@ -8346,10 +8343,10 @@
         <v>29</v>
       </c>
       <c r="M7" s="58" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N7" s="58" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8357,17 +8354,17 @@
         <v>18</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D8" s="70"/>
       <c r="E8" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="F8" s="58" t="s">
-        <v>171</v>
-      </c>
       <c r="G8" s="58" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H8" s="58" t="s">
         <v>28</v>
@@ -8385,10 +8382,10 @@
         <v>29</v>
       </c>
       <c r="M8" s="58" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N8" s="58" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8396,16 +8393,16 @@
         <v>19</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H9" s="58" t="s">
         <v>28</v>
@@ -8423,10 +8420,10 @@
         <v>29</v>
       </c>
       <c r="M9" s="58" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N9" s="58" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8434,10 +8431,10 @@
         <v>53</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H10" s="58" t="s">
         <v>27</v>
@@ -8455,21 +8452,21 @@
         <v>28</v>
       </c>
       <c r="M10" s="58" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N10" s="58" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" s="58" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G11" s="58" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H11" s="58" t="s">
         <v>27</v>
@@ -8487,21 +8484,21 @@
         <v>28</v>
       </c>
       <c r="M11" s="58" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N11" s="58" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" s="58" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H12" s="58" t="s">
         <v>27</v>
@@ -8519,10 +8516,10 @@
         <v>28</v>
       </c>
       <c r="M12" s="58" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N12" s="58" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8530,10 +8527,10 @@
         <v>63</v>
       </c>
       <c r="F13" s="60" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G13" s="60" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H13" s="60" t="s">
         <v>27</v>
@@ -8551,10 +8548,10 @@
         <v>28</v>
       </c>
       <c r="M13" s="60" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N13" s="60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8796,7 +8793,7 @@
         <v>13</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>9</v>
@@ -8835,7 +8832,7 @@
         <v>99</v>
       </c>
       <c r="W4" s="29" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X4" s="16"/>
     </row>
@@ -8844,7 +8841,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -8859,7 +8856,7 @@
         <v>22</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>25</v>
@@ -8922,7 +8919,7 @@
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -8937,7 +8934,7 @@
         <v>30</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>25</v>
@@ -9001,7 +8998,7 @@
         <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -9016,13 +9013,13 @@
         <v>34</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -9080,7 +9077,7 @@
         <v>39</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -9095,13 +9092,13 @@
         <v>39</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
@@ -9159,7 +9156,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -9174,7 +9171,7 @@
         <v>43</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>25</v>
@@ -9238,7 +9235,7 @@
         <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -9253,7 +9250,7 @@
         <v>46</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>25</v>
@@ -9314,10 +9311,10 @@
     </row>
     <row r="11" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>117</v>
@@ -9329,16 +9326,16 @@
         <v>49</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
@@ -9393,10 +9390,10 @@
     </row>
     <row r="12" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>117</v>
@@ -9408,16 +9405,16 @@
         <v>51</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
@@ -9472,10 +9469,10 @@
     </row>
     <row r="13" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>117</v>
@@ -9487,16 +9484,16 @@
         <v>52</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
@@ -9551,10 +9548,10 @@
     </row>
     <row r="14" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>120</v>
@@ -9566,16 +9563,16 @@
         <v>54</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
@@ -9630,10 +9627,10 @@
     </row>
     <row r="15" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>120</v>
@@ -9645,16 +9642,16 @@
         <v>56</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
@@ -9709,10 +9706,10 @@
     </row>
     <row r="16" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>120</v>
@@ -9724,13 +9721,13 @@
         <v>58</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>53</v>
@@ -9788,10 +9785,10 @@
     </row>
     <row r="17" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>120</v>
@@ -9803,10 +9800,10 @@
         <v>60</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>25</v>
@@ -9867,10 +9864,10 @@
     </row>
     <row r="18" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>120</v>
@@ -9882,16 +9879,16 @@
         <v>62</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
@@ -9946,10 +9943,10 @@
     </row>
     <row r="19" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>120</v>
@@ -9961,16 +9958,16 @@
         <v>64</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
@@ -10025,10 +10022,10 @@
     </row>
     <row r="20" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>120</v>
@@ -10040,16 +10037,16 @@
         <v>66</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K20" s="1">
         <v>1</v>
@@ -10104,10 +10101,10 @@
     </row>
     <row r="21" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>120</v>
@@ -10119,16 +10116,16 @@
         <v>68</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
@@ -10183,10 +10180,10 @@
     </row>
     <row r="22" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>120</v>
@@ -10198,10 +10195,10 @@
         <v>70</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>25</v>
@@ -10262,10 +10259,10 @@
     </row>
     <row r="23" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>37</v>
@@ -10277,16 +10274,16 @@
         <v>71</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K23" s="1">
         <v>1</v>
@@ -10344,16 +10341,16 @@
         <v>72</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K24" s="1">
         <v>1</v>
@@ -10411,16 +10408,16 @@
         <v>73</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
@@ -10478,16 +10475,16 @@
         <v>74</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
@@ -10545,10 +10542,10 @@
         <v>75</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>25</v>
@@ -10612,16 +10609,16 @@
         <v>77</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K28" s="1">
         <v>1</v>
@@ -10679,13 +10676,13 @@
         <v>79</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>53</v>
@@ -10746,16 +10743,16 @@
         <v>81</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
@@ -10887,7 +10884,7 @@
   <sheetData>
     <row r="2" spans="2:27" s="14" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="87" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C2" s="88"/>
       <c r="D2" s="24" t="str">
@@ -10996,43 +10993,43 @@
         <v>46</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="O3" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="P3" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="T3" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="S3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="T3" s="5" t="s">
+      <c r="U3" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="U3" s="5" t="s">
-        <v>153</v>
-      </c>
       <c r="V3" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11551,7 +11548,7 @@
         <v>Colector local principal</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D10" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C10,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -11636,7 +11633,7 @@
         <v>Colector local secundario</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D11" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C11,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -11721,7 +11718,7 @@
         <v>Colector regional</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D12" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C12,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -11806,7 +11803,7 @@
         <v>Redistribuidor zona tránsito 1</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D13" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C13,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -11891,7 +11888,7 @@
         <v>Redistribuidor zona tránsito 2</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D14" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C14,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -11976,7 +11973,7 @@
         <v>Redistribuidor principal</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D15" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C15,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -12061,7 +12058,7 @@
         <v>Redistribuidor secundario 1</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D16" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C16,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -12146,7 +12143,7 @@
         <v>Redistribuidor secundario 2</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D17" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C17,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -12231,7 +12228,7 @@
         <v>Redistribuidor intermedio</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D18" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C18,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -12316,7 +12313,7 @@
         <v>Redistribuidor logístico</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D19" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C19,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -12401,7 +12398,7 @@
         <v>Redistribuidor financiero</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D20" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C20,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -12486,7 +12483,7 @@
         <v>Redistribuidor final</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D21" s="4">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C21,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -12571,7 +12568,7 @@
         <v>Destino operativo final</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D22" s="11">
         <f>IF(COUNTIFS(Red!$G$5:$G$30,$C22,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</f>
@@ -12845,43 +12842,43 @@
         <v>46</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="O3" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="P3" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="T3" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="S3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="T3" s="5" t="s">
+      <c r="U3" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="U3" s="5" t="s">
-        <v>153</v>
-      </c>
       <c r="V3" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Y3" s="90" t="s">
         <v>95</v>
@@ -13440,7 +13437,7 @@
         <v>Colector local principal</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D10" s="35">
         <f>IF(MatrizDeAdyacencia!D10=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C10,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -13527,7 +13524,7 @@
         <v>Colector local secundario</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D11" s="35">
         <f>IF(MatrizDeAdyacencia!D11=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C11,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -13617,7 +13614,7 @@
         <v>Colector regional</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D12" s="35">
         <f>IF(MatrizDeAdyacencia!D12=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C12,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -13708,7 +13705,7 @@
         <v>Redistribuidor zona tránsito 1</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D13" s="35">
         <f>IF(MatrizDeAdyacencia!D13=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C13,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -13800,7 +13797,7 @@
         <v>Redistribuidor zona tránsito 2</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D14" s="35">
         <f>IF(MatrizDeAdyacencia!D14=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C14,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -13892,7 +13889,7 @@
         <v>Redistribuidor principal</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D15" s="35">
         <f>IF(MatrizDeAdyacencia!D15=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C15,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -13977,7 +13974,7 @@
         <v>Redistribuidor secundario 1</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D16" s="35">
         <f>IF(MatrizDeAdyacencia!D16=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C16,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -14062,7 +14059,7 @@
         <v>Redistribuidor secundario 2</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D17" s="35">
         <f>IF(MatrizDeAdyacencia!D17=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C17,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -14147,7 +14144,7 @@
         <v>Redistribuidor intermedio</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D18" s="35">
         <f>IF(MatrizDeAdyacencia!D18=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C18,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -14232,7 +14229,7 @@
         <v>Redistribuidor logístico</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D19" s="35">
         <f>IF(MatrizDeAdyacencia!D19=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C19,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -14317,7 +14314,7 @@
         <v>Redistribuidor financiero</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D20" s="35">
         <f>IF(MatrizDeAdyacencia!D20=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C20,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -14402,7 +14399,7 @@
         <v>Redistribuidor final</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D21" s="35">
         <f>IF(MatrizDeAdyacencia!D21=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C21,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -14487,7 +14484,7 @@
         <v>Destino operativo final</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D22" s="37">
         <f>IF(MatrizDeAdyacencia!D22=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C22,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -14738,43 +14735,43 @@
         <v>46</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="O3" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="P3" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="T3" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="S3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="T3" s="5" t="s">
+      <c r="U3" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="U3" s="5" t="s">
-        <v>153</v>
-      </c>
       <c r="V3" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Y3" s="90" t="s">
         <v>86</v>
@@ -15474,7 +15471,7 @@
         <v>Colector local principal</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D10" s="35">
         <f>IF(MatrizDeAdyacencia!D10=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C10,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -15576,7 +15573,7 @@
         <v>Colector local secundario</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D11" s="35">
         <f>IF(MatrizDeAdyacencia!D11=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C11,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -15679,7 +15676,7 @@
         <v>Colector regional</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D12" s="35">
         <f>IF(MatrizDeAdyacencia!D12=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C12,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -15793,7 +15790,7 @@
         <v>Redistribuidor zona tránsito 1</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D13" s="35">
         <f>IF(MatrizDeAdyacencia!D13=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C13,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -15907,7 +15904,7 @@
         <v>Redistribuidor zona tránsito 2</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D14" s="35">
         <f>IF(MatrizDeAdyacencia!D14=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C14,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -16021,7 +16018,7 @@
         <v>Redistribuidor principal</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D15" s="35">
         <f>IF(MatrizDeAdyacencia!D15=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C15,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -16117,7 +16114,7 @@
         <v>Redistribuidor secundario 1</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D16" s="35">
         <f>IF(MatrizDeAdyacencia!D16=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C16,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -16213,7 +16210,7 @@
         <v>Redistribuidor secundario 2</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D17" s="35">
         <f>IF(MatrizDeAdyacencia!D17=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C17,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -16309,7 +16306,7 @@
         <v>Redistribuidor intermedio</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D18" s="35">
         <f>IF(MatrizDeAdyacencia!D18=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C18,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -16405,7 +16402,7 @@
         <v>Redistribuidor logístico</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D19" s="35">
         <f>IF(MatrizDeAdyacencia!D19=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C19,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -16501,7 +16498,7 @@
         <v>Redistribuidor financiero</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D20" s="35">
         <f>IF(MatrizDeAdyacencia!D20=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C20,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -16597,7 +16594,7 @@
         <v>Redistribuidor final</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D21" s="35">
         <f>IF(MatrizDeAdyacencia!D21=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C21,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>
@@ -16693,7 +16690,7 @@
         <v>Destino operativo final</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D22" s="37">
         <f>IF(MatrizDeAdyacencia!D22=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C22,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</f>

--- a/Diseño Red FT.xlsx
+++ b/Diseño Red FT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00_repositorios_GitHub\TFG-AFT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A988F7-F920-40DA-AE7B-121A40476E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7321010-FE53-4B87-9285-E09DFA339068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="211">
   <si>
     <t>GENERADOR DE MODELOS DE REDES SINTÉTICAS DE FINANCIACIÓN DEL TERRORISMO</t>
   </si>
@@ -791,6 +791,9 @@
   <si>
     <t>Notas</t>
   </si>
+  <si>
+    <t>Sirve para controlar en que "columna" del grafo se pintan este tipo de nodos</t>
+  </si>
 </sst>
 </file>
 
@@ -1301,7 +1304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1575,11 +1578,139 @@
     <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="247">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color theme="0" tint="-0.1498764000366222"/>
@@ -7009,131 +7140,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -7195,79 +7201,79 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B2FB235A-71F0-400E-A6F0-508799095DA1}" name="tblTiposDeNodo" displayName="tblTiposDeNodo" ref="A4:D8" headerRowDxfId="246" dataDxfId="245" totalsRowDxfId="244">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B2FB235A-71F0-400E-A6F0-508799095DA1}" name="tblTiposDeNodo" displayName="tblTiposDeNodo" ref="A4:D8" headerRowDxfId="7" dataDxfId="6" totalsRowDxfId="5">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2D998733-2F4E-407E-BB96-65EE8D671F3E}" name="Tipo" dataDxfId="243"/>
-    <tableColumn id="2" xr3:uid="{1D05F6E9-EB6D-4FA6-9F98-305486BA8372}" name="Descripción" dataDxfId="242"/>
-    <tableColumn id="4" xr3:uid="{969BC7E1-EE89-4897-8C40-9A8A992E41A8}" name="Capa" dataDxfId="241" totalsRowDxfId="240"/>
-    <tableColumn id="3" xr3:uid="{2A05B337-8674-440C-B5E6-EDF2D3E9C7EF}" name="Notas" dataDxfId="239"/>
+    <tableColumn id="1" xr3:uid="{2D998733-2F4E-407E-BB96-65EE8D671F3E}" name="Tipo" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{1D05F6E9-EB6D-4FA6-9F98-305486BA8372}" name="Descripción" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{969BC7E1-EE89-4897-8C40-9A8A992E41A8}" name="Capa" dataDxfId="1" totalsRowDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{2A05B337-8674-440C-B5E6-EDF2D3E9C7EF}" name="Notas" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C3763AE3-0C07-44F8-B723-CD50D544B597}" name="tblMatrizPonderadaValorOperativo" displayName="tblMatrizPonderadaValorOperativo" ref="B3:V22" totalsRowShown="0" headerRowDxfId="121" dataDxfId="119" headerRowBorderDxfId="120" tableBorderDxfId="118" totalsRowBorderDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C3763AE3-0C07-44F8-B723-CD50D544B597}" name="tblMatrizPonderadaValorOperativo" displayName="tblMatrizPonderadaValorOperativo" ref="B3:V22" totalsRowShown="0" headerRowDxfId="129" dataDxfId="127" headerRowBorderDxfId="128" tableBorderDxfId="126" totalsRowBorderDxfId="125">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{AB0E4632-ED12-49C5-876A-D0C45597103C}" name="Nombre Nodo" dataDxfId="116">
+    <tableColumn id="21" xr3:uid="{AB0E4632-ED12-49C5-876A-D0C45597103C}" name="Nombre Nodo" dataDxfId="124">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{1F5E2E88-3C78-4615-A934-EA38CE88F1DA}" name="NodoOrigen \ NodoDestino" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{7A66295D-CA43-492F-8775-35115F7A44EA}" name="O1" dataDxfId="114">
+    <tableColumn id="1" xr3:uid="{1F5E2E88-3C78-4615-A934-EA38CE88F1DA}" name="NodoOrigen \ NodoDestino" dataDxfId="123"/>
+    <tableColumn id="2" xr3:uid="{7A66295D-CA43-492F-8775-35115F7A44EA}" name="O1" dataDxfId="122">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!D4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B8A230F9-7293-4177-956A-4E8B8C3CDA07}" name="O2" dataDxfId="113">
+    <tableColumn id="3" xr3:uid="{B8A230F9-7293-4177-956A-4E8B8C3CDA07}" name="O2" dataDxfId="121">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!E4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],E$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{58464D2B-4CD6-441D-AB43-966A10F72197}" name="O3" dataDxfId="112">
+    <tableColumn id="4" xr3:uid="{58464D2B-4CD6-441D-AB43-966A10F72197}" name="O3" dataDxfId="120">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!F4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],F$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B54A5E25-CEE0-4DA6-8517-04ED3BBF73C6}" name="O4" dataDxfId="111">
+    <tableColumn id="5" xr3:uid="{B54A5E25-CEE0-4DA6-8517-04ED3BBF73C6}" name="O4" dataDxfId="119">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!G4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],G$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6A0BB34B-830D-4E04-B8C9-46624641D569}" name="O5" dataDxfId="110">
+    <tableColumn id="6" xr3:uid="{6A0BB34B-830D-4E04-B8C9-46624641D569}" name="O5" dataDxfId="118">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!H4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],H$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00DB80CE-0309-4FD9-950E-24D1DFDD9FFF}" name="O6" dataDxfId="109">
+    <tableColumn id="7" xr3:uid="{00DB80CE-0309-4FD9-950E-24D1DFDD9FFF}" name="O6" dataDxfId="117">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!I4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],I$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7AA5A8CA-1E8D-4093-864B-7D03F5756DC4}" name="C1" dataDxfId="108">
+    <tableColumn id="8" xr3:uid="{7AA5A8CA-1E8D-4093-864B-7D03F5756DC4}" name="C1" dataDxfId="116">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!J4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],J$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{03497B6C-E6A2-42BB-B97E-C56E12C9418F}" name="C2" dataDxfId="107">
+    <tableColumn id="9" xr3:uid="{03497B6C-E6A2-42BB-B97E-C56E12C9418F}" name="C2" dataDxfId="115">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!K4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],K$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{0FA96BFD-FC30-4C99-86C3-1B3F7728768B}" name="C3" dataDxfId="106">
+    <tableColumn id="10" xr3:uid="{0FA96BFD-FC30-4C99-86C3-1B3F7728768B}" name="C3" dataDxfId="114">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!L4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],L$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F3EDBB22-EAE5-496E-8608-9EED6CF8096A}" name="R1" dataDxfId="105">
+    <tableColumn id="11" xr3:uid="{F3EDBB22-EAE5-496E-8608-9EED6CF8096A}" name="R1" dataDxfId="113">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!M4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],M$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EE195140-EF30-4914-AEA7-9A979743FE44}" name="R2" dataDxfId="104">
+    <tableColumn id="12" xr3:uid="{EE195140-EF30-4914-AEA7-9A979743FE44}" name="R2" dataDxfId="112">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!N4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],N$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{940C992B-DC9E-4078-B43B-AD2A2ADF88AA}" name="R3" dataDxfId="103">
+    <tableColumn id="13" xr3:uid="{940C992B-DC9E-4078-B43B-AD2A2ADF88AA}" name="R3" dataDxfId="111">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!O4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],O$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{542FFF8E-DD7B-4C4C-9B1B-C885472540BA}" name="R4" dataDxfId="102">
+    <tableColumn id="14" xr3:uid="{542FFF8E-DD7B-4C4C-9B1B-C885472540BA}" name="R4" dataDxfId="110">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!P4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],P$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{054CF94A-1A1E-4D9F-8BA6-8813EF51323B}" name="R5" dataDxfId="101">
+    <tableColumn id="15" xr3:uid="{054CF94A-1A1E-4D9F-8BA6-8813EF51323B}" name="R5" dataDxfId="109">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!Q4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],Q$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{7ED93D8E-5836-4A3E-9935-FBC89CD3F932}" name="R6" dataDxfId="100">
+    <tableColumn id="16" xr3:uid="{7ED93D8E-5836-4A3E-9935-FBC89CD3F932}" name="R6" dataDxfId="108">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!R4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],R$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{164A5867-1655-4663-992A-899F25195899}" name="R7" dataDxfId="99">
+    <tableColumn id="17" xr3:uid="{164A5867-1655-4663-992A-899F25195899}" name="R7" dataDxfId="107">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!S4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],S$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{E33E9D43-CAE7-4043-AE20-D5AC6983C7DD}" name="R8" dataDxfId="98">
+    <tableColumn id="18" xr3:uid="{E33E9D43-CAE7-4043-AE20-D5AC6983C7DD}" name="R8" dataDxfId="106">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!T4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],T$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{5758BF82-052C-40CF-8505-1FBCD9CE2809}" name="R9" dataDxfId="97">
+    <tableColumn id="19" xr3:uid="{5758BF82-052C-40CF-8505-1FBCD9CE2809}" name="R9" dataDxfId="105">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!U4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],U$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{B734CB8C-660E-449E-8793-5B1787F00081}" name="D1" dataDxfId="96">
+    <tableColumn id="20" xr3:uid="{B734CB8C-660E-449E-8793-5B1787F00081}" name="D1" dataDxfId="104">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!V4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7276,94 +7282,94 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5D156EC0-C7DA-458D-93D7-E916A2987C0A}" name="tblPesosValorOperativo" displayName="tblPesosValorOperativo" ref="Y4:AC9" totalsRowShown="0" headerRowDxfId="95" dataDxfId="93" headerRowBorderDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5D156EC0-C7DA-458D-93D7-E916A2987C0A}" name="tblPesosValorOperativo" displayName="tblPesosValorOperativo" ref="Y4:AC9" totalsRowShown="0" headerRowDxfId="103" dataDxfId="101" headerRowBorderDxfId="102">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B21AD536-482D-4B9A-AB5E-37E015551681}" name="Valor" dataDxfId="92"/>
-    <tableColumn id="2" xr3:uid="{F200399A-6022-47BF-9665-7A71F541FDA5}" name="Eficiencia" dataDxfId="91"/>
-    <tableColumn id="3" xr3:uid="{FF663B4E-11C8-434F-A1B1-0562E8F7FB14}" name="Exposición" dataDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{D5B0977C-E15F-4467-A561-675FCAB097AB}" name="Capacidad" dataDxfId="89"/>
-    <tableColumn id="5" xr3:uid="{A82F60D0-C02D-4214-9AB5-F7EDAD97FCF6}" name="Resiliencia" dataDxfId="88"/>
+    <tableColumn id="1" xr3:uid="{B21AD536-482D-4B9A-AB5E-37E015551681}" name="Valor" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{F200399A-6022-47BF-9665-7A71F541FDA5}" name="Eficiencia" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{FF663B4E-11C8-434F-A1B1-0562E8F7FB14}" name="Exposición" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{D5B0977C-E15F-4467-A561-675FCAB097AB}" name="Capacidad" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{A82F60D0-C02D-4214-9AB5-F7EDAD97FCF6}" name="Resiliencia" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9318777C-0265-4E44-A0BA-CFC469B6C744}" name="tblRangoEnlace1ValorOpertivo" displayName="tblRangoEnlace1ValorOpertivo" ref="Y12:AD14" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9318777C-0265-4E44-A0BA-CFC469B6C744}" name="tblRangoEnlace1ValorOpertivo" displayName="tblRangoEnlace1ValorOpertivo" ref="Y12:AD14" totalsRowShown="0" headerRowDxfId="95" dataDxfId="93" headerRowBorderDxfId="94">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{753333F3-816E-431E-BB43-7A7927A7163F}" name="Rango del Enlace" dataDxfId="84"/>
-    <tableColumn id="2" xr3:uid="{72E9BB48-4FA1-4371-A282-0262F904FF9A}" name="Eficiencia" dataDxfId="83"/>
-    <tableColumn id="3" xr3:uid="{87F86AC7-35A2-437C-87BC-FB7CF221D935}" name="Exposición" dataDxfId="82"/>
-    <tableColumn id="4" xr3:uid="{3BA6459E-1C77-4D92-88F9-A4DA307EB1FF}" name="Capacidad" dataDxfId="81"/>
-    <tableColumn id="5" xr3:uid="{CED3CA81-A959-4820-A212-1AB6D2F76092}" name="Resiliencia" dataDxfId="80"/>
-    <tableColumn id="6" xr3:uid="{AFD0E7F4-AEB0-480B-BEDB-0D56FC9A258D}" name="Total" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{753333F3-816E-431E-BB43-7A7927A7163F}" name="Rango del Enlace" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{72E9BB48-4FA1-4371-A282-0262F904FF9A}" name="Eficiencia" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{87F86AC7-35A2-437C-87BC-FB7CF221D935}" name="Exposición" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{3BA6459E-1C77-4D92-88F9-A4DA307EB1FF}" name="Capacidad" dataDxfId="89"/>
+    <tableColumn id="5" xr3:uid="{CED3CA81-A959-4820-A212-1AB6D2F76092}" name="Resiliencia" dataDxfId="88"/>
+    <tableColumn id="6" xr3:uid="{AFD0E7F4-AEB0-480B-BEDB-0D56FC9A258D}" name="Total" dataDxfId="87"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DCB388D3-5907-4F27-B1F2-50F7C3CEFD03}" name="tblMatrizTradeOff" displayName="tblMatrizTradeOff" ref="B3:V22" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DCB388D3-5907-4F27-B1F2-50F7C3CEFD03}" name="tblMatrizTradeOff" displayName="tblMatrizTradeOff" ref="B3:V22" totalsRowShown="0" headerRowDxfId="86" dataDxfId="84" headerRowBorderDxfId="85" tableBorderDxfId="83" totalsRowBorderDxfId="82">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{AA1E6080-4E20-4F11-BF7D-BCF3B7198FDD}" name="Nombre Nodo" dataDxfId="73">
+    <tableColumn id="21" xr3:uid="{AA1E6080-4E20-4F11-BF7D-BCF3B7198FDD}" name="Nombre Nodo" dataDxfId="81">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{894C4500-CF7B-4D11-8AA7-3C7C1BD512C6}" name="NodoOrigen \ NodoDestino" dataDxfId="72"/>
-    <tableColumn id="2" xr3:uid="{9F705910-1DB5-40FC-A6DE-98805525ACF0}" name="O1" dataDxfId="71">
+    <tableColumn id="1" xr3:uid="{894C4500-CF7B-4D11-8AA7-3C7C1BD512C6}" name="NodoOrigen \ NodoDestino" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{9F705910-1DB5-40FC-A6DE-98805525ACF0}" name="O1" dataDxfId="79">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!D4=0,MatrizPonderadaValorOperativo!D4=0),0,MatrizPonderadaValorOperativo!D4/MatrizPonderadaCostes!D4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{50058AD6-7468-4AC7-97C5-05F954228EC1}" name="O2" dataDxfId="70">
+    <tableColumn id="3" xr3:uid="{50058AD6-7468-4AC7-97C5-05F954228EC1}" name="O2" dataDxfId="78">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!E4=0,MatrizPonderadaValorOperativo!E4=0),0,MatrizPonderadaValorOperativo!E4/MatrizPonderadaCostes!E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7C94D72A-7710-415D-86F3-659E59F93C96}" name="O3" dataDxfId="69">
+    <tableColumn id="4" xr3:uid="{7C94D72A-7710-415D-86F3-659E59F93C96}" name="O3" dataDxfId="77">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!F4=0,MatrizPonderadaValorOperativo!F4=0),0,MatrizPonderadaValorOperativo!F4/MatrizPonderadaCostes!F4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{532BA85E-D317-4F75-A439-3A5B03302C28}" name="O4" dataDxfId="68">
+    <tableColumn id="5" xr3:uid="{532BA85E-D317-4F75-A439-3A5B03302C28}" name="O4" dataDxfId="76">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!G4=0,MatrizPonderadaValorOperativo!G4=0),0,MatrizPonderadaValorOperativo!G4/MatrizPonderadaCostes!G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{063CA99D-B02A-474E-BF88-15CCC8190E67}" name="O5" dataDxfId="67">
+    <tableColumn id="6" xr3:uid="{063CA99D-B02A-474E-BF88-15CCC8190E67}" name="O5" dataDxfId="75">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!H4=0,MatrizPonderadaValorOperativo!H4=0),0,MatrizPonderadaValorOperativo!H4/MatrizPonderadaCostes!H4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{7BAB99D6-E0DD-44E8-812E-F31B042D5A8F}" name="O6" dataDxfId="66">
+    <tableColumn id="7" xr3:uid="{7BAB99D6-E0DD-44E8-812E-F31B042D5A8F}" name="O6" dataDxfId="74">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!I4=0,MatrizPonderadaValorOperativo!I4=0),0,MatrizPonderadaValorOperativo!I4/MatrizPonderadaCostes!I4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7A6532A5-C6A7-497A-9950-E4CF326FB1D0}" name="I1" dataDxfId="65">
+    <tableColumn id="8" xr3:uid="{7A6532A5-C6A7-497A-9950-E4CF326FB1D0}" name="I1" dataDxfId="73">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!J4=0,MatrizPonderadaValorOperativo!J4=0),0,MatrizPonderadaValorOperativo!J4/MatrizPonderadaCostes!J4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{7D782904-1F98-40F1-90DB-B287194DD5EC}" name="I2" dataDxfId="64">
+    <tableColumn id="9" xr3:uid="{7D782904-1F98-40F1-90DB-B287194DD5EC}" name="I2" dataDxfId="72">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!K4=0,MatrizPonderadaValorOperativo!K4=0),0,MatrizPonderadaValorOperativo!K4/MatrizPonderadaCostes!K4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F8DFA04B-3F58-4A4C-84F2-C08ECA18C8D0}" name="I3" dataDxfId="63">
+    <tableColumn id="10" xr3:uid="{F8DFA04B-3F58-4A4C-84F2-C08ECA18C8D0}" name="I3" dataDxfId="71">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!L4=0,MatrizPonderadaValorOperativo!L4=0),0,MatrizPonderadaValorOperativo!L4/MatrizPonderadaCostes!L4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{BEE1D8C4-0249-4AEB-85C7-3C1964171690}" name="I4" dataDxfId="62">
+    <tableColumn id="11" xr3:uid="{BEE1D8C4-0249-4AEB-85C7-3C1964171690}" name="I4" dataDxfId="70">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!M4=0,MatrizPonderadaValorOperativo!M4=0),0,MatrizPonderadaValorOperativo!M4/MatrizPonderadaCostes!M4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5E8D8652-5E54-4316-9F7E-FE077E7F3845}" name="I5" dataDxfId="61">
+    <tableColumn id="12" xr3:uid="{5E8D8652-5E54-4316-9F7E-FE077E7F3845}" name="I5" dataDxfId="69">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!N4=0,MatrizPonderadaValorOperativo!N4=0),0,MatrizPonderadaValorOperativo!N4/MatrizPonderadaCostes!N4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{19070E8B-9ED0-4B66-9707-071DEBF3C994}" name="I6" dataDxfId="60">
+    <tableColumn id="13" xr3:uid="{19070E8B-9ED0-4B66-9707-071DEBF3C994}" name="I6" dataDxfId="68">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!O4=0,MatrizPonderadaValorOperativo!O4=0),0,MatrizPonderadaValorOperativo!O4/MatrizPonderadaCostes!O4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{76F2DA9F-DAF7-439A-84BF-1733FA9657FD}" name="I7" dataDxfId="59">
+    <tableColumn id="14" xr3:uid="{76F2DA9F-DAF7-439A-84BF-1733FA9657FD}" name="I7" dataDxfId="67">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!P4=0,MatrizPonderadaValorOperativo!P4=0),0,MatrizPonderadaValorOperativo!P4/MatrizPonderadaCostes!P4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7D6FF674-D8C7-4CDC-B88A-E9A853759EB2}" name="I8" dataDxfId="58">
+    <tableColumn id="15" xr3:uid="{7D6FF674-D8C7-4CDC-B88A-E9A853759EB2}" name="I8" dataDxfId="66">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!Q4=0,MatrizPonderadaValorOperativo!Q4=0),0,MatrizPonderadaValorOperativo!Q4/MatrizPonderadaCostes!Q4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{4874BEF7-C26F-4D06-BE1E-88E85D5250AC}" name="I9" dataDxfId="57">
+    <tableColumn id="16" xr3:uid="{4874BEF7-C26F-4D06-BE1E-88E85D5250AC}" name="I9" dataDxfId="65">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!R4=0,MatrizPonderadaValorOperativo!R4=0),0,MatrizPonderadaValorOperativo!R4/MatrizPonderadaCostes!R4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{A372A997-A44F-44EB-AAED-77C0B6E13538}" name="G1" dataDxfId="56">
+    <tableColumn id="17" xr3:uid="{A372A997-A44F-44EB-AAED-77C0B6E13538}" name="G1" dataDxfId="64">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!S4=0,MatrizPonderadaValorOperativo!S4=0),0,MatrizPonderadaValorOperativo!S4/MatrizPonderadaCostes!S4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{0F8CF6FF-ABAA-4A01-AD38-A32A28F3744E}" name="G2" dataDxfId="55">
+    <tableColumn id="18" xr3:uid="{0F8CF6FF-ABAA-4A01-AD38-A32A28F3744E}" name="G2" dataDxfId="63">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!T4=0,MatrizPonderadaValorOperativo!T4=0),0,MatrizPonderadaValorOperativo!T4/MatrizPonderadaCostes!T4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{AB7C5AA0-D767-454C-BA7B-5A2B55F42FB8}" name="G3" dataDxfId="54">
+    <tableColumn id="19" xr3:uid="{AB7C5AA0-D767-454C-BA7B-5A2B55F42FB8}" name="G3" dataDxfId="62">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!U4=0,MatrizPonderadaValorOperativo!U4=0),0,MatrizPonderadaValorOperativo!U4/MatrizPonderadaCostes!U4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{23B65986-1386-4DD0-B9E1-CF1D12F9896F}" name="D" dataDxfId="53">
+    <tableColumn id="20" xr3:uid="{23B65986-1386-4DD0-B9E1-CF1D12F9896F}" name="D" dataDxfId="61">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!V4=0,MatrizPonderadaValorOperativo!V4=0),0,MatrizPonderadaValorOperativo!V4/MatrizPonderadaCostes!V4)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7372,67 +7378,67 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5873A7B6-81FB-4D79-A0FB-9D6FB64CE88D}" name="tblMatrizDistancias" displayName="tblMatrizDistancias" ref="X3:AR22" totalsRowShown="0" headerRowDxfId="52" dataDxfId="50" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5873A7B6-81FB-4D79-A0FB-9D6FB64CE88D}" name="tblMatrizDistancias" displayName="tblMatrizDistancias" ref="X3:AR22" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57" totalsRowBorderDxfId="56">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{1BAD8E49-23F7-4BE2-B973-AA604F8B446D}" name="Nombre Nodo" dataDxfId="47">
+    <tableColumn id="21" xr3:uid="{1BAD8E49-23F7-4BE2-B973-AA604F8B446D}" name="Nombre Nodo" dataDxfId="55">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{CCA43D7E-3A02-4B90-B8B1-A5C2C1770B89}" name="NodoOrigen \ NodoDestino" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{258A9219-735F-4D5E-96CD-61C2192DE988}" name="O1" dataDxfId="45">
+    <tableColumn id="1" xr3:uid="{CCA43D7E-3A02-4B90-B8B1-A5C2C1770B89}" name="NodoOrigen \ NodoDestino" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{258A9219-735F-4D5E-96CD-61C2192DE988}" name="O1" dataDxfId="53">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O1",0,IF(tblMatrizTradeOff[[#This Row],[O1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A742D52A-B21E-494D-9BEC-A3E5CC2D1787}" name="O2" dataDxfId="44">
+    <tableColumn id="3" xr3:uid="{A742D52A-B21E-494D-9BEC-A3E5CC2D1787}" name="O2" dataDxfId="52">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O2",0,IF(tblMatrizTradeOff[[#This Row],[O2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E3462037-DD10-4D8C-B6A1-5ADBA379FEB1}" name="O3" dataDxfId="43">
+    <tableColumn id="4" xr3:uid="{E3462037-DD10-4D8C-B6A1-5ADBA379FEB1}" name="O3" dataDxfId="51">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O3",0,IF(tblMatrizTradeOff[[#This Row],[O3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E48B988C-DC5A-4772-9E34-F71B68D92DCB}" name="O4" dataDxfId="42">
+    <tableColumn id="5" xr3:uid="{E48B988C-DC5A-4772-9E34-F71B68D92DCB}" name="O4" dataDxfId="50">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O4",0,IF(tblMatrizTradeOff[[#This Row],[O4]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O4]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{43CEAEF6-D25A-41BD-B40B-81780EA42997}" name="O5" dataDxfId="41">
+    <tableColumn id="6" xr3:uid="{43CEAEF6-D25A-41BD-B40B-81780EA42997}" name="O5" dataDxfId="49">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O5",0,IF(tblMatrizTradeOff[[#This Row],[O5]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O5]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3924F7A5-FD83-43F2-A080-29822934E0BE}" name="O6" dataDxfId="40">
+    <tableColumn id="7" xr3:uid="{3924F7A5-FD83-43F2-A080-29822934E0BE}" name="O6" dataDxfId="48">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O6",0,IF(tblMatrizTradeOff[[#This Row],[O6]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O6]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7547ECC7-C391-409A-A35D-75672D9B0DFF}" name="I1" dataDxfId="39">
+    <tableColumn id="8" xr3:uid="{7547ECC7-C391-409A-A35D-75672D9B0DFF}" name="I1" dataDxfId="47">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I1",0,IF(tblMatrizTradeOff[[#This Row],[I1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{10E4BD07-2311-4179-8574-4C902D93606E}" name="I2" dataDxfId="38">
+    <tableColumn id="9" xr3:uid="{10E4BD07-2311-4179-8574-4C902D93606E}" name="I2" dataDxfId="46">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I2",0,IF(tblMatrizTradeOff[[#This Row],[I2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C7634E23-202A-42C0-8E82-749F13342982}" name="I3" dataDxfId="37">
+    <tableColumn id="10" xr3:uid="{C7634E23-202A-42C0-8E82-749F13342982}" name="I3" dataDxfId="45">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I3",0,IF(tblMatrizTradeOff[[#This Row],[I3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{80F89DAB-DC38-4E1B-8C6E-ABAE0670FA4C}" name="I4" dataDxfId="36">
+    <tableColumn id="11" xr3:uid="{80F89DAB-DC38-4E1B-8C6E-ABAE0670FA4C}" name="I4" dataDxfId="44">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I4",0,IF(tblMatrizTradeOff[[#This Row],[I4]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I4]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{1690E7CA-C688-4A77-B2E4-78675EA5F6AF}" name="I5" dataDxfId="35">
+    <tableColumn id="12" xr3:uid="{1690E7CA-C688-4A77-B2E4-78675EA5F6AF}" name="I5" dataDxfId="43">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I5",0,IF(tblMatrizTradeOff[[#This Row],[I5]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I5]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{3A1E36E4-69D3-406F-91FA-CE9683D234A1}" name="I6" dataDxfId="34">
+    <tableColumn id="13" xr3:uid="{3A1E36E4-69D3-406F-91FA-CE9683D234A1}" name="I6" dataDxfId="42">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I6",0,IF(tblMatrizTradeOff[[#This Row],[I6]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I6]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{37A3FAD7-64EF-4C10-A216-8F4121D763FE}" name="I7" dataDxfId="33">
+    <tableColumn id="14" xr3:uid="{37A3FAD7-64EF-4C10-A216-8F4121D763FE}" name="I7" dataDxfId="41">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I7",0,IF(tblMatrizTradeOff[[#This Row],[I7]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I7]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{C79CE9F5-E392-4C54-A368-4072A211349B}" name="I8" dataDxfId="32">
+    <tableColumn id="15" xr3:uid="{C79CE9F5-E392-4C54-A368-4072A211349B}" name="I8" dataDxfId="40">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I8",0,IF(tblMatrizTradeOff[[#This Row],[I8]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I8]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{AF9AF109-E8FC-499B-B541-D049A2CD781D}" name="I9" dataDxfId="31">
+    <tableColumn id="16" xr3:uid="{AF9AF109-E8FC-499B-B541-D049A2CD781D}" name="I9" dataDxfId="39">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I9",0,IF(tblMatrizTradeOff[[#This Row],[I9]]=0,9999,1/tblMatrizTradeOff[[#This Row],[I9]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C49A9B94-D73C-40C2-9773-A0B40E4AAC62}" name="G1" dataDxfId="30">
+    <tableColumn id="17" xr3:uid="{C49A9B94-D73C-40C2-9773-A0B40E4AAC62}" name="G1" dataDxfId="38">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G1",0,IF(tblMatrizTradeOff[[#This Row],[G1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[G1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{37DF13C5-7088-4645-80B8-632B4668B1C6}" name="G2" dataDxfId="29">
+    <tableColumn id="18" xr3:uid="{37DF13C5-7088-4645-80B8-632B4668B1C6}" name="G2" dataDxfId="37">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G2",0,IF(tblMatrizTradeOff[[#This Row],[G2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[G2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{0C6F5759-0A04-44DB-ABD3-792D0DD2FD39}" name="G3" dataDxfId="28">
+    <tableColumn id="19" xr3:uid="{0C6F5759-0A04-44DB-ABD3-792D0DD2FD39}" name="G3" dataDxfId="36">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G3",0,IF(tblMatrizTradeOff[[#This Row],[G3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[G3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{08ECC6AD-B105-48DC-B6EF-5213E3FB7C76}" name="D" dataDxfId="27">
+    <tableColumn id="20" xr3:uid="{08ECC6AD-B105-48DC-B6EF-5213E3FB7C76}" name="D" dataDxfId="35">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="D",0,IF(tblMatrizTradeOff[[#This Row],[D]]=0,9999,1/tblMatrizTradeOff[[#This Row],[D]]))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7441,25 +7447,25 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7B2B6549-1979-4B25-A35A-52BA4A0A39EE}" name="tblGradoPonderado" displayName="tblGradoPonderado" ref="B3:H23" totalsRowCount="1" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7B2B6549-1979-4B25-A35A-52BA4A0A39EE}" name="tblGradoPonderado" displayName="tblGradoPonderado" ref="B3:H23" totalsRowCount="1" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31" totalsRowBorderDxfId="30">
   <tableColumns count="7">
-    <tableColumn id="21" xr3:uid="{77F6B8A9-151C-415D-A901-35466078EF18}" name="Nombre Nodo" totalsRowLabel="Totales / Máximos / Mínimos" dataDxfId="21" totalsRowDxfId="20">
+    <tableColumn id="21" xr3:uid="{77F6B8A9-151C-415D-A901-35466078EF18}" name="Nombre Nodo" totalsRowLabel="Totales / Máximos / Mínimos" dataDxfId="29" totalsRowDxfId="28">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{253666FE-A069-4260-AC52-8AE7DE9B8F38}" name="Nodo" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{AA42A750-6BE0-4870-A26E-410A2BC2C73B}" name="Grado Ponderado de Entrada" dataDxfId="17" totalsRowDxfId="16">
+    <tableColumn id="1" xr3:uid="{253666FE-A069-4260-AC52-8AE7DE9B8F38}" name="Nodo" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{AA42A750-6BE0-4870-A26E-410A2BC2C73B}" name="Grado Ponderado de Entrada" dataDxfId="25" totalsRowDxfId="24">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.n,tblGradoPonderado[[#This Row],[Nodo]],_xlpm.col,_xlfn.XLOOKUP(_xlpm.n,tblMatrizTradeOff[#Headers],tblMatrizTradeOff[#Data]),SUM(_xlpm.col))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{378B0278-AE86-49A4-8668-271111E0777E}" name="Grado Ponderado de Salida" dataDxfId="15" totalsRowDxfId="14">
+    <tableColumn id="3" xr3:uid="{378B0278-AE86-49A4-8668-271111E0777E}" name="Grado Ponderado de Salida" dataDxfId="23" totalsRowDxfId="22">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.n,tblGradoPonderado[[#This Row],[Nodo]],_xlpm.row,_xlfn.XLOOKUP(_xlpm.n,tblMatrizTradeOff[NodoOrigen \ NodoDestino],tblMatrizTradeOff[[O1]:[D]]),SUM(_xlpm.row))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3C52036B-2CF5-484C-8203-C94636D157F9}" name="Grado Ponderado Total" totalsRowFunction="max" dataDxfId="13" totalsRowDxfId="12">
+    <tableColumn id="4" xr3:uid="{3C52036B-2CF5-484C-8203-C94636D157F9}" name="Grado Ponderado Total" totalsRowFunction="max" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado de Entrada]]+tblGradoPonderado[[#This Row],[Grado Ponderado de Salida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FFBA1243-72FC-40D4-AE6E-AE5864D502FB}" name="Balance Neto" dataDxfId="11" totalsRowDxfId="10">
+    <tableColumn id="5" xr3:uid="{FFBA1243-72FC-40D4-AE6E-AE5864D502FB}" name="Balance Neto" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado de Salida]]-tblGradoPonderado[[#This Row],[Grado Ponderado de Entrada]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{94B10867-99D5-439C-B33C-5612EB83F5A4}" name="Grado Normalizado" dataDxfId="9" totalsRowDxfId="8">
+    <tableColumn id="6" xr3:uid="{94B10867-99D5-439C-B33C-5612EB83F5A4}" name="Grado Normalizado" dataDxfId="17" totalsRowDxfId="16">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado Total]]/tblGradoPonderado[[#Totals],[Grado Ponderado Total]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7468,77 +7474,77 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{684D43B5-10F8-42CD-A78F-0A2D7790FEBB}" name="tblPropiedadesCanales" displayName="tblPropiedadesCanales" ref="B4:C9" totalsRowShown="0" headerRowDxfId="238" dataDxfId="236" headerRowBorderDxfId="237" tableBorderDxfId="235">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{684D43B5-10F8-42CD-A78F-0A2D7790FEBB}" name="tblPropiedadesCanales" displayName="tblPropiedadesCanales" ref="B4:C9" totalsRowShown="0" headerRowDxfId="246" dataDxfId="244" headerRowBorderDxfId="245" tableBorderDxfId="243">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AE28D037-8200-4290-B185-521BE4E5D98F}" name="Variable" dataDxfId="234"/>
-    <tableColumn id="2" xr3:uid="{6EBF46F3-2102-4B98-9EA7-E0EC740C287C}" name="Definición recomendada" dataDxfId="233"/>
+    <tableColumn id="1" xr3:uid="{AE28D037-8200-4290-B185-521BE4E5D98F}" name="Variable" dataDxfId="242"/>
+    <tableColumn id="2" xr3:uid="{6EBF46F3-2102-4B98-9EA7-E0EC740C287C}" name="Definición recomendada" dataDxfId="241"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{A4F8E1C4-8F10-4A16-A363-66F29C756757}" name="tblCanales" displayName="tblCanales" ref="E4:N13" totalsRowShown="0" headerRowDxfId="232" dataDxfId="230" headerRowBorderDxfId="231" tableBorderDxfId="229" totalsRowBorderDxfId="228">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{A4F8E1C4-8F10-4A16-A363-66F29C756757}" name="tblCanales" displayName="tblCanales" ref="E4:N13" totalsRowShown="0" headerRowDxfId="240" dataDxfId="238" headerRowBorderDxfId="239" tableBorderDxfId="237" totalsRowBorderDxfId="236">
   <tableColumns count="10">
-    <tableColumn id="2" xr3:uid="{EC47E1C1-969B-40D7-A166-5065044FE8EE}" name="Nombre" dataDxfId="227"/>
-    <tableColumn id="4" xr3:uid="{C51CDB64-59EA-4881-B723-18B95E872D00}" name="Descripción" dataDxfId="226"/>
-    <tableColumn id="3" xr3:uid="{1CBE7731-79F9-40FF-82B5-B5E44A771838}" name="Tipo" dataDxfId="225"/>
-    <tableColumn id="5" xr3:uid="{E8249A44-897D-4018-B0CA-C983252BCFC8}" name="Coste" dataDxfId="224"/>
-    <tableColumn id="6" xr3:uid="{CE3CC37C-5B67-40F0-93BA-BA26DF959A93}" name="Eficiencia" dataDxfId="223"/>
-    <tableColumn id="7" xr3:uid="{C41E7A4D-CE1C-4D71-B522-398A7272A699}" name="Exposición" dataDxfId="222"/>
-    <tableColumn id="8" xr3:uid="{7AB4DB4D-AE68-4160-A03A-FCDB4E7546E5}" name="Capacidad" dataDxfId="221"/>
-    <tableColumn id="9" xr3:uid="{1354059D-8430-454F-87FD-5887F9F6B688}" name="Resiliencia" dataDxfId="220"/>
-    <tableColumn id="10" xr3:uid="{BC196392-856A-4221-9F76-9E4E7BC1F726}" name="GAFI" dataDxfId="219"/>
-    <tableColumn id="11" xr3:uid="{1CE9226F-8F31-4975-BF4A-078BB1C41195}" name="MODELO" dataDxfId="218"/>
+    <tableColumn id="2" xr3:uid="{EC47E1C1-969B-40D7-A166-5065044FE8EE}" name="Nombre" dataDxfId="235"/>
+    <tableColumn id="4" xr3:uid="{C51CDB64-59EA-4881-B723-18B95E872D00}" name="Descripción" dataDxfId="234"/>
+    <tableColumn id="3" xr3:uid="{1CBE7731-79F9-40FF-82B5-B5E44A771838}" name="Tipo" dataDxfId="233"/>
+    <tableColumn id="5" xr3:uid="{E8249A44-897D-4018-B0CA-C983252BCFC8}" name="Coste" dataDxfId="232"/>
+    <tableColumn id="6" xr3:uid="{CE3CC37C-5B67-40F0-93BA-BA26DF959A93}" name="Eficiencia" dataDxfId="231"/>
+    <tableColumn id="7" xr3:uid="{C41E7A4D-CE1C-4D71-B522-398A7272A699}" name="Exposición" dataDxfId="230"/>
+    <tableColumn id="8" xr3:uid="{7AB4DB4D-AE68-4160-A03A-FCDB4E7546E5}" name="Capacidad" dataDxfId="229"/>
+    <tableColumn id="9" xr3:uid="{1354059D-8430-454F-87FD-5887F9F6B688}" name="Resiliencia" dataDxfId="228"/>
+    <tableColumn id="10" xr3:uid="{BC196392-856A-4221-9F76-9E4E7BC1F726}" name="GAFI" dataDxfId="227"/>
+    <tableColumn id="11" xr3:uid="{1CE9226F-8F31-4975-BF4A-078BB1C41195}" name="MODELO" dataDxfId="226"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="F4:W30" headerRowDxfId="217" dataDxfId="216" totalsRowDxfId="215">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="F4:W30" headerRowDxfId="225" dataDxfId="224" totalsRowDxfId="223">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F5:Q30">
     <sortCondition ref="F4:F30"/>
   </sortState>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="214"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="213"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="212"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="211"/>
-    <tableColumn id="21" xr3:uid="{9EA0CAA5-0A23-473B-943E-3CC802BE75BA}" name="Canal" dataDxfId="210"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="209"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="208"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="207">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="222"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="221"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="220"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="219"/>
+    <tableColumn id="21" xr3:uid="{9EA0CAA5-0A23-473B-943E-3CC802BE75BA}" name="Canal" dataDxfId="218"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="217"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="216"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="215">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="206">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="214">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],5,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="205">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="213">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],6,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="204">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="212">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],7,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="203">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="211">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],8,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{D5ECEEAB-319C-416C-A120-BD842AFC8541}" name="Coste (peso)" dataDxfId="202" totalsRowDxfId="201">
+    <tableColumn id="23" xr3:uid="{D5ECEEAB-319C-416C-A120-BD842AFC8541}" name="Coste (peso)" dataDxfId="210" totalsRowDxfId="209">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesosCoste[Valor],tblPesosCoste[Coste],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{38505D25-3830-4BBB-8DCF-E8583124C910}" name="Eficiencia (peso)" dataDxfId="200" totalsRowDxfId="199">
+    <tableColumn id="24" xr3:uid="{38505D25-3830-4BBB-8DCF-E8583124C910}" name="Eficiencia (peso)" dataDxfId="208" totalsRowDxfId="207">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Eficiencia],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{8E52D89B-D169-4F48-AD66-44B1E56CB633}" name="Exposición (peso)" dataDxfId="198" totalsRowDxfId="197">
+    <tableColumn id="25" xr3:uid="{8E52D89B-D169-4F48-AD66-44B1E56CB633}" name="Exposición (peso)" dataDxfId="206" totalsRowDxfId="205">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Exposición],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{1F2413A4-A4B8-4902-8061-3A60A70F9F2F}" name="Capacidad (peso)" dataDxfId="196" totalsRowDxfId="195">
+    <tableColumn id="26" xr3:uid="{1F2413A4-A4B8-4902-8061-3A60A70F9F2F}" name="Capacidad (peso)" dataDxfId="204" totalsRowDxfId="203">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Capacidad],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{67FAA096-3D2B-4E91-9E1F-AEE59F7A690B}" name="Resiliencia (peso)" dataDxfId="194" totalsRowDxfId="193">
+    <tableColumn id="27" xr3:uid="{67FAA096-3D2B-4E91-9E1F-AEE59F7A690B}" name="Resiliencia (peso)" dataDxfId="202" totalsRowDxfId="201">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Resiliencia],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{378FBC0C-D6D1-4CC5-A688-4AE8E0EEFF15}" name="Valor Operativo (peso)" dataDxfId="192" totalsRowDxfId="191">
+    <tableColumn id="28" xr3:uid="{378FBC0C-D6D1-4CC5-A688-4AE8E0EEFF15}" name="Valor Operativo (peso)" dataDxfId="200" totalsRowDxfId="199">
       <calculatedColumnFormula>tblEnlaces[[#This Row],[Eficiencia (peso)]]+tblEnlaces[[#This Row],[Resiliencia (peso)]]+tblEnlaces[[#This Row],[Capacidad (peso)]]+tblEnlaces[[#This Row],[Exposición (peso)]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7547,80 +7553,80 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}" name="tblNodos" displayName="tblNodos" ref="A4:D23" headerRowDxfId="190" dataDxfId="189" totalsRowDxfId="188">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}" name="tblNodos" displayName="tblNodos" ref="A4:D23" headerRowDxfId="198" dataDxfId="197" totalsRowDxfId="196">
   <autoFilter ref="A4:D23" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C216D4B9-76C9-4611-A97A-027837B07F56}" name="NodoID" dataDxfId="187"/>
-    <tableColumn id="2" xr3:uid="{425384C0-D0A9-4E9A-A93C-65C1B3B77DB1}" name="Nombre" dataDxfId="186"/>
-    <tableColumn id="3" xr3:uid="{434558A9-CDA8-4827-AF85-9621517F0875}" name="Tipo" dataDxfId="185"/>
-    <tableColumn id="4" xr3:uid="{B0504143-65F8-445A-9B1A-9CA91BFF8129}" name="Activo" dataDxfId="184"/>
+    <tableColumn id="1" xr3:uid="{C216D4B9-76C9-4611-A97A-027837B07F56}" name="NodoID" dataDxfId="195"/>
+    <tableColumn id="2" xr3:uid="{425384C0-D0A9-4E9A-A93C-65C1B3B77DB1}" name="Nombre" dataDxfId="194"/>
+    <tableColumn id="3" xr3:uid="{434558A9-CDA8-4827-AF85-9621517F0875}" name="Tipo" dataDxfId="193"/>
+    <tableColumn id="4" xr3:uid="{B0504143-65F8-445A-9B1A-9CA91BFF8129}" name="Activo" dataDxfId="192"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="183" dataDxfId="181" headerRowBorderDxfId="182" tableBorderDxfId="180" totalsRowBorderDxfId="179">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="191" dataDxfId="189" headerRowBorderDxfId="190" tableBorderDxfId="188" totalsRowBorderDxfId="187">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="178">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="186">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="177"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="176">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="185"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="184">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="175">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="183">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,E$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="174">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="182">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,F$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="173">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="181">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,G$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="172">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="180">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,H$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="171">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="179">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,I$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="C1" dataDxfId="170">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="C1" dataDxfId="178">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,J$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="C2" dataDxfId="169">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="C2" dataDxfId="177">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,K$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="C3" dataDxfId="168">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="C3" dataDxfId="176">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,L$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="R1" dataDxfId="167">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="R1" dataDxfId="175">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,M$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="R2" dataDxfId="166">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="R2" dataDxfId="174">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,N$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="R3" dataDxfId="165">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="R3" dataDxfId="173">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,O$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="R4" dataDxfId="164">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="R4" dataDxfId="172">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,P$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="R5" dataDxfId="163">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="R5" dataDxfId="171">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,Q$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="R6" dataDxfId="162">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="R6" dataDxfId="170">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,R$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="R7" dataDxfId="161">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="R7" dataDxfId="169">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,S$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="R8" dataDxfId="160">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="R8" dataDxfId="168">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,T$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="R9" dataDxfId="159">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="R9" dataDxfId="167">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,U$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D1" dataDxfId="158">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D1" dataDxfId="166">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,V$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7629,67 +7635,67 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{619F938E-46CC-49F1-9A1F-6017755965D1}" name="tblMatrizPonderadaCostes" displayName="tblMatrizPonderadaCostes" ref="B3:V22" totalsRowShown="0" headerRowDxfId="157" dataDxfId="155" headerRowBorderDxfId="156" tableBorderDxfId="154" totalsRowBorderDxfId="153">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{619F938E-46CC-49F1-9A1F-6017755965D1}" name="tblMatrizPonderadaCostes" displayName="tblMatrizPonderadaCostes" ref="B3:V22" totalsRowShown="0" headerRowDxfId="165" dataDxfId="163" headerRowBorderDxfId="164" tableBorderDxfId="162" totalsRowBorderDxfId="161">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{2A9AC9D7-CC14-4058-8CF2-7CDFEC15F78F}" name="Nombre Nodo" dataDxfId="152">
+    <tableColumn id="21" xr3:uid="{2A9AC9D7-CC14-4058-8CF2-7CDFEC15F78F}" name="Nombre Nodo" dataDxfId="160">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{3A911174-7F39-43D0-8D1B-0D1A251C78CF}" name="NodoOrigen \ NodoDestino" dataDxfId="151"/>
-    <tableColumn id="2" xr3:uid="{79E6108F-3B54-4663-83BD-0E9A6288B0A8}" name="O1" dataDxfId="150">
+    <tableColumn id="1" xr3:uid="{3A911174-7F39-43D0-8D1B-0D1A251C78CF}" name="NodoOrigen \ NodoDestino" dataDxfId="159"/>
+    <tableColumn id="2" xr3:uid="{79E6108F-3B54-4663-83BD-0E9A6288B0A8}" name="O1" dataDxfId="158">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!D4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{74BBA163-10F6-4D74-863C-C4517633500F}" name="O2" dataDxfId="149">
+    <tableColumn id="3" xr3:uid="{74BBA163-10F6-4D74-863C-C4517633500F}" name="O2" dataDxfId="157">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!E4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],E$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5D6ADA5C-E165-41EC-803D-18F7A270611C}" name="O3" dataDxfId="148">
+    <tableColumn id="4" xr3:uid="{5D6ADA5C-E165-41EC-803D-18F7A270611C}" name="O3" dataDxfId="156">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!F4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],F$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{035B34FA-1623-4B86-B0EE-0CC6694FFD7C}" name="O4" dataDxfId="147">
+    <tableColumn id="5" xr3:uid="{035B34FA-1623-4B86-B0EE-0CC6694FFD7C}" name="O4" dataDxfId="155">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!G4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],G$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{27739639-E082-4698-9A4C-15EDA8612A83}" name="O5" dataDxfId="146">
+    <tableColumn id="6" xr3:uid="{27739639-E082-4698-9A4C-15EDA8612A83}" name="O5" dataDxfId="154">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!H4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],H$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{ED768978-7E7B-49CD-A202-FE8EBE9E64E0}" name="O6" dataDxfId="145">
+    <tableColumn id="7" xr3:uid="{ED768978-7E7B-49CD-A202-FE8EBE9E64E0}" name="O6" dataDxfId="153">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!I4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],I$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{37684012-4DC0-48DA-8E67-185403ABB81C}" name="C1" dataDxfId="144">
+    <tableColumn id="8" xr3:uid="{37684012-4DC0-48DA-8E67-185403ABB81C}" name="C1" dataDxfId="152">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!J4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],J$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E3684910-7769-4AEF-8800-33DC2F8D7ABC}" name="C2" dataDxfId="143">
+    <tableColumn id="9" xr3:uid="{E3684910-7769-4AEF-8800-33DC2F8D7ABC}" name="C2" dataDxfId="151">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!K4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],K$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A095B3C4-5019-4082-93A5-E12BDE733061}" name="C3" dataDxfId="142">
+    <tableColumn id="10" xr3:uid="{A095B3C4-5019-4082-93A5-E12BDE733061}" name="C3" dataDxfId="150">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!L4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],L$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{C5072B89-856A-4694-9D8B-17C4DB67DFF8}" name="R1" dataDxfId="141">
+    <tableColumn id="11" xr3:uid="{C5072B89-856A-4694-9D8B-17C4DB67DFF8}" name="R1" dataDxfId="149">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!M4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],M$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{0BD76649-1EE0-46D9-8718-F9A6F67BE379}" name="R2" dataDxfId="140">
+    <tableColumn id="12" xr3:uid="{0BD76649-1EE0-46D9-8718-F9A6F67BE379}" name="R2" dataDxfId="148">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!N4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],N$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{263255E9-BE7D-4E45-A463-5AD358998CB9}" name="R3" dataDxfId="139">
+    <tableColumn id="13" xr3:uid="{263255E9-BE7D-4E45-A463-5AD358998CB9}" name="R3" dataDxfId="147">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!O4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],O$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{7AF510BB-CB1B-461F-8746-C7133DC25996}" name="R4" dataDxfId="138">
+    <tableColumn id="14" xr3:uid="{7AF510BB-CB1B-461F-8746-C7133DC25996}" name="R4" dataDxfId="146">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!P4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],P$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{42A7B19E-8A6C-4FA9-A2E9-2B83EC8917D4}" name="R5" dataDxfId="137">
+    <tableColumn id="15" xr3:uid="{42A7B19E-8A6C-4FA9-A2E9-2B83EC8917D4}" name="R5" dataDxfId="145">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!Q4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],Q$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C9AE28B0-4117-4A3D-8381-F7E9417F1616}" name="R6" dataDxfId="136">
+    <tableColumn id="16" xr3:uid="{C9AE28B0-4117-4A3D-8381-F7E9417F1616}" name="R6" dataDxfId="144">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!R4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],R$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{92A0B734-1347-429D-A2CB-8D857E4CD34E}" name="R7" dataDxfId="135">
+    <tableColumn id="17" xr3:uid="{92A0B734-1347-429D-A2CB-8D857E4CD34E}" name="R7" dataDxfId="143">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!S4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],S$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{667134D2-C221-4A4D-9FB1-909ACDC0DDB5}" name="R8" dataDxfId="134">
+    <tableColumn id="18" xr3:uid="{667134D2-C221-4A4D-9FB1-909ACDC0DDB5}" name="R8" dataDxfId="142">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!T4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],T$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{338C87EB-B9DD-49EE-9C5C-4BCE63EF4744}" name="R9" dataDxfId="133">
+    <tableColumn id="19" xr3:uid="{338C87EB-B9DD-49EE-9C5C-4BCE63EF4744}" name="R9" dataDxfId="141">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!U4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],U$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{6E3807F5-486A-4D01-9C7A-D8CBDABFB157}" name="D1" dataDxfId="132">
+    <tableColumn id="20" xr3:uid="{6E3807F5-486A-4D01-9C7A-D8CBDABFB157}" name="D1" dataDxfId="140">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!V4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7698,24 +7704,24 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}" name="tblPesosCoste" displayName="tblPesosCoste" ref="Y4:Z9" totalsRowShown="0" headerRowDxfId="131" dataDxfId="129" headerRowBorderDxfId="130" tableBorderDxfId="128">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}" name="tblPesosCoste" displayName="tblPesosCoste" ref="Y4:Z9" totalsRowShown="0" headerRowDxfId="139" dataDxfId="137" headerRowBorderDxfId="138" tableBorderDxfId="136">
   <autoFilter ref="Y4:Z9" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E1E6CBAC-71D7-49B4-97B4-D7CD1992E449}" name="Valor" dataDxfId="127"/>
-    <tableColumn id="4" xr3:uid="{5D97B706-55F4-46C7-B8B4-663F39805E8B}" name="Coste" dataDxfId="126"/>
+    <tableColumn id="1" xr3:uid="{E1E6CBAC-71D7-49B4-97B4-D7CD1992E449}" name="Valor" dataDxfId="135"/>
+    <tableColumn id="4" xr3:uid="{5D97B706-55F4-46C7-B8B4-663F39805E8B}" name="Coste" dataDxfId="134"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66EEA98C-81AE-44A3-B7B7-DDC02BD7FDF3}" name="tblRangoEnlace" displayName="tblRangoEnlace" ref="Y12:Z14" totalsRowShown="0" headerRowDxfId="125" headerRowBorderDxfId="124">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66EEA98C-81AE-44A3-B7B7-DDC02BD7FDF3}" name="tblRangoEnlace" displayName="tblRangoEnlace" ref="Y12:Z14" totalsRowShown="0" headerRowDxfId="133" headerRowBorderDxfId="132">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{241E10B4-3B7B-4E19-92EA-AA4D53964641}" name="Rango del Enlace" dataDxfId="123"/>
-    <tableColumn id="2" xr3:uid="{20B4E6FB-3DB7-4113-AD20-5780FA4D1775}" name="Coste" dataDxfId="122"/>
+    <tableColumn id="1" xr3:uid="{241E10B4-3B7B-4E19-92EA-AA4D53964641}" name="Rango del Enlace" dataDxfId="131"/>
+    <tableColumn id="2" xr3:uid="{20B4E6FB-3DB7-4113-AD20-5780FA4D1775}" name="Coste" dataDxfId="130"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -8105,7 +8111,11 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:4" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="93" t="s">
+        <v>210</v>
+      </c>
+    </row>
     <row r="10" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12702,10 +12712,10 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:V22">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14580,7 +14590,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16786,7 +16796,7 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:I4 L4:V4 D5:V22">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16813,7 +16823,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28019,7 +28029,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="66" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28032,7 +28042,7 @@
         <color rgb="FFFCFCFF"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>9999</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36690,7 +36700,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="64" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Diseño Red FT.xlsx
+++ b/Diseño Red FT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00_repositorios_GitHub\TFG-AFT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1210E307-E2AF-4CA6-B8FD-3E0B9F1DA6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63601883-7EA0-455F-A750-70304A3BF5EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base-Nodos" sheetId="10" r:id="rId1"/>
@@ -1484,6 +1484,15 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1524,12 +1533,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1539,418 +1542,11 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="247">
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1" tint="0.34998626667073579"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1" tint="0.34998626667073579"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1" tint="0.34998626667073579"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1" tint="0.34998626667073579"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1" tint="0.34998626667073579"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <color theme="0" tint="-0.1498764000366222"/>
@@ -2017,6 +1613,424 @@
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
         <right style="thin">
           <color rgb="FFD9D9D9"/>
         </right>
@@ -2184,6 +2198,40 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color rgb="FFD9D9D9"/>
@@ -2851,658 +2899,25 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
+        <sz val="8"/>
+        <color theme="1" tint="0.34998626667073579"/>
         <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
+      <border>
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
@@ -4521,6 +3936,40 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color rgb="FFD9D9D9"/>
@@ -5351,6 +4800,40 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -7101,6 +6584,523 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -7162,79 +7162,79 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B2FB235A-71F0-400E-A6F0-508799095DA1}" name="tblTiposDeNodo" displayName="tblTiposDeNodo" ref="A4:D8" headerRowDxfId="246" dataDxfId="245" totalsRowDxfId="244">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B2FB235A-71F0-400E-A6F0-508799095DA1}" name="tblTiposDeNodo" displayName="tblTiposDeNodo" ref="A4:D8" headerRowDxfId="227" dataDxfId="226" totalsRowDxfId="225">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2D998733-2F4E-407E-BB96-65EE8D671F3E}" name="Tipo" dataDxfId="243"/>
-    <tableColumn id="2" xr3:uid="{1D05F6E9-EB6D-4FA6-9F98-305486BA8372}" name="Descripción" dataDxfId="242"/>
-    <tableColumn id="4" xr3:uid="{969BC7E1-EE89-4897-8C40-9A8A992E41A8}" name="Capa" dataDxfId="241" totalsRowDxfId="240"/>
-    <tableColumn id="3" xr3:uid="{2A05B337-8674-440C-B5E6-EDF2D3E9C7EF}" name="Notas" dataDxfId="239"/>
+    <tableColumn id="1" xr3:uid="{2D998733-2F4E-407E-BB96-65EE8D671F3E}" name="Tipo" dataDxfId="224"/>
+    <tableColumn id="2" xr3:uid="{1D05F6E9-EB6D-4FA6-9F98-305486BA8372}" name="Descripción" dataDxfId="223"/>
+    <tableColumn id="4" xr3:uid="{969BC7E1-EE89-4897-8C40-9A8A992E41A8}" name="Capa" dataDxfId="222" totalsRowDxfId="221"/>
+    <tableColumn id="3" xr3:uid="{2A05B337-8674-440C-B5E6-EDF2D3E9C7EF}" name="Notas" dataDxfId="220"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C3763AE3-0C07-44F8-B723-CD50D544B597}" name="tblMatrizPonderadaValorOperativo" displayName="tblMatrizPonderadaValorOperativo" ref="B3:V22" totalsRowShown="0" headerRowDxfId="122" dataDxfId="120" headerRowBorderDxfId="121" tableBorderDxfId="119" totalsRowBorderDxfId="118">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C3763AE3-0C07-44F8-B723-CD50D544B597}" name="tblMatrizPonderadaValorOperativo" displayName="tblMatrizPonderadaValorOperativo" ref="B3:V22" totalsRowShown="0" headerRowDxfId="102" dataDxfId="100" headerRowBorderDxfId="101" tableBorderDxfId="99" totalsRowBorderDxfId="98">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{AB0E4632-ED12-49C5-876A-D0C45597103C}" name="Nombre Nodo" dataDxfId="10">
+    <tableColumn id="21" xr3:uid="{AB0E4632-ED12-49C5-876A-D0C45597103C}" name="Nombre Nodo" dataDxfId="97">
       <calculatedColumnFormula>VLOOKUP(tblMatrizPonderadaValorOperativo[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{1F5E2E88-3C78-4615-A934-EA38CE88F1DA}" name="NodoOrigen \ NodoDestino" dataDxfId="117"/>
-    <tableColumn id="2" xr3:uid="{7A66295D-CA43-492F-8775-35115F7A44EA}" name="O1" dataDxfId="116">
+    <tableColumn id="1" xr3:uid="{1F5E2E88-3C78-4615-A934-EA38CE88F1DA}" name="NodoOrigen \ NodoDestino" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{7A66295D-CA43-492F-8775-35115F7A44EA}" name="O1" dataDxfId="95">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!D4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B8A230F9-7293-4177-956A-4E8B8C3CDA07}" name="O2" dataDxfId="115">
+    <tableColumn id="3" xr3:uid="{B8A230F9-7293-4177-956A-4E8B8C3CDA07}" name="O2" dataDxfId="94">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!E4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],E$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{58464D2B-4CD6-441D-AB43-966A10F72197}" name="O3" dataDxfId="114">
+    <tableColumn id="4" xr3:uid="{58464D2B-4CD6-441D-AB43-966A10F72197}" name="O3" dataDxfId="93">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!F4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],F$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B54A5E25-CEE0-4DA6-8517-04ED3BBF73C6}" name="O4" dataDxfId="113">
+    <tableColumn id="5" xr3:uid="{B54A5E25-CEE0-4DA6-8517-04ED3BBF73C6}" name="O4" dataDxfId="92">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!G4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],G$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6A0BB34B-830D-4E04-B8C9-46624641D569}" name="O5" dataDxfId="112">
+    <tableColumn id="6" xr3:uid="{6A0BB34B-830D-4E04-B8C9-46624641D569}" name="O5" dataDxfId="91">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!H4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],H$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00DB80CE-0309-4FD9-950E-24D1DFDD9FFF}" name="O6" dataDxfId="111">
+    <tableColumn id="7" xr3:uid="{00DB80CE-0309-4FD9-950E-24D1DFDD9FFF}" name="O6" dataDxfId="90">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!I4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],I$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7AA5A8CA-1E8D-4093-864B-7D03F5756DC4}" name="C1" dataDxfId="110">
+    <tableColumn id="8" xr3:uid="{7AA5A8CA-1E8D-4093-864B-7D03F5756DC4}" name="C1" dataDxfId="89">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!J4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],J$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{03497B6C-E6A2-42BB-B97E-C56E12C9418F}" name="C2" dataDxfId="109">
+    <tableColumn id="9" xr3:uid="{03497B6C-E6A2-42BB-B97E-C56E12C9418F}" name="C2" dataDxfId="88">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!K4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],K$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{0FA96BFD-FC30-4C99-86C3-1B3F7728768B}" name="C3" dataDxfId="108">
+    <tableColumn id="10" xr3:uid="{0FA96BFD-FC30-4C99-86C3-1B3F7728768B}" name="C3" dataDxfId="87">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!L4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],L$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F3EDBB22-EAE5-496E-8608-9EED6CF8096A}" name="R1" dataDxfId="107">
+    <tableColumn id="11" xr3:uid="{F3EDBB22-EAE5-496E-8608-9EED6CF8096A}" name="R1" dataDxfId="86">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!M4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],M$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EE195140-EF30-4914-AEA7-9A979743FE44}" name="R2" dataDxfId="106">
+    <tableColumn id="12" xr3:uid="{EE195140-EF30-4914-AEA7-9A979743FE44}" name="R2" dataDxfId="85">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!N4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],N$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{940C992B-DC9E-4078-B43B-AD2A2ADF88AA}" name="R3" dataDxfId="105">
+    <tableColumn id="13" xr3:uid="{940C992B-DC9E-4078-B43B-AD2A2ADF88AA}" name="R3" dataDxfId="84">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!O4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],O$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{542FFF8E-DD7B-4C4C-9B1B-C885472540BA}" name="R4" dataDxfId="104">
+    <tableColumn id="14" xr3:uid="{542FFF8E-DD7B-4C4C-9B1B-C885472540BA}" name="R4" dataDxfId="83">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!P4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],P$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{054CF94A-1A1E-4D9F-8BA6-8813EF51323B}" name="R5" dataDxfId="103">
+    <tableColumn id="15" xr3:uid="{054CF94A-1A1E-4D9F-8BA6-8813EF51323B}" name="R5" dataDxfId="82">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!Q4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],Q$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{7ED93D8E-5836-4A3E-9935-FBC89CD3F932}" name="R6" dataDxfId="102">
+    <tableColumn id="16" xr3:uid="{7ED93D8E-5836-4A3E-9935-FBC89CD3F932}" name="R6" dataDxfId="81">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!R4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],R$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{164A5867-1655-4663-992A-899F25195899}" name="R7" dataDxfId="101">
+    <tableColumn id="17" xr3:uid="{164A5867-1655-4663-992A-899F25195899}" name="R7" dataDxfId="80">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!S4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],S$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{E33E9D43-CAE7-4043-AE20-D5AC6983C7DD}" name="R8" dataDxfId="100">
+    <tableColumn id="18" xr3:uid="{E33E9D43-CAE7-4043-AE20-D5AC6983C7DD}" name="R8" dataDxfId="79">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!T4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],T$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{5758BF82-052C-40CF-8505-1FBCD9CE2809}" name="R9" dataDxfId="99">
+    <tableColumn id="19" xr3:uid="{5758BF82-052C-40CF-8505-1FBCD9CE2809}" name="R9" dataDxfId="78">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!U4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],U$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{B734CB8C-660E-449E-8793-5B1787F00081}" name="D1" dataDxfId="98">
+    <tableColumn id="20" xr3:uid="{B734CB8C-660E-449E-8793-5B1787F00081}" name="D1" dataDxfId="77">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!V4=1,SUMIFS(tblEnlaces[Valor Operativo (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7243,94 +7243,94 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5D156EC0-C7DA-458D-93D7-E916A2987C0A}" name="tblPesosValorOperativo" displayName="tblPesosValorOperativo" ref="Y4:AC9" totalsRowShown="0" headerRowDxfId="97" dataDxfId="95" headerRowBorderDxfId="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5D156EC0-C7DA-458D-93D7-E916A2987C0A}" name="tblPesosValorOperativo" displayName="tblPesosValorOperativo" ref="Y4:AC9" totalsRowShown="0" headerRowDxfId="76" dataDxfId="74" headerRowBorderDxfId="75">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B21AD536-482D-4B9A-AB5E-37E015551681}" name="Valor" dataDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{F200399A-6022-47BF-9665-7A71F541FDA5}" name="Eficiencia" dataDxfId="93"/>
-    <tableColumn id="3" xr3:uid="{FF663B4E-11C8-434F-A1B1-0562E8F7FB14}" name="Exposición" dataDxfId="92"/>
-    <tableColumn id="4" xr3:uid="{D5B0977C-E15F-4467-A561-675FCAB097AB}" name="Capacidad" dataDxfId="91"/>
-    <tableColumn id="5" xr3:uid="{A82F60D0-C02D-4214-9AB5-F7EDAD97FCF6}" name="Resiliencia" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{B21AD536-482D-4B9A-AB5E-37E015551681}" name="Valor" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{F200399A-6022-47BF-9665-7A71F541FDA5}" name="Eficiencia" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{FF663B4E-11C8-434F-A1B1-0562E8F7FB14}" name="Exposición" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{D5B0977C-E15F-4467-A561-675FCAB097AB}" name="Capacidad" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{A82F60D0-C02D-4214-9AB5-F7EDAD97FCF6}" name="Resiliencia" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9318777C-0265-4E44-A0BA-CFC469B6C744}" name="tblRangoEnlace1ValorOpertivo" displayName="tblRangoEnlace1ValorOpertivo" ref="Y12:AD14" totalsRowShown="0" headerRowDxfId="89" dataDxfId="87" headerRowBorderDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9318777C-0265-4E44-A0BA-CFC469B6C744}" name="tblRangoEnlace1ValorOpertivo" displayName="tblRangoEnlace1ValorOpertivo" ref="Y12:AD14" totalsRowShown="0" headerRowDxfId="68" dataDxfId="66" headerRowBorderDxfId="67">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{753333F3-816E-431E-BB43-7A7927A7163F}" name="Rango del Enlace" dataDxfId="86"/>
-    <tableColumn id="2" xr3:uid="{72E9BB48-4FA1-4371-A282-0262F904FF9A}" name="Eficiencia" dataDxfId="85"/>
-    <tableColumn id="3" xr3:uid="{87F86AC7-35A2-437C-87BC-FB7CF221D935}" name="Exposición" dataDxfId="84"/>
-    <tableColumn id="4" xr3:uid="{3BA6459E-1C77-4D92-88F9-A4DA307EB1FF}" name="Capacidad" dataDxfId="83"/>
-    <tableColumn id="5" xr3:uid="{CED3CA81-A959-4820-A212-1AB6D2F76092}" name="Resiliencia" dataDxfId="82"/>
-    <tableColumn id="6" xr3:uid="{AFD0E7F4-AEB0-480B-BEDB-0D56FC9A258D}" name="Total" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{753333F3-816E-431E-BB43-7A7927A7163F}" name="Rango del Enlace" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{72E9BB48-4FA1-4371-A282-0262F904FF9A}" name="Eficiencia" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{87F86AC7-35A2-437C-87BC-FB7CF221D935}" name="Exposición" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{3BA6459E-1C77-4D92-88F9-A4DA307EB1FF}" name="Capacidad" dataDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{CED3CA81-A959-4820-A212-1AB6D2F76092}" name="Resiliencia" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{AFD0E7F4-AEB0-480B-BEDB-0D56FC9A258D}" name="Total" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DCB388D3-5907-4F27-B1F2-50F7C3CEFD03}" name="tblMatrizTradeOff" displayName="tblMatrizTradeOff" ref="B3:V22" totalsRowShown="0" headerRowDxfId="80" dataDxfId="78" headerRowBorderDxfId="79" tableBorderDxfId="77" totalsRowBorderDxfId="76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DCB388D3-5907-4F27-B1F2-50F7C3CEFD03}" name="tblMatrizTradeOff" displayName="tblMatrizTradeOff" ref="B3:V22" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{AA1E6080-4E20-4F11-BF7D-BCF3B7198FDD}" name="Nombre Nodo" dataDxfId="9">
+    <tableColumn id="21" xr3:uid="{AA1E6080-4E20-4F11-BF7D-BCF3B7198FDD}" name="Nombre Nodo" dataDxfId="54">
       <calculatedColumnFormula>VLOOKUP(tblMatrizTradeOff[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{894C4500-CF7B-4D11-8AA7-3C7C1BD512C6}" name="NodoOrigen \ NodoDestino" dataDxfId="75"/>
-    <tableColumn id="2" xr3:uid="{9F705910-1DB5-40FC-A6DE-98805525ACF0}" name="O1" dataDxfId="74">
+    <tableColumn id="1" xr3:uid="{894C4500-CF7B-4D11-8AA7-3C7C1BD512C6}" name="NodoOrigen \ NodoDestino" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{9F705910-1DB5-40FC-A6DE-98805525ACF0}" name="O1" dataDxfId="52">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!D4=0,MatrizPonderadaValorOperativo!D4=0),0,MatrizPonderadaValorOperativo!D4/MatrizPonderadaCostes!D4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{50058AD6-7468-4AC7-97C5-05F954228EC1}" name="O2" dataDxfId="73">
+    <tableColumn id="3" xr3:uid="{50058AD6-7468-4AC7-97C5-05F954228EC1}" name="O2" dataDxfId="51">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!E4=0,MatrizPonderadaValorOperativo!E4=0),0,MatrizPonderadaValorOperativo!E4/MatrizPonderadaCostes!E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7C94D72A-7710-415D-86F3-659E59F93C96}" name="O3" dataDxfId="72">
+    <tableColumn id="4" xr3:uid="{7C94D72A-7710-415D-86F3-659E59F93C96}" name="O3" dataDxfId="50">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!F4=0,MatrizPonderadaValorOperativo!F4=0),0,MatrizPonderadaValorOperativo!F4/MatrizPonderadaCostes!F4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{532BA85E-D317-4F75-A439-3A5B03302C28}" name="O4" dataDxfId="71">
+    <tableColumn id="5" xr3:uid="{532BA85E-D317-4F75-A439-3A5B03302C28}" name="O4" dataDxfId="49">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!G4=0,MatrizPonderadaValorOperativo!G4=0),0,MatrizPonderadaValorOperativo!G4/MatrizPonderadaCostes!G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{063CA99D-B02A-474E-BF88-15CCC8190E67}" name="O5" dataDxfId="70">
+    <tableColumn id="6" xr3:uid="{063CA99D-B02A-474E-BF88-15CCC8190E67}" name="O5" dataDxfId="48">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!H4=0,MatrizPonderadaValorOperativo!H4=0),0,MatrizPonderadaValorOperativo!H4/MatrizPonderadaCostes!H4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{7BAB99D6-E0DD-44E8-812E-F31B042D5A8F}" name="O6" dataDxfId="69">
+    <tableColumn id="7" xr3:uid="{7BAB99D6-E0DD-44E8-812E-F31B042D5A8F}" name="O6" dataDxfId="47">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!I4=0,MatrizPonderadaValorOperativo!I4=0),0,MatrizPonderadaValorOperativo!I4/MatrizPonderadaCostes!I4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7A6532A5-C6A7-497A-9950-E4CF326FB1D0}" name="C1" dataDxfId="68">
+    <tableColumn id="8" xr3:uid="{7A6532A5-C6A7-497A-9950-E4CF326FB1D0}" name="C1" dataDxfId="46">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!J4=0,MatrizPonderadaValorOperativo!J4=0),0,MatrizPonderadaValorOperativo!J4/MatrizPonderadaCostes!J4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{7D782904-1F98-40F1-90DB-B287194DD5EC}" name="C2" dataDxfId="67">
+    <tableColumn id="9" xr3:uid="{7D782904-1F98-40F1-90DB-B287194DD5EC}" name="C2" dataDxfId="45">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!K4=0,MatrizPonderadaValorOperativo!K4=0),0,MatrizPonderadaValorOperativo!K4/MatrizPonderadaCostes!K4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F8DFA04B-3F58-4A4C-84F2-C08ECA18C8D0}" name="C3" dataDxfId="66">
+    <tableColumn id="10" xr3:uid="{F8DFA04B-3F58-4A4C-84F2-C08ECA18C8D0}" name="C3" dataDxfId="44">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!L4=0,MatrizPonderadaValorOperativo!L4=0),0,MatrizPonderadaValorOperativo!L4/MatrizPonderadaCostes!L4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{BEE1D8C4-0249-4AEB-85C7-3C1964171690}" name="R1" dataDxfId="65">
+    <tableColumn id="11" xr3:uid="{BEE1D8C4-0249-4AEB-85C7-3C1964171690}" name="R1" dataDxfId="43">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!M4=0,MatrizPonderadaValorOperativo!M4=0),0,MatrizPonderadaValorOperativo!M4/MatrizPonderadaCostes!M4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5E8D8652-5E54-4316-9F7E-FE077E7F3845}" name="R2" dataDxfId="64">
+    <tableColumn id="12" xr3:uid="{5E8D8652-5E54-4316-9F7E-FE077E7F3845}" name="R2" dataDxfId="42">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!N4=0,MatrizPonderadaValorOperativo!N4=0),0,MatrizPonderadaValorOperativo!N4/MatrizPonderadaCostes!N4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{19070E8B-9ED0-4B66-9707-071DEBF3C994}" name="R3" dataDxfId="63">
+    <tableColumn id="13" xr3:uid="{19070E8B-9ED0-4B66-9707-071DEBF3C994}" name="R3" dataDxfId="41">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!O4=0,MatrizPonderadaValorOperativo!O4=0),0,MatrizPonderadaValorOperativo!O4/MatrizPonderadaCostes!O4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{76F2DA9F-DAF7-439A-84BF-1733FA9657FD}" name="R4" dataDxfId="62">
+    <tableColumn id="14" xr3:uid="{76F2DA9F-DAF7-439A-84BF-1733FA9657FD}" name="R4" dataDxfId="40">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!P4=0,MatrizPonderadaValorOperativo!P4=0),0,MatrizPonderadaValorOperativo!P4/MatrizPonderadaCostes!P4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7D6FF674-D8C7-4CDC-B88A-E9A853759EB2}" name="R5" dataDxfId="61">
+    <tableColumn id="15" xr3:uid="{7D6FF674-D8C7-4CDC-B88A-E9A853759EB2}" name="R5" dataDxfId="39">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!Q4=0,MatrizPonderadaValorOperativo!Q4=0),0,MatrizPonderadaValorOperativo!Q4/MatrizPonderadaCostes!Q4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{4874BEF7-C26F-4D06-BE1E-88E85D5250AC}" name="R6" dataDxfId="60">
+    <tableColumn id="16" xr3:uid="{4874BEF7-C26F-4D06-BE1E-88E85D5250AC}" name="R6" dataDxfId="38">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!R4=0,MatrizPonderadaValorOperativo!R4=0),0,MatrizPonderadaValorOperativo!R4/MatrizPonderadaCostes!R4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{A372A997-A44F-44EB-AAED-77C0B6E13538}" name="R7" dataDxfId="59">
+    <tableColumn id="17" xr3:uid="{A372A997-A44F-44EB-AAED-77C0B6E13538}" name="R7" dataDxfId="37">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!S4=0,MatrizPonderadaValorOperativo!S4=0),0,MatrizPonderadaValorOperativo!S4/MatrizPonderadaCostes!S4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{0F8CF6FF-ABAA-4A01-AD38-A32A28F3744E}" name="R8" dataDxfId="58">
+    <tableColumn id="18" xr3:uid="{0F8CF6FF-ABAA-4A01-AD38-A32A28F3744E}" name="R8" dataDxfId="36">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!T4=0,MatrizPonderadaValorOperativo!T4=0),0,MatrizPonderadaValorOperativo!T4/MatrizPonderadaCostes!T4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{AB7C5AA0-D767-454C-BA7B-5A2B55F42FB8}" name="R9" dataDxfId="57">
+    <tableColumn id="19" xr3:uid="{AB7C5AA0-D767-454C-BA7B-5A2B55F42FB8}" name="R9" dataDxfId="35">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!U4=0,MatrizPonderadaValorOperativo!U4=0),0,MatrizPonderadaValorOperativo!U4/MatrizPonderadaCostes!U4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{23B65986-1386-4DD0-B9E1-CF1D12F9896F}" name="D1" dataDxfId="56">
+    <tableColumn id="20" xr3:uid="{23B65986-1386-4DD0-B9E1-CF1D12F9896F}" name="D1" dataDxfId="34">
       <calculatedColumnFormula>IF(OR(MatrizPonderadaCostes!V4=0,MatrizPonderadaValorOperativo!V4=0),0,MatrizPonderadaValorOperativo!V4/MatrizPonderadaCostes!V4)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7339,67 +7339,67 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5873A7B6-81FB-4D79-A0FB-9D6FB64CE88D}" name="tblMatrizDistancias" displayName="tblMatrizDistancias" ref="X3:AR22" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5873A7B6-81FB-4D79-A0FB-9D6FB64CE88D}" name="tblMatrizDistancias" displayName="tblMatrizDistancias" ref="X3:AR22" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{1BAD8E49-23F7-4BE2-B973-AA604F8B446D}" name="Nombre Nodo" dataDxfId="8">
+    <tableColumn id="21" xr3:uid="{1BAD8E49-23F7-4BE2-B973-AA604F8B446D}" name="Nombre Nodo" dataDxfId="28">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{CCA43D7E-3A02-4B90-B8B1-A5C2C1770B89}" name="NodoOrigen \ NodoDestino" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{258A9219-735F-4D5E-96CD-61C2192DE988}" name="O1" dataDxfId="49">
+    <tableColumn id="1" xr3:uid="{CCA43D7E-3A02-4B90-B8B1-A5C2C1770B89}" name="NodoOrigen \ NodoDestino" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{258A9219-735F-4D5E-96CD-61C2192DE988}" name="O1" dataDxfId="26">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O1",0,IF(tblMatrizTradeOff[[#This Row],[O1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A742D52A-B21E-494D-9BEC-A3E5CC2D1787}" name="O2" dataDxfId="48">
+    <tableColumn id="3" xr3:uid="{A742D52A-B21E-494D-9BEC-A3E5CC2D1787}" name="O2" dataDxfId="25">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O2",0,IF(tblMatrizTradeOff[[#This Row],[O2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E3462037-DD10-4D8C-B6A1-5ADBA379FEB1}" name="O3" dataDxfId="47">
+    <tableColumn id="4" xr3:uid="{E3462037-DD10-4D8C-B6A1-5ADBA379FEB1}" name="O3" dataDxfId="24">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O3",0,IF(tblMatrizTradeOff[[#This Row],[O3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E48B988C-DC5A-4772-9E34-F71B68D92DCB}" name="O4" dataDxfId="46">
+    <tableColumn id="5" xr3:uid="{E48B988C-DC5A-4772-9E34-F71B68D92DCB}" name="O4" dataDxfId="23">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O4",0,IF(tblMatrizTradeOff[[#This Row],[O4]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O4]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{43CEAEF6-D25A-41BD-B40B-81780EA42997}" name="O5" dataDxfId="45">
+    <tableColumn id="6" xr3:uid="{43CEAEF6-D25A-41BD-B40B-81780EA42997}" name="O5" dataDxfId="22">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O5",0,IF(tblMatrizTradeOff[[#This Row],[O5]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O5]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3924F7A5-FD83-43F2-A080-29822934E0BE}" name="O6" dataDxfId="44">
+    <tableColumn id="7" xr3:uid="{3924F7A5-FD83-43F2-A080-29822934E0BE}" name="O6" dataDxfId="21">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="O6",0,IF(tblMatrizTradeOff[[#This Row],[O6]]=0,9999,1/tblMatrizTradeOff[[#This Row],[O6]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7547ECC7-C391-409A-A35D-75672D9B0DFF}" name="C1" dataDxfId="43">
+    <tableColumn id="8" xr3:uid="{7547ECC7-C391-409A-A35D-75672D9B0DFF}" name="C1" dataDxfId="20">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I1",0,IF(tblMatrizTradeOff[[#This Row],[C1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[C1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{10E4BD07-2311-4179-8574-4C902D93606E}" name="C2" dataDxfId="42">
+    <tableColumn id="9" xr3:uid="{10E4BD07-2311-4179-8574-4C902D93606E}" name="C2" dataDxfId="19">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I2",0,IF(tblMatrizTradeOff[[#This Row],[C2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[C2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C7634E23-202A-42C0-8E82-749F13342982}" name="C3" dataDxfId="41">
+    <tableColumn id="10" xr3:uid="{C7634E23-202A-42C0-8E82-749F13342982}" name="C3" dataDxfId="18">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I3",0,IF(tblMatrizTradeOff[[#This Row],[C3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[C3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{80F89DAB-DC38-4E1B-8C6E-ABAE0670FA4C}" name="R1" dataDxfId="40">
+    <tableColumn id="11" xr3:uid="{80F89DAB-DC38-4E1B-8C6E-ABAE0670FA4C}" name="R1" dataDxfId="17">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I4",0,IF(tblMatrizTradeOff[[#This Row],[R1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[R1]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{1690E7CA-C688-4A77-B2E4-78675EA5F6AF}" name="R2" dataDxfId="39">
+    <tableColumn id="12" xr3:uid="{1690E7CA-C688-4A77-B2E4-78675EA5F6AF}" name="R2" dataDxfId="16">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I5",0,IF(tblMatrizTradeOff[[#This Row],[R2]]=0,9999,1/tblMatrizTradeOff[[#This Row],[R2]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{3A1E36E4-69D3-406F-91FA-CE9683D234A1}" name="R3" dataDxfId="38">
+    <tableColumn id="13" xr3:uid="{3A1E36E4-69D3-406F-91FA-CE9683D234A1}" name="R3" dataDxfId="15">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I6",0,IF(tblMatrizTradeOff[[#This Row],[R3]]=0,9999,1/tblMatrizTradeOff[[#This Row],[R3]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{37A3FAD7-64EF-4C10-A216-8F4121D763FE}" name="R4" dataDxfId="37">
+    <tableColumn id="14" xr3:uid="{37A3FAD7-64EF-4C10-A216-8F4121D763FE}" name="R4" dataDxfId="14">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I7",0,IF(tblMatrizTradeOff[[#This Row],[R4]]=0,9999,1/tblMatrizTradeOff[[#This Row],[R4]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{C79CE9F5-E392-4C54-A368-4072A211349B}" name="R5" dataDxfId="36">
+    <tableColumn id="15" xr3:uid="{C79CE9F5-E392-4C54-A368-4072A211349B}" name="R5" dataDxfId="13">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I8",0,IF(tblMatrizTradeOff[[#This Row],[R5]]=0,9999,1/tblMatrizTradeOff[[#This Row],[R5]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{AF9AF109-E8FC-499B-B541-D049A2CD781D}" name="R6" dataDxfId="35">
+    <tableColumn id="16" xr3:uid="{AF9AF109-E8FC-499B-B541-D049A2CD781D}" name="R6" dataDxfId="12">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="I9",0,IF(tblMatrizTradeOff[[#This Row],[R6]]=0,9999,1/tblMatrizTradeOff[[#This Row],[R6]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C49A9B94-D73C-40C2-9773-A0B40E4AAC62}" name="R7" dataDxfId="34">
+    <tableColumn id="17" xr3:uid="{C49A9B94-D73C-40C2-9773-A0B40E4AAC62}" name="R7" dataDxfId="11">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G1",0,IF(tblMatrizTradeOff[[#This Row],[R7]]=0,9999,1/tblMatrizTradeOff[[#This Row],[R7]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{37DF13C5-7088-4645-80B8-632B4668B1C6}" name="R8" dataDxfId="33">
+    <tableColumn id="18" xr3:uid="{37DF13C5-7088-4645-80B8-632B4668B1C6}" name="R8" dataDxfId="10">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G2",0,IF(tblMatrizTradeOff[[#This Row],[R8]]=0,9999,1/tblMatrizTradeOff[[#This Row],[R8]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{0C6F5759-0A04-44DB-ABD3-792D0DD2FD39}" name="R9" dataDxfId="32">
+    <tableColumn id="19" xr3:uid="{0C6F5759-0A04-44DB-ABD3-792D0DD2FD39}" name="R9" dataDxfId="9">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="G3",0,IF(tblMatrizTradeOff[[#This Row],[R9]]=0,9999,1/tblMatrizTradeOff[[#This Row],[R9]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{08ECC6AD-B105-48DC-B6EF-5213E3FB7C76}" name="D1" dataDxfId="31">
+    <tableColumn id="20" xr3:uid="{08ECC6AD-B105-48DC-B6EF-5213E3FB7C76}" name="D1" dataDxfId="8">
       <calculatedColumnFormula>IF(tblMatrizDistancias[[#This Row],[NodoOrigen \ NodoDestino]]="D",0,IF(tblMatrizTradeOff[[#This Row],[D1]]=0,9999,1/tblMatrizTradeOff[[#This Row],[D1]]))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7408,25 +7408,25 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7B2B6549-1979-4B25-A35A-52BA4A0A39EE}" name="tblGradoPonderado" displayName="tblGradoPonderado" ref="B3:H23" totalsRowCount="1" headerRowDxfId="30" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27" totalsRowBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7B2B6549-1979-4B25-A35A-52BA4A0A39EE}" name="tblGradoPonderado" displayName="tblGradoPonderado" ref="B3:H23" totalsRowCount="1" headerRowDxfId="246" dataDxfId="244" headerRowBorderDxfId="245" tableBorderDxfId="243" totalsRowBorderDxfId="242">
   <tableColumns count="7">
-    <tableColumn id="21" xr3:uid="{77F6B8A9-151C-415D-A901-35466078EF18}" name="Nombre Nodo" totalsRowLabel="Totales / Máximos / Mínimos" dataDxfId="0" totalsRowDxfId="7">
+    <tableColumn id="21" xr3:uid="{77F6B8A9-151C-415D-A901-35466078EF18}" name="Nombre Nodo" totalsRowLabel="Totales / Máximos / Mínimos" dataDxfId="241" totalsRowDxfId="240">
       <calculatedColumnFormula>VLOOKUP(tblGradoPonderado[[#This Row],[Nodo]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{253666FE-A069-4260-AC52-8AE7DE9B8F38}" name="Nodo" dataDxfId="25" totalsRowDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{AA42A750-6BE0-4870-A26E-410A2BC2C73B}" name="Grado Ponderado de Entrada" dataDxfId="24" totalsRowDxfId="5">
+    <tableColumn id="1" xr3:uid="{253666FE-A069-4260-AC52-8AE7DE9B8F38}" name="Nodo" dataDxfId="239" totalsRowDxfId="238"/>
+    <tableColumn id="2" xr3:uid="{AA42A750-6BE0-4870-A26E-410A2BC2C73B}" name="Grado Ponderado de Entrada" dataDxfId="237" totalsRowDxfId="236">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.n,tblGradoPonderado[[#This Row],[Nodo]],_xlpm.col,_xlfn.XLOOKUP(_xlpm.n,tblMatrizTradeOff[#Headers],tblMatrizTradeOff[#Data]),SUM(_xlpm.col))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{378B0278-AE86-49A4-8668-271111E0777E}" name="Grado Ponderado de Salida" dataDxfId="23" totalsRowDxfId="4">
+    <tableColumn id="3" xr3:uid="{378B0278-AE86-49A4-8668-271111E0777E}" name="Grado Ponderado de Salida" dataDxfId="235" totalsRowDxfId="234">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.n,tblGradoPonderado[[#This Row],[Nodo]],_xlpm.row,_xlfn.XLOOKUP(_xlpm.n,tblMatrizTradeOff[NodoOrigen \ NodoDestino],tblMatrizTradeOff[[O1]:[D1]]),SUM(_xlpm.row))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3C52036B-2CF5-484C-8203-C94636D157F9}" name="Grado Ponderado Total" totalsRowFunction="max" dataDxfId="22" totalsRowDxfId="3">
+    <tableColumn id="4" xr3:uid="{3C52036B-2CF5-484C-8203-C94636D157F9}" name="Grado Ponderado Total" totalsRowFunction="max" dataDxfId="233" totalsRowDxfId="232">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado de Entrada]]+tblGradoPonderado[[#This Row],[Grado Ponderado de Salida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FFBA1243-72FC-40D4-AE6E-AE5864D502FB}" name="Balance Neto" dataDxfId="21" totalsRowDxfId="2">
+    <tableColumn id="5" xr3:uid="{FFBA1243-72FC-40D4-AE6E-AE5864D502FB}" name="Balance Neto" dataDxfId="231" totalsRowDxfId="230">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado de Salida]]-tblGradoPonderado[[#This Row],[Grado Ponderado de Entrada]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{94B10867-99D5-439C-B33C-5612EB83F5A4}" name="Grado Normalizado" dataDxfId="20" totalsRowDxfId="1">
+    <tableColumn id="6" xr3:uid="{94B10867-99D5-439C-B33C-5612EB83F5A4}" name="Grado Normalizado" dataDxfId="229" totalsRowDxfId="228">
       <calculatedColumnFormula>tblGradoPonderado[[#This Row],[Grado Ponderado Total]]/tblGradoPonderado[[#Totals],[Grado Ponderado Total]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7435,77 +7435,77 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{684D43B5-10F8-42CD-A78F-0A2D7790FEBB}" name="tblPropiedadesCanales" displayName="tblPropiedadesCanales" ref="B4:C9" totalsRowShown="0" headerRowDxfId="238" dataDxfId="236" headerRowBorderDxfId="237" tableBorderDxfId="235">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{684D43B5-10F8-42CD-A78F-0A2D7790FEBB}" name="tblPropiedadesCanales" displayName="tblPropiedadesCanales" ref="B4:C9" totalsRowShown="0" headerRowDxfId="219" dataDxfId="217" headerRowBorderDxfId="218" tableBorderDxfId="216">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AE28D037-8200-4290-B185-521BE4E5D98F}" name="Variable" dataDxfId="234"/>
-    <tableColumn id="2" xr3:uid="{6EBF46F3-2102-4B98-9EA7-E0EC740C287C}" name="Definición recomendada" dataDxfId="233"/>
+    <tableColumn id="1" xr3:uid="{AE28D037-8200-4290-B185-521BE4E5D98F}" name="Variable" dataDxfId="215"/>
+    <tableColumn id="2" xr3:uid="{6EBF46F3-2102-4B98-9EA7-E0EC740C287C}" name="Definición recomendada" dataDxfId="214"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{A4F8E1C4-8F10-4A16-A363-66F29C756757}" name="tblCanales" displayName="tblCanales" ref="E4:N13" totalsRowShown="0" headerRowDxfId="232" dataDxfId="230" headerRowBorderDxfId="231" tableBorderDxfId="229" totalsRowBorderDxfId="228">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{A4F8E1C4-8F10-4A16-A363-66F29C756757}" name="tblCanales" displayName="tblCanales" ref="E4:N13" totalsRowShown="0" headerRowDxfId="213" dataDxfId="211" headerRowBorderDxfId="212" tableBorderDxfId="210" totalsRowBorderDxfId="209">
   <tableColumns count="10">
-    <tableColumn id="2" xr3:uid="{EC47E1C1-969B-40D7-A166-5065044FE8EE}" name="Nombre" dataDxfId="227"/>
-    <tableColumn id="4" xr3:uid="{C51CDB64-59EA-4881-B723-18B95E872D00}" name="Descripción" dataDxfId="226"/>
-    <tableColumn id="3" xr3:uid="{1CBE7731-79F9-40FF-82B5-B5E44A771838}" name="Tipo" dataDxfId="225"/>
-    <tableColumn id="5" xr3:uid="{E8249A44-897D-4018-B0CA-C983252BCFC8}" name="Coste" dataDxfId="224"/>
-    <tableColumn id="6" xr3:uid="{CE3CC37C-5B67-40F0-93BA-BA26DF959A93}" name="Eficiencia" dataDxfId="223"/>
-    <tableColumn id="7" xr3:uid="{C41E7A4D-CE1C-4D71-B522-398A7272A699}" name="Exposición" dataDxfId="222"/>
-    <tableColumn id="8" xr3:uid="{7AB4DB4D-AE68-4160-A03A-FCDB4E7546E5}" name="Capacidad" dataDxfId="221"/>
-    <tableColumn id="9" xr3:uid="{1354059D-8430-454F-87FD-5887F9F6B688}" name="Resiliencia" dataDxfId="220"/>
-    <tableColumn id="10" xr3:uid="{BC196392-856A-4221-9F76-9E4E7BC1F726}" name="GAFI" dataDxfId="219"/>
-    <tableColumn id="11" xr3:uid="{1CE9226F-8F31-4975-BF4A-078BB1C41195}" name="MODELO" dataDxfId="218"/>
+    <tableColumn id="2" xr3:uid="{EC47E1C1-969B-40D7-A166-5065044FE8EE}" name="Nombre" dataDxfId="208"/>
+    <tableColumn id="4" xr3:uid="{C51CDB64-59EA-4881-B723-18B95E872D00}" name="Descripción" dataDxfId="207"/>
+    <tableColumn id="3" xr3:uid="{1CBE7731-79F9-40FF-82B5-B5E44A771838}" name="Tipo" dataDxfId="206"/>
+    <tableColumn id="5" xr3:uid="{E8249A44-897D-4018-B0CA-C983252BCFC8}" name="Coste" dataDxfId="205"/>
+    <tableColumn id="6" xr3:uid="{CE3CC37C-5B67-40F0-93BA-BA26DF959A93}" name="Eficiencia" dataDxfId="204"/>
+    <tableColumn id="7" xr3:uid="{C41E7A4D-CE1C-4D71-B522-398A7272A699}" name="Exposición" dataDxfId="203"/>
+    <tableColumn id="8" xr3:uid="{7AB4DB4D-AE68-4160-A03A-FCDB4E7546E5}" name="Capacidad" dataDxfId="202"/>
+    <tableColumn id="9" xr3:uid="{1354059D-8430-454F-87FD-5887F9F6B688}" name="Resiliencia" dataDxfId="201"/>
+    <tableColumn id="10" xr3:uid="{BC196392-856A-4221-9F76-9E4E7BC1F726}" name="GAFI" dataDxfId="200"/>
+    <tableColumn id="11" xr3:uid="{1CE9226F-8F31-4975-BF4A-078BB1C41195}" name="MODELO" dataDxfId="199"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="F4:W30" headerRowDxfId="217" dataDxfId="216" totalsRowDxfId="215">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblEnlaces" displayName="tblEnlaces" ref="F4:W30" headerRowDxfId="198" dataDxfId="197" totalsRowDxfId="196">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F5:Q30">
     <sortCondition ref="F4:F30"/>
   </sortState>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="214"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="213"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="212"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="211"/>
-    <tableColumn id="21" xr3:uid="{9EA0CAA5-0A23-473B-943E-3CC802BE75BA}" name="Canal" dataDxfId="210"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="209"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="208"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="207">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="EdgeID" dataDxfId="195"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nodo Origen" dataDxfId="194"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Nodo Destino" dataDxfId="193"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Tipo de Enlace" dataDxfId="192"/>
+    <tableColumn id="21" xr3:uid="{9EA0CAA5-0A23-473B-943E-3CC802BE75BA}" name="Canal" dataDxfId="191"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Activo" dataDxfId="190"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tipo de Justificación" dataDxfId="189"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Coste" dataDxfId="188">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="206">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Eficiencia" dataDxfId="187">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],5,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="205">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Exposición" dataDxfId="186">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],6,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="204">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Capacidad" dataDxfId="185">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],7,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="203">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Resiliencia" dataDxfId="184">
       <calculatedColumnFormula>VLOOKUP(tblEnlaces[[#This Row],[Canal]],tblCanales[#All],8,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{D5ECEEAB-319C-416C-A120-BD842AFC8541}" name="Coste (peso)" dataDxfId="202" totalsRowDxfId="201">
+    <tableColumn id="23" xr3:uid="{D5ECEEAB-319C-416C-A120-BD842AFC8541}" name="Coste (peso)" dataDxfId="183" totalsRowDxfId="182">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Coste]],tblPesosCoste[Valor],tblPesosCoste[Coste],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{38505D25-3830-4BBB-8DCF-E8583124C910}" name="Eficiencia (peso)" dataDxfId="200" totalsRowDxfId="199">
+    <tableColumn id="24" xr3:uid="{38505D25-3830-4BBB-8DCF-E8583124C910}" name="Eficiencia (peso)" dataDxfId="181" totalsRowDxfId="180">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Eficiencia]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Eficiencia],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{8E52D89B-D169-4F48-AD66-44B1E56CB633}" name="Exposición (peso)" dataDxfId="198" totalsRowDxfId="197">
+    <tableColumn id="25" xr3:uid="{8E52D89B-D169-4F48-AD66-44B1E56CB633}" name="Exposición (peso)" dataDxfId="179" totalsRowDxfId="178">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Exposición]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Exposición],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{1F2413A4-A4B8-4902-8061-3A60A70F9F2F}" name="Capacidad (peso)" dataDxfId="196" totalsRowDxfId="195">
+    <tableColumn id="26" xr3:uid="{1F2413A4-A4B8-4902-8061-3A60A70F9F2F}" name="Capacidad (peso)" dataDxfId="177" totalsRowDxfId="176">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Capacidad]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Capacidad],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{67FAA096-3D2B-4E91-9E1F-AEE59F7A690B}" name="Resiliencia (peso)" dataDxfId="194" totalsRowDxfId="193">
+    <tableColumn id="27" xr3:uid="{67FAA096-3D2B-4E91-9E1F-AEE59F7A690B}" name="Resiliencia (peso)" dataDxfId="175" totalsRowDxfId="174">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tblEnlaces[[#This Row],[Resiliencia]],tblPesosValorOperativo[Valor],tblPesosValorOperativo[Resiliencia],0),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{378FBC0C-D6D1-4CC5-A688-4AE8E0EEFF15}" name="Valor Operativo (peso)" dataDxfId="192" totalsRowDxfId="191">
+    <tableColumn id="28" xr3:uid="{378FBC0C-D6D1-4CC5-A688-4AE8E0EEFF15}" name="Valor Operativo (peso)" dataDxfId="173" totalsRowDxfId="172">
       <calculatedColumnFormula>tblEnlaces[[#This Row],[Eficiencia (peso)]]+tblEnlaces[[#This Row],[Resiliencia (peso)]]+tblEnlaces[[#This Row],[Capacidad (peso)]]+tblEnlaces[[#This Row],[Exposición (peso)]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7514,80 +7514,80 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}" name="tblNodos" displayName="tblNodos" ref="A4:D23" headerRowDxfId="190" dataDxfId="189" totalsRowDxfId="188">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}" name="tblNodos" displayName="tblNodos" ref="A4:D23" headerRowDxfId="171" dataDxfId="170" totalsRowDxfId="169">
   <autoFilter ref="A4:D23" xr:uid="{EDC6F96A-F4EE-47C4-BDEE-5FEF01404F9B}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C216D4B9-76C9-4611-A97A-027837B07F56}" name="NodoID" dataDxfId="187"/>
-    <tableColumn id="2" xr3:uid="{425384C0-D0A9-4E9A-A93C-65C1B3B77DB1}" name="Nombre" dataDxfId="186"/>
-    <tableColumn id="3" xr3:uid="{434558A9-CDA8-4827-AF85-9621517F0875}" name="Tipo" dataDxfId="185"/>
-    <tableColumn id="4" xr3:uid="{B0504143-65F8-445A-9B1A-9CA91BFF8129}" name="Activo" dataDxfId="184"/>
+    <tableColumn id="1" xr3:uid="{C216D4B9-76C9-4611-A97A-027837B07F56}" name="NodoID" dataDxfId="168"/>
+    <tableColumn id="2" xr3:uid="{425384C0-D0A9-4E9A-A93C-65C1B3B77DB1}" name="Nombre" dataDxfId="167"/>
+    <tableColumn id="3" xr3:uid="{434558A9-CDA8-4827-AF85-9621517F0875}" name="Tipo" dataDxfId="166"/>
+    <tableColumn id="4" xr3:uid="{B0504143-65F8-445A-9B1A-9CA91BFF8129}" name="Activo" dataDxfId="165"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="183" dataDxfId="181" headerRowBorderDxfId="182" tableBorderDxfId="180" totalsRowBorderDxfId="179">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblMatrizDeAdyacencia" displayName="tblMatrizDeAdyacencia" ref="B3:V22" totalsRowShown="0" headerRowDxfId="164" dataDxfId="162" headerRowBorderDxfId="163" tableBorderDxfId="161" totalsRowBorderDxfId="160">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="178">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Nombre Nodo" dataDxfId="159">
       <calculatedColumnFormula>VLOOKUP(tblMatrizDeAdyacencia[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="177"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="176">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="NodoOrigen \ NodoDestino" dataDxfId="158"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="O1" dataDxfId="157">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,D$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="175">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="O2" dataDxfId="156">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,E$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="174">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="O3" dataDxfId="155">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,F$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="173">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="O4" dataDxfId="154">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,G$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="172">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="O5" dataDxfId="153">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,H$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="171">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="O6" dataDxfId="152">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,I$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="C1" dataDxfId="170">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="C1" dataDxfId="151">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,J$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="C2" dataDxfId="169">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="C2" dataDxfId="150">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,K$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="C3" dataDxfId="168">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="C3" dataDxfId="149">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,L$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="R1" dataDxfId="167">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="R1" dataDxfId="148">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,M$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="R2" dataDxfId="166">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="R2" dataDxfId="147">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,N$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="R3" dataDxfId="165">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="R3" dataDxfId="146">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,O$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="R4" dataDxfId="164">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="R4" dataDxfId="145">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,P$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="R5" dataDxfId="163">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="R5" dataDxfId="144">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,Q$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="R6" dataDxfId="162">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="R6" dataDxfId="143">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,R$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="R7" dataDxfId="161">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="R7" dataDxfId="142">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,S$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="R8" dataDxfId="160">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="R8" dataDxfId="141">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,T$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="R9" dataDxfId="159">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="R9" dataDxfId="140">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,U$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D1" dataDxfId="158">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="D1" dataDxfId="139">
       <calculatedColumnFormula>IF(COUNTIFS(Red!$G$5:$G$30,$C4,Red!$H$5:$H$30,V$3,Red!$K$5:$K$30,1)&gt;0,1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7596,67 +7596,67 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{619F938E-46CC-49F1-9A1F-6017755965D1}" name="tblMatrizPonderadaCostes" displayName="tblMatrizPonderadaCostes" ref="B3:V22" totalsRowShown="0" headerRowDxfId="157" dataDxfId="155" headerRowBorderDxfId="156" tableBorderDxfId="154" totalsRowBorderDxfId="153">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{619F938E-46CC-49F1-9A1F-6017755965D1}" name="tblMatrizPonderadaCostes" displayName="tblMatrizPonderadaCostes" ref="B3:V22" totalsRowShown="0" headerRowDxfId="138" dataDxfId="136" headerRowBorderDxfId="137" tableBorderDxfId="135" totalsRowBorderDxfId="134">
   <tableColumns count="21">
-    <tableColumn id="21" xr3:uid="{2A9AC9D7-CC14-4058-8CF2-7CDFEC15F78F}" name="Nombre Nodo" dataDxfId="11">
+    <tableColumn id="21" xr3:uid="{2A9AC9D7-CC14-4058-8CF2-7CDFEC15F78F}" name="Nombre Nodo" dataDxfId="133">
       <calculatedColumnFormula>VLOOKUP(tblMatrizPonderadaCostes[[#This Row],[NodoOrigen \ NodoDestino]],tblNodos[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{3A911174-7F39-43D0-8D1B-0D1A251C78CF}" name="NodoOrigen \ NodoDestino" dataDxfId="152"/>
-    <tableColumn id="2" xr3:uid="{79E6108F-3B54-4663-83BD-0E9A6288B0A8}" name="O1" dataDxfId="151">
+    <tableColumn id="1" xr3:uid="{3A911174-7F39-43D0-8D1B-0D1A251C78CF}" name="NodoOrigen \ NodoDestino" dataDxfId="132"/>
+    <tableColumn id="2" xr3:uid="{79E6108F-3B54-4663-83BD-0E9A6288B0A8}" name="O1" dataDxfId="131">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!D4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],D$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{74BBA163-10F6-4D74-863C-C4517633500F}" name="O2" dataDxfId="150">
+    <tableColumn id="3" xr3:uid="{74BBA163-10F6-4D74-863C-C4517633500F}" name="O2" dataDxfId="130">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!E4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],E$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5D6ADA5C-E165-41EC-803D-18F7A270611C}" name="O3" dataDxfId="149">
+    <tableColumn id="4" xr3:uid="{5D6ADA5C-E165-41EC-803D-18F7A270611C}" name="O3" dataDxfId="129">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!F4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],F$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{035B34FA-1623-4B86-B0EE-0CC6694FFD7C}" name="O4" dataDxfId="148">
+    <tableColumn id="5" xr3:uid="{035B34FA-1623-4B86-B0EE-0CC6694FFD7C}" name="O4" dataDxfId="128">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!G4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],G$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{27739639-E082-4698-9A4C-15EDA8612A83}" name="O5" dataDxfId="147">
+    <tableColumn id="6" xr3:uid="{27739639-E082-4698-9A4C-15EDA8612A83}" name="O5" dataDxfId="127">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!H4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],H$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{ED768978-7E7B-49CD-A202-FE8EBE9E64E0}" name="O6" dataDxfId="146">
+    <tableColumn id="7" xr3:uid="{ED768978-7E7B-49CD-A202-FE8EBE9E64E0}" name="O6" dataDxfId="126">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!I4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],I$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{37684012-4DC0-48DA-8E67-185403ABB81C}" name="C1" dataDxfId="145">
+    <tableColumn id="8" xr3:uid="{37684012-4DC0-48DA-8E67-185403ABB81C}" name="C1" dataDxfId="125">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!J4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],J$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E3684910-7769-4AEF-8800-33DC2F8D7ABC}" name="C2" dataDxfId="144">
+    <tableColumn id="9" xr3:uid="{E3684910-7769-4AEF-8800-33DC2F8D7ABC}" name="C2" dataDxfId="124">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!K4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],K$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A095B3C4-5019-4082-93A5-E12BDE733061}" name="C3" dataDxfId="143">
+    <tableColumn id="10" xr3:uid="{A095B3C4-5019-4082-93A5-E12BDE733061}" name="C3" dataDxfId="123">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!L4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],L$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{C5072B89-856A-4694-9D8B-17C4DB67DFF8}" name="R1" dataDxfId="142">
+    <tableColumn id="11" xr3:uid="{C5072B89-856A-4694-9D8B-17C4DB67DFF8}" name="R1" dataDxfId="122">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!M4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],M$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{0BD76649-1EE0-46D9-8718-F9A6F67BE379}" name="R2" dataDxfId="141">
+    <tableColumn id="12" xr3:uid="{0BD76649-1EE0-46D9-8718-F9A6F67BE379}" name="R2" dataDxfId="121">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!N4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],N$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{263255E9-BE7D-4E45-A463-5AD358998CB9}" name="R3" dataDxfId="140">
+    <tableColumn id="13" xr3:uid="{263255E9-BE7D-4E45-A463-5AD358998CB9}" name="R3" dataDxfId="120">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!O4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],O$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{7AF510BB-CB1B-461F-8746-C7133DC25996}" name="R4" dataDxfId="139">
+    <tableColumn id="14" xr3:uid="{7AF510BB-CB1B-461F-8746-C7133DC25996}" name="R4" dataDxfId="119">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!P4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],P$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{42A7B19E-8A6C-4FA9-A2E9-2B83EC8917D4}" name="R5" dataDxfId="138">
+    <tableColumn id="15" xr3:uid="{42A7B19E-8A6C-4FA9-A2E9-2B83EC8917D4}" name="R5" dataDxfId="118">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!Q4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],Q$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C9AE28B0-4117-4A3D-8381-F7E9417F1616}" name="R6" dataDxfId="137">
+    <tableColumn id="16" xr3:uid="{C9AE28B0-4117-4A3D-8381-F7E9417F1616}" name="R6" dataDxfId="117">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!R4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],R$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{92A0B734-1347-429D-A2CB-8D857E4CD34E}" name="R7" dataDxfId="136">
+    <tableColumn id="17" xr3:uid="{92A0B734-1347-429D-A2CB-8D857E4CD34E}" name="R7" dataDxfId="116">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!S4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],S$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{667134D2-C221-4A4D-9FB1-909ACDC0DDB5}" name="R8" dataDxfId="135">
+    <tableColumn id="18" xr3:uid="{667134D2-C221-4A4D-9FB1-909ACDC0DDB5}" name="R8" dataDxfId="115">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!T4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],T$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{338C87EB-B9DD-49EE-9C5C-4BCE63EF4744}" name="R9" dataDxfId="134">
+    <tableColumn id="19" xr3:uid="{338C87EB-B9DD-49EE-9C5C-4BCE63EF4744}" name="R9" dataDxfId="114">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!U4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],U$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{6E3807F5-486A-4D01-9C7A-D8CBDABFB157}" name="D1" dataDxfId="133">
+    <tableColumn id="20" xr3:uid="{6E3807F5-486A-4D01-9C7A-D8CBDABFB157}" name="D1" dataDxfId="113">
       <calculatedColumnFormula>IF(MatrizDeAdyacencia!V4=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C4,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7665,24 +7665,24 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}" name="tblPesosCoste" displayName="tblPesosCoste" ref="Y4:Z9" totalsRowShown="0" headerRowDxfId="132" dataDxfId="130" headerRowBorderDxfId="131" tableBorderDxfId="129">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}" name="tblPesosCoste" displayName="tblPesosCoste" ref="Y4:Z9" totalsRowShown="0" headerRowDxfId="112" dataDxfId="110" headerRowBorderDxfId="111" tableBorderDxfId="109">
   <autoFilter ref="Y4:Z9" xr:uid="{53A860C4-F3F6-438A-94ED-DFA95D98100E}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E1E6CBAC-71D7-49B4-97B4-D7CD1992E449}" name="Valor" dataDxfId="128"/>
-    <tableColumn id="4" xr3:uid="{5D97B706-55F4-46C7-B8B4-663F39805E8B}" name="Coste" dataDxfId="127"/>
+    <tableColumn id="1" xr3:uid="{E1E6CBAC-71D7-49B4-97B4-D7CD1992E449}" name="Valor" dataDxfId="108"/>
+    <tableColumn id="4" xr3:uid="{5D97B706-55F4-46C7-B8B4-663F39805E8B}" name="Coste" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66EEA98C-81AE-44A3-B7B7-DDC02BD7FDF3}" name="tblRangoEnlace" displayName="tblRangoEnlace" ref="Y12:Z14" totalsRowShown="0" headerRowDxfId="126" headerRowBorderDxfId="125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{66EEA98C-81AE-44A3-B7B7-DDC02BD7FDF3}" name="tblRangoEnlace" displayName="tblRangoEnlace" ref="Y12:Z14" totalsRowShown="0" headerRowDxfId="106" headerRowBorderDxfId="105">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{241E10B4-3B7B-4E19-92EA-AA4D53964641}" name="Rango del Enlace" dataDxfId="124"/>
-    <tableColumn id="2" xr3:uid="{20B4E6FB-3DB7-4113-AD20-5780FA4D1775}" name="Coste" dataDxfId="123"/>
+    <tableColumn id="1" xr3:uid="{241E10B4-3B7B-4E19-92EA-AA4D53964641}" name="Rango del Enlace" dataDxfId="104"/>
+    <tableColumn id="2" xr3:uid="{20B4E6FB-3DB7-4113-AD20-5780FA4D1775}" name="Coste" dataDxfId="103"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -7982,25 +7982,25 @@
     <col min="1" max="1" width="11.42578125" style="15" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" style="15" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" style="15" customWidth="1"/>
-    <col min="4" max="4" width="66.85546875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="42.5703125" style="15" customWidth="1"/>
     <col min="5" max="16384" width="11.42578125" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
+      <c r="A1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
     </row>
     <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
     </row>
     <row r="4" spans="1:4" s="16" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -8016,7 +8016,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>105</v>
       </c>
@@ -8044,7 +8044,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>108</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -8145,23 +8145,23 @@
     </row>
     <row r="2" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="C3" s="76"/>
+      <c r="C3" s="79"/>
       <c r="D3" s="69"/>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="84" t="s">
         <v>168</v>
       </c>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
       <c r="O3" s="16"/>
     </row>
     <row r="4" spans="2:15" s="16" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -8613,34 +8613,34 @@
       <c r="L37" s="24"/>
     </row>
     <row r="38" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="77" t="s">
+      <c r="B38" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="78"/>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="78"/>
-      <c r="H38" s="78"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="78"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="78"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="81"/>
+      <c r="K38" s="81"/>
+      <c r="L38" s="81"/>
     </row>
     <row r="39" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="79" t="s">
+      <c r="B39" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="C39" s="80"/>
-      <c r="D39" s="80"/>
-      <c r="E39" s="80"/>
-      <c r="F39" s="80"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="80"/>
-      <c r="I39" s="80"/>
-      <c r="J39" s="80"/>
-      <c r="K39" s="80"/>
-      <c r="L39" s="80"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="83"/>
+      <c r="I39" s="83"/>
+      <c r="J39" s="83"/>
+      <c r="K39" s="83"/>
+      <c r="L39" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8688,55 +8688,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="84" t="s">
+      <c r="A1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
     </row>
     <row r="3" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="F3" s="81" t="s">
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="F3" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="82"/>
-      <c r="S3" s="82"/>
-      <c r="T3" s="82"/>
-      <c r="U3" s="82"/>
-      <c r="V3" s="82"/>
-      <c r="W3" s="82"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
+      <c r="Q3" s="85"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
+      <c r="U3" s="85"/>
+      <c r="V3" s="85"/>
+      <c r="W3" s="85"/>
     </row>
     <row r="4" spans="1:24" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -10854,10 +10854,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:27" s="13" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="73" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="88"/>
+      <c r="C2" s="75"/>
       <c r="D2" s="23" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -12619,52 +12619,52 @@
       </c>
     </row>
     <row r="25" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="85" t="s">
+      <c r="B25" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="86"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="86"/>
-      <c r="O25" s="86"/>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="86"/>
-      <c r="R25" s="86"/>
-      <c r="S25" s="86"/>
-      <c r="T25" s="86"/>
-      <c r="U25" s="86"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="89"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="89"/>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="89"/>
+      <c r="N25" s="89"/>
+      <c r="O25" s="89"/>
+      <c r="P25" s="89"/>
+      <c r="Q25" s="89"/>
+      <c r="R25" s="89"/>
+      <c r="S25" s="89"/>
+      <c r="T25" s="89"/>
+      <c r="U25" s="89"/>
     </row>
     <row r="26" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="85" t="s">
+      <c r="B26" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="86"/>
-      <c r="M26" s="86"/>
-      <c r="N26" s="86"/>
-      <c r="O26" s="86"/>
-      <c r="P26" s="86"/>
-      <c r="Q26" s="86"/>
-      <c r="R26" s="86"/>
-      <c r="S26" s="86"/>
-      <c r="T26" s="86"/>
-      <c r="U26" s="86"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="89"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="89"/>
+      <c r="K26" s="89"/>
+      <c r="L26" s="89"/>
+      <c r="M26" s="89"/>
+      <c r="N26" s="89"/>
+      <c r="O26" s="89"/>
+      <c r="P26" s="89"/>
+      <c r="Q26" s="89"/>
+      <c r="R26" s="89"/>
+      <c r="S26" s="89"/>
+      <c r="T26" s="89"/>
+      <c r="U26" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -12673,10 +12673,10 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:V22">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12705,10 +12705,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:27" s="13" customFormat="1" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="88"/>
+      <c r="C2" s="75"/>
       <c r="D2" s="23" t="str">
         <f>VLOOKUP(tblMatrizPonderadaCostes[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -12851,10 +12851,10 @@
       <c r="V3" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="Y3" s="90" t="s">
+      <c r="Y3" s="91" t="s">
         <v>83</v>
       </c>
-      <c r="Z3" s="91"/>
+      <c r="Z3" s="92"/>
     </row>
     <row r="4" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="str">
@@ -13573,10 +13573,10 @@
         <f>IF(MatrizDeAdyacencia!V11=1,SUMIFS(tblEnlaces[Coste (peso)],tblEnlaces[Nodo Origen],$C11,tblEnlaces[Nodo Destino],V$3,tblEnlaces[Activo],1),0)</f>
         <v>0</v>
       </c>
-      <c r="Y11" s="89" t="s">
+      <c r="Y11" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="Z11" s="89"/>
+      <c r="Z11" s="90"/>
       <c r="AA11" s="32"/>
     </row>
     <row r="12" spans="2:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14551,7 +14551,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14587,10 +14587,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" s="13" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="73" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="88"/>
+      <c r="C2" s="75"/>
       <c r="D2" s="23" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -14744,13 +14744,13 @@
       <c r="V3" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="Y3" s="90" t="s">
+      <c r="Y3" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="Z3" s="91"/>
-      <c r="AA3" s="91"/>
-      <c r="AB3" s="91"/>
-      <c r="AC3" s="91"/>
+      <c r="Z3" s="92"/>
+      <c r="AA3" s="92"/>
+      <c r="AB3" s="92"/>
+      <c r="AC3" s="92"/>
       <c r="AD3" s="39"/>
       <c r="AF3"/>
       <c r="AG3"/>
@@ -16757,7 +16757,7 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:I4 L4:V4 D5:V22">
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16784,7 +16784,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16817,10 +16817,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:44" s="13" customFormat="1" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="73" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="88"/>
+      <c r="C2" s="75"/>
       <c r="D2" s="23" t="str">
         <f>VLOOKUP(tblMatrizDeAdyacencia[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -16898,10 +16898,10 @@
         <v>Destino operativo final</v>
       </c>
       <c r="W2"/>
-      <c r="X2" s="87" t="s">
+      <c r="X2" s="73" t="s">
         <v>103</v>
       </c>
-      <c r="Y2" s="88"/>
+      <c r="Y2" s="75"/>
       <c r="Z2" s="23" t="str">
         <f>VLOOKUP(tblMatrizDistancias[[#Headers],[O1]],tblNodos[],2,FALSE)</f>
         <v>Extorsión local</v>
@@ -27990,7 +27990,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="66" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28003,7 +28003,7 @@
         <color rgb="FFFCFCFF"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>9999</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28033,15 +28033,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="73" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="88"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
       <c r="I2" s="23"/>
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
@@ -36661,7 +36661,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="64" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
